--- a/quiniela_mundial_2026.xlsx
+++ b/quiniela_mundial_2026.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Bracket" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Referencias" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Clasificados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Bracket" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Referencias" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="29">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -107,6 +108,42 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="002F2F2F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00276221"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="009C5700"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="009C5700"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00F4C842"/>
       <sz val="20"/>
     </font>
@@ -156,18 +193,6 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00D9D9D9"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="002F2F2F"/>
       <sz val="9"/>
     </font>
     <font>
@@ -237,17 +262,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -394,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -432,38 +457,62 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -472,64 +521,58 @@
     <xf numFmtId="0" fontId="2" fillId="14" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -940,27 +983,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R198"/>
+  <dimension ref="A1:S197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="3" customWidth="1" min="8" max="8"/>
-    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="5" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
     <col width="5" customWidth="1" min="17" max="17"/>
     <col width="5" customWidth="1" min="18" max="18"/>
+    <col hidden="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1061,6 +1105,10 @@
         <f>3*L3+M3</f>
         <v/>
       </c>
+      <c r="S3">
+        <f>R3*10000000+(Q3+99)*100000+O3*100+4</f>
+        <v/>
+      </c>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="I4" s="3" t="inlineStr"/>
@@ -1101,6 +1149,10 @@
         <f>3*L4+M4</f>
         <v/>
       </c>
+      <c r="S4">
+        <f>R4*10000000+(Q4+99)*100000+O4*100+3</f>
+        <v/>
+      </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="I5" s="3" t="inlineStr"/>
@@ -1141,6 +1193,10 @@
         <f>3*L5+M5</f>
         <v/>
       </c>
+      <c r="S5">
+        <f>R5*10000000+(Q5+99)*100000+O5*100+2</f>
+        <v/>
+      </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="I6" s="3" t="inlineStr"/>
@@ -1181,6 +1237,10 @@
         <f>3*L6+M6</f>
         <v/>
       </c>
+      <c r="S6">
+        <f>R6*10000000+(Q6+99)*100000+O6*100+1</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
@@ -1464,11 +1524,11 @@
         <v/>
       </c>
       <c r="O19" s="5">
-        <f>IF(AND(D25&lt;&gt;"",E25&lt;&gt;""),D25,0)+IF(AND(D28&lt;&gt;"",E28&lt;&gt;""),D28,0)+IF(AND(D29&lt;&gt;"",E29&lt;&gt;""),D29,0)</f>
+        <f>IF(AND(D25&lt;&gt;"",E25&lt;&gt;""),D25,0)+IF(AND(D28&lt;&gt;"",E28&lt;&gt;""),D28,0)+IF(AND(D29&lt;&gt;"",E29&lt;&gt;""),D29,0)+0</f>
         <v/>
       </c>
       <c r="P19" s="5">
-        <f>IF(AND(D25&lt;&gt;"",E25&lt;&gt;""),E25,0)+IF(AND(D28&lt;&gt;"",E28&lt;&gt;""),E28,0)+IF(AND(D29&lt;&gt;"",E29&lt;&gt;""),E29,0)</f>
+        <f>IF(AND(D25&lt;&gt;"",E25&lt;&gt;""),E25,0)+IF(AND(D28&lt;&gt;"",E28&lt;&gt;""),E28,0)+IF(AND(D29&lt;&gt;"",E29&lt;&gt;""),E29,0)+0</f>
         <v/>
       </c>
       <c r="Q19" s="5">
@@ -1477,6 +1537,10 @@
       </c>
       <c r="R19" s="5">
         <f>3*L19+M19</f>
+        <v/>
+      </c>
+      <c r="S19">
+        <f>R19*10000000+(Q19+99)*100000+O19*100+4</f>
         <v/>
       </c>
     </row>
@@ -1519,6 +1583,10 @@
         <f>3*L20+M20</f>
         <v/>
       </c>
+      <c r="S20">
+        <f>R20*10000000+(Q20+99)*100000+O20*100+3</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="I21" s="3" t="inlineStr"/>
@@ -1559,6 +1627,10 @@
         <f>3*L21+M21</f>
         <v/>
       </c>
+      <c r="S21">
+        <f>R21*10000000+(Q21+99)*100000+O21*100+2</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="I22" s="3" t="inlineStr"/>
@@ -1599,6 +1671,10 @@
         <f>3*L22+M22</f>
         <v/>
       </c>
+      <c r="S22">
+        <f>R22*10000000+(Q22+99)*100000+O22*100+1</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
@@ -1897,6 +1973,10 @@
         <f>3*L35+M35</f>
         <v/>
       </c>
+      <c r="S35">
+        <f>R35*10000000+(Q35+99)*100000+O35*100+4</f>
+        <v/>
+      </c>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="I36" s="3" t="inlineStr"/>
@@ -1937,6 +2017,10 @@
         <f>3*L36+M36</f>
         <v/>
       </c>
+      <c r="S36">
+        <f>R36*10000000+(Q36+99)*100000+O36*100+3</f>
+        <v/>
+      </c>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="I37" s="3" t="inlineStr"/>
@@ -1977,6 +2061,10 @@
         <f>3*L37+M37</f>
         <v/>
       </c>
+      <c r="S37">
+        <f>R37*10000000+(Q37+99)*100000+O37*100+2</f>
+        <v/>
+      </c>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="I38" s="3" t="inlineStr"/>
@@ -2017,6 +2105,10 @@
         <f>3*L38+M38</f>
         <v/>
       </c>
+      <c r="S38">
+        <f>R38*10000000+(Q38+99)*100000+O38*100+1</f>
+        <v/>
+      </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
@@ -2315,6 +2407,10 @@
         <f>3*L51+M51</f>
         <v/>
       </c>
+      <c r="S51">
+        <f>R51*10000000+(Q51+99)*100000+O51*100+4</f>
+        <v/>
+      </c>
     </row>
     <row r="52" ht="17" customHeight="1">
       <c r="I52" s="3" t="inlineStr"/>
@@ -2355,6 +2451,10 @@
         <f>3*L52+M52</f>
         <v/>
       </c>
+      <c r="S52">
+        <f>R52*10000000+(Q52+99)*100000+O52*100+3</f>
+        <v/>
+      </c>
     </row>
     <row r="53" ht="17" customHeight="1">
       <c r="I53" s="3" t="inlineStr"/>
@@ -2395,6 +2495,10 @@
         <f>3*L53+M53</f>
         <v/>
       </c>
+      <c r="S53">
+        <f>R53*10000000+(Q53+99)*100000+O53*100+2</f>
+        <v/>
+      </c>
     </row>
     <row r="54" ht="17" customHeight="1">
       <c r="I54" s="3" t="inlineStr"/>
@@ -2435,6 +2539,10 @@
         <f>3*L54+M54</f>
         <v/>
       </c>
+      <c r="S54">
+        <f>R54*10000000+(Q54+99)*100000+O54*100+1</f>
+        <v/>
+      </c>
     </row>
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
@@ -2733,6 +2841,10 @@
         <f>3*L67+M67</f>
         <v/>
       </c>
+      <c r="S67">
+        <f>R67*10000000+(Q67+99)*100000+O67*100+4</f>
+        <v/>
+      </c>
     </row>
     <row r="68" ht="17" customHeight="1">
       <c r="I68" s="3" t="inlineStr"/>
@@ -2773,6 +2885,10 @@
         <f>3*L68+M68</f>
         <v/>
       </c>
+      <c r="S68">
+        <f>R68*10000000+(Q68+99)*100000+O68*100+3</f>
+        <v/>
+      </c>
     </row>
     <row r="69" ht="17" customHeight="1">
       <c r="I69" s="3" t="inlineStr"/>
@@ -2813,6 +2929,10 @@
         <f>3*L69+M69</f>
         <v/>
       </c>
+      <c r="S69">
+        <f>R69*10000000+(Q69+99)*100000+O69*100+2</f>
+        <v/>
+      </c>
     </row>
     <row r="70" ht="17" customHeight="1">
       <c r="I70" s="3" t="inlineStr"/>
@@ -2853,6 +2973,10 @@
         <f>3*L70+M70</f>
         <v/>
       </c>
+      <c r="S70">
+        <f>R70*10000000+(Q70+99)*100000+O70*100+1</f>
+        <v/>
+      </c>
     </row>
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
@@ -3151,6 +3275,10 @@
         <f>3*L83+M83</f>
         <v/>
       </c>
+      <c r="S83">
+        <f>R83*10000000+(Q83+99)*100000+O83*100+4</f>
+        <v/>
+      </c>
     </row>
     <row r="84" ht="17" customHeight="1">
       <c r="I84" s="3" t="inlineStr"/>
@@ -3191,6 +3319,10 @@
         <f>3*L84+M84</f>
         <v/>
       </c>
+      <c r="S84">
+        <f>R84*10000000+(Q84+99)*100000+O84*100+3</f>
+        <v/>
+      </c>
     </row>
     <row r="85" ht="17" customHeight="1">
       <c r="I85" s="3" t="inlineStr"/>
@@ -3231,6 +3363,10 @@
         <f>3*L85+M85</f>
         <v/>
       </c>
+      <c r="S85">
+        <f>R85*10000000+(Q85+99)*100000+O85*100+2</f>
+        <v/>
+      </c>
     </row>
     <row r="86" ht="17" customHeight="1">
       <c r="I86" s="3" t="inlineStr"/>
@@ -3271,6 +3407,10 @@
         <f>3*L86+M86</f>
         <v/>
       </c>
+      <c r="S86">
+        <f>R86*10000000+(Q86+99)*100000+O86*100+1</f>
+        <v/>
+      </c>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
@@ -3569,6 +3709,10 @@
         <f>3*L99+M99</f>
         <v/>
       </c>
+      <c r="S99">
+        <f>R99*10000000+(Q99+99)*100000+O99*100+4</f>
+        <v/>
+      </c>
     </row>
     <row r="100" ht="17" customHeight="1">
       <c r="I100" s="3" t="inlineStr"/>
@@ -3609,6 +3753,10 @@
         <f>3*L100+M100</f>
         <v/>
       </c>
+      <c r="S100">
+        <f>R100*10000000+(Q100+99)*100000+O100*100+3</f>
+        <v/>
+      </c>
     </row>
     <row r="101" ht="17" customHeight="1">
       <c r="I101" s="3" t="inlineStr"/>
@@ -3649,6 +3797,10 @@
         <f>3*L101+M101</f>
         <v/>
       </c>
+      <c r="S101">
+        <f>R101*10000000+(Q101+99)*100000+O101*100+2</f>
+        <v/>
+      </c>
     </row>
     <row r="102" ht="17" customHeight="1">
       <c r="I102" s="3" t="inlineStr"/>
@@ -3689,6 +3841,10 @@
         <f>3*L102+M102</f>
         <v/>
       </c>
+      <c r="S102">
+        <f>R102*10000000+(Q102+99)*100000+O102*100+1</f>
+        <v/>
+      </c>
     </row>
     <row r="104" ht="16" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
@@ -3987,6 +4143,10 @@
         <f>3*L115+M115</f>
         <v/>
       </c>
+      <c r="S115">
+        <f>R115*10000000+(Q115+99)*100000+O115*100+4</f>
+        <v/>
+      </c>
     </row>
     <row r="116" ht="17" customHeight="1">
       <c r="I116" s="3" t="inlineStr"/>
@@ -4027,6 +4187,10 @@
         <f>3*L116+M116</f>
         <v/>
       </c>
+      <c r="S116">
+        <f>R116*10000000+(Q116+99)*100000+O116*100+3</f>
+        <v/>
+      </c>
     </row>
     <row r="117" ht="17" customHeight="1">
       <c r="I117" s="3" t="inlineStr"/>
@@ -4067,6 +4231,10 @@
         <f>3*L117+M117</f>
         <v/>
       </c>
+      <c r="S117">
+        <f>R117*10000000+(Q117+99)*100000+O117*100+2</f>
+        <v/>
+      </c>
     </row>
     <row r="118" ht="17" customHeight="1">
       <c r="I118" s="3" t="inlineStr"/>
@@ -4107,6 +4275,10 @@
         <f>3*L118+M118</f>
         <v/>
       </c>
+      <c r="S118">
+        <f>R118*10000000+(Q118+99)*100000+O118*100+1</f>
+        <v/>
+      </c>
     </row>
     <row r="120" ht="16" customHeight="1">
       <c r="A120" s="6" t="inlineStr">
@@ -4405,6 +4577,10 @@
         <f>3*L131+M131</f>
         <v/>
       </c>
+      <c r="S131">
+        <f>R131*10000000+(Q131+99)*100000+O131*100+4</f>
+        <v/>
+      </c>
     </row>
     <row r="132" ht="17" customHeight="1">
       <c r="I132" s="3" t="inlineStr"/>
@@ -4445,6 +4621,10 @@
         <f>3*L132+M132</f>
         <v/>
       </c>
+      <c r="S132">
+        <f>R132*10000000+(Q132+99)*100000+O132*100+3</f>
+        <v/>
+      </c>
     </row>
     <row r="133" ht="17" customHeight="1">
       <c r="I133" s="3" t="inlineStr"/>
@@ -4485,6 +4665,10 @@
         <f>3*L133+M133</f>
         <v/>
       </c>
+      <c r="S133">
+        <f>R133*10000000+(Q133+99)*100000+O133*100+2</f>
+        <v/>
+      </c>
     </row>
     <row r="134" ht="17" customHeight="1">
       <c r="I134" s="3" t="inlineStr"/>
@@ -4525,6 +4709,10 @@
         <f>3*L134+M134</f>
         <v/>
       </c>
+      <c r="S134">
+        <f>R134*10000000+(Q134+99)*100000+O134*100+1</f>
+        <v/>
+      </c>
     </row>
     <row r="136" ht="16" customHeight="1">
       <c r="A136" s="6" t="inlineStr">
@@ -4823,6 +5011,10 @@
         <f>3*L147+M147</f>
         <v/>
       </c>
+      <c r="S147">
+        <f>R147*10000000+(Q147+99)*100000+O147*100+4</f>
+        <v/>
+      </c>
     </row>
     <row r="148" ht="17" customHeight="1">
       <c r="I148" s="3" t="inlineStr"/>
@@ -4863,6 +5055,10 @@
         <f>3*L148+M148</f>
         <v/>
       </c>
+      <c r="S148">
+        <f>R148*10000000+(Q148+99)*100000+O148*100+3</f>
+        <v/>
+      </c>
     </row>
     <row r="149" ht="17" customHeight="1">
       <c r="I149" s="3" t="inlineStr"/>
@@ -4903,6 +5099,10 @@
         <f>3*L149+M149</f>
         <v/>
       </c>
+      <c r="S149">
+        <f>R149*10000000+(Q149+99)*100000+O149*100+2</f>
+        <v/>
+      </c>
     </row>
     <row r="150" ht="17" customHeight="1">
       <c r="I150" s="3" t="inlineStr"/>
@@ -4943,6 +5143,10 @@
         <f>3*L150+M150</f>
         <v/>
       </c>
+      <c r="S150">
+        <f>R150*10000000+(Q150+99)*100000+O150*100+1</f>
+        <v/>
+      </c>
     </row>
     <row r="152" ht="16" customHeight="1">
       <c r="A152" s="6" t="inlineStr">
@@ -5241,6 +5445,10 @@
         <f>3*L163+M163</f>
         <v/>
       </c>
+      <c r="S163">
+        <f>R163*10000000+(Q163+99)*100000+O163*100+4</f>
+        <v/>
+      </c>
     </row>
     <row r="164" ht="17" customHeight="1">
       <c r="I164" s="3" t="inlineStr"/>
@@ -5281,6 +5489,10 @@
         <f>3*L164+M164</f>
         <v/>
       </c>
+      <c r="S164">
+        <f>R164*10000000+(Q164+99)*100000+O164*100+3</f>
+        <v/>
+      </c>
     </row>
     <row r="165" ht="17" customHeight="1">
       <c r="I165" s="3" t="inlineStr"/>
@@ -5321,6 +5533,10 @@
         <f>3*L165+M165</f>
         <v/>
       </c>
+      <c r="S165">
+        <f>R165*10000000+(Q165+99)*100000+O165*100+2</f>
+        <v/>
+      </c>
     </row>
     <row r="166" ht="17" customHeight="1">
       <c r="I166" s="3" t="inlineStr"/>
@@ -5361,6 +5577,10 @@
         <f>3*L166+M166</f>
         <v/>
       </c>
+      <c r="S166">
+        <f>R166*10000000+(Q166+99)*100000+O166*100+1</f>
+        <v/>
+      </c>
     </row>
     <row r="168" ht="16" customHeight="1">
       <c r="A168" s="6" t="inlineStr">
@@ -5659,6 +5879,10 @@
         <f>3*L179+M179</f>
         <v/>
       </c>
+      <c r="S179">
+        <f>R179*10000000+(Q179+99)*100000+O179*100+4</f>
+        <v/>
+      </c>
     </row>
     <row r="180" ht="17" customHeight="1">
       <c r="I180" s="3" t="inlineStr"/>
@@ -5699,6 +5923,10 @@
         <f>3*L180+M180</f>
         <v/>
       </c>
+      <c r="S180">
+        <f>R180*10000000+(Q180+99)*100000+O180*100+3</f>
+        <v/>
+      </c>
     </row>
     <row r="181" ht="17" customHeight="1">
       <c r="I181" s="3" t="inlineStr"/>
@@ -5739,6 +5967,10 @@
         <f>3*L181+M181</f>
         <v/>
       </c>
+      <c r="S181">
+        <f>R181*10000000+(Q181+99)*100000+O181*100+2</f>
+        <v/>
+      </c>
     </row>
     <row r="182" ht="17" customHeight="1">
       <c r="I182" s="3" t="inlineStr"/>
@@ -5779,6 +6011,10 @@
         <f>3*L182+M182</f>
         <v/>
       </c>
+      <c r="S182">
+        <f>R182*10000000+(Q182+99)*100000+O182*100+1</f>
+        <v/>
+      </c>
     </row>
     <row r="184" ht="16" customHeight="1">
       <c r="A184" s="6" t="inlineStr">
@@ -5989,58 +6225,50 @@
     <row r="194" ht="16" customHeight="1">
       <c r="A194" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ✅  1st &amp; 2nd place — qualify automatically</t>
+          <t xml:space="preserve">  ✅  1st &amp; 2nd place — qualify automatically to Round of 32</t>
         </is>
       </c>
     </row>
     <row r="195" ht="16" customHeight="1">
       <c r="A195" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  🟢  2nd place — qualify automatically</t>
+          <t xml:space="preserve">  ⚠️   3rd place — may qualify as one of the 8 best third-place finishers</t>
         </is>
       </c>
     </row>
     <row r="196" ht="16" customHeight="1">
       <c r="A196" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ⚠️   3rd place — may qualify as best 3rd</t>
+          <t xml:space="preserve">  ❌  4th place — eliminated</t>
         </is>
       </c>
     </row>
     <row r="197" ht="16" customHeight="1">
       <c r="A197" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ❌  4th place — eliminated</t>
-        </is>
-      </c>
-    </row>
-    <row r="198" ht="16" customHeight="1">
-      <c r="A198" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ✏️   Yellow cell — enter goals here (integer ≥ 0)</t>
+          <t xml:space="preserve">  ✏️   Yellow cell — enter number of goals scored (integer ≥ 0)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A65:R65"/>
-    <mergeCell ref="A81:R81"/>
-    <mergeCell ref="A113:R113"/>
-    <mergeCell ref="A33:R33"/>
-    <mergeCell ref="A49:R49"/>
-    <mergeCell ref="A129:R129"/>
-    <mergeCell ref="A193:F193"/>
-    <mergeCell ref="A161:R161"/>
-    <mergeCell ref="A177:R177"/>
-    <mergeCell ref="A194:F194"/>
-    <mergeCell ref="A197:F197"/>
-    <mergeCell ref="A198:F198"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A17:R17"/>
-    <mergeCell ref="A196:F196"/>
-    <mergeCell ref="A97:R97"/>
-    <mergeCell ref="A195:F195"/>
-    <mergeCell ref="A145:R145"/>
+  <mergeCells count="17">
+    <mergeCell ref="A65:S65"/>
+    <mergeCell ref="A81:S81"/>
+    <mergeCell ref="A113:S113"/>
+    <mergeCell ref="A33:S33"/>
+    <mergeCell ref="A49:S49"/>
+    <mergeCell ref="A129:S129"/>
+    <mergeCell ref="A161:S161"/>
+    <mergeCell ref="A177:S177"/>
+    <mergeCell ref="A193:G193"/>
+    <mergeCell ref="A197:G197"/>
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A17:S17"/>
+    <mergeCell ref="A97:S97"/>
+    <mergeCell ref="A196:G196"/>
+    <mergeCell ref="A195:G195"/>
+    <mergeCell ref="A145:S145"/>
+    <mergeCell ref="A194:G194"/>
   </mergeCells>
   <conditionalFormatting sqref="I3:R6">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -6654,49 +6882,399 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ49"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  🏟️  Clasificados · Qualified Teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rankings update automatically as you enter scores in the Fase de Grupos tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>1st Place ✅</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>2nd Place ✅</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>3rd Place ⚠️</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>4th Place ❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Group A</t>
+        </is>
+      </c>
+      <c r="B4" s="22">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$3:$J$6,MATCH(LARGE('Fase de Grupos'!$S$3:$S$6,1),'Fase de Grupos'!$S$3:$S$6,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="C4" s="23">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$3:$J$6,MATCH(LARGE('Fase de Grupos'!$S$3:$S$6,2),'Fase de Grupos'!$S$3:$S$6,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="D4" s="24">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$3:$J$6,MATCH(LARGE('Fase de Grupos'!$S$3:$S$6,3),'Fase de Grupos'!$S$3:$S$6,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="E4" s="25">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$3:$J$6,MATCH(LARGE('Fase de Grupos'!$S$3:$S$6,4),'Fase de Grupos'!$S$3:$S$6,0)),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>Group B</t>
+        </is>
+      </c>
+      <c r="B5" s="22">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$19:$J$22,MATCH(LARGE('Fase de Grupos'!$S$19:$S$22,1),'Fase de Grupos'!$S$19:$S$22,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="C5" s="23">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$19:$J$22,MATCH(LARGE('Fase de Grupos'!$S$19:$S$22,2),'Fase de Grupos'!$S$19:$S$22,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="D5" s="24">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$19:$J$22,MATCH(LARGE('Fase de Grupos'!$S$19:$S$22,3),'Fase de Grupos'!$S$19:$S$22,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="E5" s="25">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$19:$J$22,MATCH(LARGE('Fase de Grupos'!$S$19:$S$22,4),'Fase de Grupos'!$S$19:$S$22,0)),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Group C</t>
+        </is>
+      </c>
+      <c r="B6" s="22">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$35:$J$38,MATCH(LARGE('Fase de Grupos'!$S$35:$S$38,1),'Fase de Grupos'!$S$35:$S$38,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="C6" s="23">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$35:$J$38,MATCH(LARGE('Fase de Grupos'!$S$35:$S$38,2),'Fase de Grupos'!$S$35:$S$38,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="D6" s="24">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$35:$J$38,MATCH(LARGE('Fase de Grupos'!$S$35:$S$38,3),'Fase de Grupos'!$S$35:$S$38,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="E6" s="25">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$35:$J$38,MATCH(LARGE('Fase de Grupos'!$S$35:$S$38,4),'Fase de Grupos'!$S$35:$S$38,0)),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Group D</t>
+        </is>
+      </c>
+      <c r="B7" s="22">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$51:$J$54,MATCH(LARGE('Fase de Grupos'!$S$51:$S$54,1),'Fase de Grupos'!$S$51:$S$54,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="C7" s="23">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$51:$J$54,MATCH(LARGE('Fase de Grupos'!$S$51:$S$54,2),'Fase de Grupos'!$S$51:$S$54,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="D7" s="24">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$51:$J$54,MATCH(LARGE('Fase de Grupos'!$S$51:$S$54,3),'Fase de Grupos'!$S$51:$S$54,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="E7" s="25">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$51:$J$54,MATCH(LARGE('Fase de Grupos'!$S$51:$S$54,4),'Fase de Grupos'!$S$51:$S$54,0)),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Group E</t>
+        </is>
+      </c>
+      <c r="B8" s="22">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$67:$J$70,MATCH(LARGE('Fase de Grupos'!$S$67:$S$70,1),'Fase de Grupos'!$S$67:$S$70,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="C8" s="23">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$67:$J$70,MATCH(LARGE('Fase de Grupos'!$S$67:$S$70,2),'Fase de Grupos'!$S$67:$S$70,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="D8" s="24">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$67:$J$70,MATCH(LARGE('Fase de Grupos'!$S$67:$S$70,3),'Fase de Grupos'!$S$67:$S$70,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="E8" s="25">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$67:$J$70,MATCH(LARGE('Fase de Grupos'!$S$67:$S$70,4),'Fase de Grupos'!$S$67:$S$70,0)),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Group F</t>
+        </is>
+      </c>
+      <c r="B9" s="22">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$83:$J$86,MATCH(LARGE('Fase de Grupos'!$S$83:$S$86,1),'Fase de Grupos'!$S$83:$S$86,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="C9" s="23">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$83:$J$86,MATCH(LARGE('Fase de Grupos'!$S$83:$S$86,2),'Fase de Grupos'!$S$83:$S$86,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="D9" s="24">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$83:$J$86,MATCH(LARGE('Fase de Grupos'!$S$83:$S$86,3),'Fase de Grupos'!$S$83:$S$86,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="E9" s="25">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$83:$J$86,MATCH(LARGE('Fase de Grupos'!$S$83:$S$86,4),'Fase de Grupos'!$S$83:$S$86,0)),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Group G</t>
+        </is>
+      </c>
+      <c r="B10" s="22">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$99:$J$102,MATCH(LARGE('Fase de Grupos'!$S$99:$S$102,1),'Fase de Grupos'!$S$99:$S$102,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="C10" s="23">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$99:$J$102,MATCH(LARGE('Fase de Grupos'!$S$99:$S$102,2),'Fase de Grupos'!$S$99:$S$102,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="D10" s="24">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$99:$J$102,MATCH(LARGE('Fase de Grupos'!$S$99:$S$102,3),'Fase de Grupos'!$S$99:$S$102,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="E10" s="25">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$99:$J$102,MATCH(LARGE('Fase de Grupos'!$S$99:$S$102,4),'Fase de Grupos'!$S$99:$S$102,0)),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Group H</t>
+        </is>
+      </c>
+      <c r="B11" s="22">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$115:$J$118,MATCH(LARGE('Fase de Grupos'!$S$115:$S$118,1),'Fase de Grupos'!$S$115:$S$118,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="C11" s="23">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$115:$J$118,MATCH(LARGE('Fase de Grupos'!$S$115:$S$118,2),'Fase de Grupos'!$S$115:$S$118,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="D11" s="24">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$115:$J$118,MATCH(LARGE('Fase de Grupos'!$S$115:$S$118,3),'Fase de Grupos'!$S$115:$S$118,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="E11" s="25">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$115:$J$118,MATCH(LARGE('Fase de Grupos'!$S$115:$S$118,4),'Fase de Grupos'!$S$115:$S$118,0)),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Group I</t>
+        </is>
+      </c>
+      <c r="B12" s="22">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$131:$J$134,MATCH(LARGE('Fase de Grupos'!$S$131:$S$134,1),'Fase de Grupos'!$S$131:$S$134,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="C12" s="23">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$131:$J$134,MATCH(LARGE('Fase de Grupos'!$S$131:$S$134,2),'Fase de Grupos'!$S$131:$S$134,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$131:$J$134,MATCH(LARGE('Fase de Grupos'!$S$131:$S$134,3),'Fase de Grupos'!$S$131:$S$134,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="E12" s="25">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$131:$J$134,MATCH(LARGE('Fase de Grupos'!$S$131:$S$134,4),'Fase de Grupos'!$S$131:$S$134,0)),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Group J</t>
+        </is>
+      </c>
+      <c r="B13" s="22">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$147:$J$150,MATCH(LARGE('Fase de Grupos'!$S$147:$S$150,1),'Fase de Grupos'!$S$147:$S$150,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="C13" s="23">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$147:$J$150,MATCH(LARGE('Fase de Grupos'!$S$147:$S$150,2),'Fase de Grupos'!$S$147:$S$150,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="D13" s="24">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$147:$J$150,MATCH(LARGE('Fase de Grupos'!$S$147:$S$150,3),'Fase de Grupos'!$S$147:$S$150,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="E13" s="25">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$147:$J$150,MATCH(LARGE('Fase de Grupos'!$S$147:$S$150,4),'Fase de Grupos'!$S$147:$S$150,0)),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Group K</t>
+        </is>
+      </c>
+      <c r="B14" s="22">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$163:$J$166,MATCH(LARGE('Fase de Grupos'!$S$163:$S$166,1),'Fase de Grupos'!$S$163:$S$166,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="C14" s="23">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$163:$J$166,MATCH(LARGE('Fase de Grupos'!$S$163:$S$166,2),'Fase de Grupos'!$S$163:$S$166,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="D14" s="24">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$163:$J$166,MATCH(LARGE('Fase de Grupos'!$S$163:$S$166,3),'Fase de Grupos'!$S$163:$S$166,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="E14" s="25">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$163:$J$166,MATCH(LARGE('Fase de Grupos'!$S$163:$S$166,4),'Fase de Grupos'!$S$163:$S$166,0)),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>Group L</t>
+        </is>
+      </c>
+      <c r="B15" s="22">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$179:$J$182,MATCH(LARGE('Fase de Grupos'!$S$179:$S$182,1),'Fase de Grupos'!$S$179:$S$182,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="C15" s="23">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$179:$J$182,MATCH(LARGE('Fase de Grupos'!$S$179:$S$182,2),'Fase de Grupos'!$S$179:$S$182,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="D15" s="24">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$179:$J$182,MATCH(LARGE('Fase de Grupos'!$S$179:$S$182,3),'Fase de Grupos'!$S$179:$S$182,0)),"—")</f>
+        <v/>
+      </c>
+      <c r="E15" s="25">
+        <f>IFERROR(INDEX('Fase de Grupos'!$J$179:$J$182,MATCH(LARGE('Fase de Grupos'!$S$179:$S$182,4),'Fase de Grupos'!$S$179:$S$182,0)),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ⚠️  The 8 best 3rd-place finishers also advance to the Round of 32. Those slots are determined after all groups complete and must be entered manually in the Bracket tab.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A17:E17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AJ51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="5" customWidth="1" min="6" max="6"/>
     <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
     <col width="5" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="5" customWidth="1" min="18" max="18"/>
     <col width="5" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
     <col width="5" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
     <col width="5" customWidth="1" min="26" max="26"/>
     <col width="5" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
     <col width="5" customWidth="1" min="30" max="30"/>
     <col width="5" customWidth="1" min="31" max="31"/>
-    <col width="13" customWidth="1" min="32" max="32"/>
-    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
     <col width="5" customWidth="1" min="34" max="34"/>
     <col width="5" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="14" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>🏆  FIFA WORLD CUP 2026  ·  KNOCKOUT BRACKET  🏆</t>
         </is>
@@ -6704,138 +7282,138 @@
     </row>
     <row r="2" ht="8" customHeight="1"/>
     <row r="3" ht="14" customHeight="1">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ✏️ Yellow cells = goals (90 min + ET combined)  ·  Blue-grey rows = Penalty shootout score (optional — only fill if match is still tied after extra time)</t>
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ✏️ Yellow cells = goals (90 min + ET combined)  ·  Blue-grey rows = Penalty shootout score (optional — only if tied after ET)  ·  Blue-grey team cells = best 3rd-place slot — enter manually after group stage</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="21" t="n"/>
-      <c r="B4" s="21" t="n"/>
-      <c r="C4" s="21" t="n"/>
-      <c r="D4" s="21" t="n"/>
-      <c r="E4" s="21" t="n"/>
-      <c r="F4" s="21" t="n"/>
-      <c r="G4" s="21" t="n"/>
-      <c r="H4" s="21" t="n"/>
-      <c r="I4" s="21" t="n"/>
-      <c r="J4" s="21" t="n"/>
-      <c r="K4" s="21" t="n"/>
-      <c r="L4" s="21" t="n"/>
-      <c r="M4" s="21" t="n"/>
-      <c r="N4" s="21" t="n"/>
-      <c r="O4" s="21" t="n"/>
-      <c r="P4" s="21" t="n"/>
-      <c r="Q4" s="21" t="n"/>
-      <c r="R4" s="21" t="n"/>
-      <c r="S4" s="21" t="n"/>
-      <c r="T4" s="21" t="n"/>
-      <c r="U4" s="21" t="n"/>
-      <c r="V4" s="21" t="n"/>
-      <c r="W4" s="21" t="n"/>
-      <c r="X4" s="21" t="n"/>
-      <c r="Y4" s="21" t="n"/>
-      <c r="Z4" s="21" t="n"/>
-      <c r="AA4" s="21" t="n"/>
-      <c r="AB4" s="21" t="n"/>
-      <c r="AC4" s="21" t="n"/>
-      <c r="AD4" s="21" t="n"/>
-      <c r="AE4" s="21" t="n"/>
-      <c r="AF4" s="21" t="n"/>
-      <c r="AG4" s="21" t="n"/>
-      <c r="AH4" s="21" t="n"/>
-      <c r="AI4" s="21" t="n"/>
-      <c r="AJ4" s="21" t="n"/>
+      <c r="A4" s="29" t="n"/>
+      <c r="B4" s="29" t="n"/>
+      <c r="C4" s="29" t="n"/>
+      <c r="D4" s="29" t="n"/>
+      <c r="E4" s="29" t="n"/>
+      <c r="F4" s="29" t="n"/>
+      <c r="G4" s="29" t="n"/>
+      <c r="H4" s="29" t="n"/>
+      <c r="I4" s="29" t="n"/>
+      <c r="J4" s="29" t="n"/>
+      <c r="K4" s="29" t="n"/>
+      <c r="L4" s="29" t="n"/>
+      <c r="M4" s="29" t="n"/>
+      <c r="N4" s="29" t="n"/>
+      <c r="O4" s="29" t="n"/>
+      <c r="P4" s="29" t="n"/>
+      <c r="Q4" s="29" t="n"/>
+      <c r="R4" s="29" t="n"/>
+      <c r="S4" s="29" t="n"/>
+      <c r="T4" s="29" t="n"/>
+      <c r="U4" s="29" t="n"/>
+      <c r="V4" s="29" t="n"/>
+      <c r="W4" s="29" t="n"/>
+      <c r="X4" s="29" t="n"/>
+      <c r="Y4" s="29" t="n"/>
+      <c r="Z4" s="29" t="n"/>
+      <c r="AA4" s="29" t="n"/>
+      <c r="AB4" s="29" t="n"/>
+      <c r="AC4" s="29" t="n"/>
+      <c r="AD4" s="29" t="n"/>
+      <c r="AE4" s="29" t="n"/>
+      <c r="AF4" s="29" t="n"/>
+      <c r="AG4" s="29" t="n"/>
+      <c r="AH4" s="29" t="n"/>
+      <c r="AI4" s="29" t="n"/>
+      <c r="AJ4" s="29" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="21" t="n"/>
-      <c r="B5" s="21" t="n"/>
-      <c r="C5" s="21" t="n"/>
-      <c r="D5" s="21" t="n"/>
-      <c r="E5" s="21" t="n"/>
-      <c r="F5" s="21" t="n"/>
-      <c r="G5" s="21" t="n"/>
-      <c r="H5" s="21" t="n"/>
-      <c r="I5" s="21" t="n"/>
-      <c r="J5" s="21" t="n"/>
-      <c r="K5" s="21" t="n"/>
-      <c r="L5" s="21" t="n"/>
-      <c r="M5" s="21" t="n"/>
-      <c r="N5" s="21" t="n"/>
-      <c r="O5" s="21" t="n"/>
-      <c r="P5" s="21" t="n"/>
-      <c r="Q5" s="21" t="n"/>
-      <c r="R5" s="21" t="n"/>
-      <c r="S5" s="21" t="n"/>
-      <c r="T5" s="21" t="n"/>
-      <c r="U5" s="21" t="n"/>
-      <c r="V5" s="21" t="n"/>
-      <c r="W5" s="21" t="n"/>
-      <c r="X5" s="21" t="n"/>
-      <c r="Y5" s="21" t="n"/>
-      <c r="Z5" s="21" t="n"/>
-      <c r="AA5" s="21" t="n"/>
-      <c r="AB5" s="21" t="n"/>
-      <c r="AC5" s="21" t="n"/>
-      <c r="AD5" s="21" t="n"/>
-      <c r="AE5" s="21" t="n"/>
-      <c r="AF5" s="21" t="n"/>
-      <c r="AG5" s="21" t="n"/>
-      <c r="AH5" s="21" t="n"/>
-      <c r="AI5" s="21" t="n"/>
-      <c r="AJ5" s="21" t="n"/>
+      <c r="A5" s="29" t="n"/>
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="29" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="29" t="n"/>
+      <c r="L5" s="29" t="n"/>
+      <c r="M5" s="29" t="n"/>
+      <c r="N5" s="29" t="n"/>
+      <c r="O5" s="29" t="n"/>
+      <c r="P5" s="29" t="n"/>
+      <c r="Q5" s="29" t="n"/>
+      <c r="R5" s="29" t="n"/>
+      <c r="S5" s="29" t="n"/>
+      <c r="T5" s="29" t="n"/>
+      <c r="U5" s="29" t="n"/>
+      <c r="V5" s="29" t="n"/>
+      <c r="W5" s="29" t="n"/>
+      <c r="X5" s="29" t="n"/>
+      <c r="Y5" s="29" t="n"/>
+      <c r="Z5" s="29" t="n"/>
+      <c r="AA5" s="29" t="n"/>
+      <c r="AB5" s="29" t="n"/>
+      <c r="AC5" s="29" t="n"/>
+      <c r="AD5" s="29" t="n"/>
+      <c r="AE5" s="29" t="n"/>
+      <c r="AF5" s="29" t="n"/>
+      <c r="AG5" s="29" t="n"/>
+      <c r="AH5" s="29" t="n"/>
+      <c r="AI5" s="29" t="n"/>
+      <c r="AJ5" s="29" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>ROUND OF 32
 Jun 28 – Jul 3</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>ROUND OF 16
 Jul 4 – 7</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I6" s="31" t="inlineStr">
         <is>
           <t>QUARTER-FINALS
 Jul 9 – 11</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr">
+      <c r="M6" s="31" t="inlineStr">
         <is>
           <t>SEMI-FINALS
 Jul 14 – 15</t>
         </is>
       </c>
-      <c r="Q6" s="23" t="inlineStr">
+      <c r="Q6" s="31" t="inlineStr">
         <is>
           <t>🏆  FINAL  🏆
 Jul 19 · New York / NJ</t>
         </is>
       </c>
-      <c r="U6" s="23" t="inlineStr">
+      <c r="U6" s="31" t="inlineStr">
         <is>
           <t>SEMI-FINALS
 Jul 14 – 15</t>
         </is>
       </c>
-      <c r="Y6" s="23" t="inlineStr">
+      <c r="Y6" s="31" t="inlineStr">
         <is>
           <t>QUARTER-FINALS
 Jul 9 – 11</t>
         </is>
       </c>
-      <c r="AC6" s="22" t="inlineStr">
+      <c r="AC6" s="30" t="inlineStr">
         <is>
           <t>ROUND OF 16
 Jul 4 – 7</t>
         </is>
       </c>
-      <c r="AG6" s="22" t="inlineStr">
+      <c r="AG6" s="30" t="inlineStr">
         <is>
           <t>ROUND OF 32
 Jun 28 – Jul 3</t>
@@ -6843,2184 +7421,2203 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="21" t="n"/>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="21" t="n"/>
-      <c r="D7" s="21" t="n"/>
-      <c r="E7" s="21" t="n"/>
-      <c r="F7" s="21" t="n"/>
-      <c r="G7" s="21" t="n"/>
-      <c r="H7" s="21" t="n"/>
-      <c r="I7" s="21" t="n"/>
-      <c r="J7" s="21" t="n"/>
-      <c r="K7" s="21" t="n"/>
-      <c r="L7" s="21" t="n"/>
-      <c r="M7" s="21" t="n"/>
-      <c r="N7" s="21" t="n"/>
-      <c r="O7" s="21" t="n"/>
-      <c r="P7" s="21" t="n"/>
-      <c r="Q7" s="21" t="n"/>
-      <c r="R7" s="21" t="n"/>
-      <c r="S7" s="21" t="n"/>
-      <c r="T7" s="21" t="n"/>
-      <c r="U7" s="21" t="n"/>
-      <c r="V7" s="21" t="n"/>
-      <c r="W7" s="21" t="n"/>
-      <c r="X7" s="21" t="n"/>
-      <c r="Y7" s="21" t="n"/>
-      <c r="Z7" s="21" t="n"/>
-      <c r="AA7" s="21" t="n"/>
-      <c r="AB7" s="21" t="n"/>
-      <c r="AC7" s="21" t="n"/>
-      <c r="AD7" s="21" t="n"/>
-      <c r="AE7" s="21" t="n"/>
-      <c r="AF7" s="21" t="n"/>
-      <c r="AG7" s="21" t="n"/>
-      <c r="AH7" s="21" t="n"/>
-      <c r="AI7" s="21" t="n"/>
-      <c r="AJ7" s="21" t="n"/>
+      <c r="A7" s="29" t="n"/>
+      <c r="B7" s="29" t="n"/>
+      <c r="C7" s="29" t="n"/>
+      <c r="D7" s="29" t="n"/>
+      <c r="E7" s="29" t="n"/>
+      <c r="F7" s="29" t="n"/>
+      <c r="G7" s="29" t="n"/>
+      <c r="H7" s="29" t="n"/>
+      <c r="I7" s="29" t="n"/>
+      <c r="J7" s="29" t="n"/>
+      <c r="K7" s="29" t="n"/>
+      <c r="L7" s="29" t="n"/>
+      <c r="M7" s="29" t="n"/>
+      <c r="N7" s="29" t="n"/>
+      <c r="O7" s="29" t="n"/>
+      <c r="P7" s="29" t="n"/>
+      <c r="Q7" s="29" t="n"/>
+      <c r="R7" s="29" t="n"/>
+      <c r="S7" s="29" t="n"/>
+      <c r="T7" s="29" t="n"/>
+      <c r="U7" s="29" t="n"/>
+      <c r="V7" s="29" t="n"/>
+      <c r="W7" s="29" t="n"/>
+      <c r="X7" s="29" t="n"/>
+      <c r="Y7" s="29" t="n"/>
+      <c r="Z7" s="29" t="n"/>
+      <c r="AA7" s="29" t="n"/>
+      <c r="AB7" s="29" t="n"/>
+      <c r="AC7" s="29" t="n"/>
+      <c r="AD7" s="29" t="n"/>
+      <c r="AE7" s="29" t="n"/>
+      <c r="AF7" s="29" t="n"/>
+      <c r="AG7" s="29" t="n"/>
+      <c r="AH7" s="29" t="n"/>
+      <c r="AI7" s="29" t="n"/>
+      <c r="AJ7" s="29" t="n"/>
     </row>
     <row r="8" ht="13" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>Jun 28  ·  Los Angeles</t>
         </is>
       </c>
-      <c r="E8" s="21" t="n"/>
-      <c r="F8" s="21" t="n"/>
-      <c r="G8" s="21" t="n"/>
-      <c r="H8" s="21" t="n"/>
-      <c r="I8" s="21" t="n"/>
-      <c r="J8" s="21" t="n"/>
-      <c r="K8" s="21" t="n"/>
-      <c r="L8" s="21" t="n"/>
-      <c r="M8" s="21" t="n"/>
-      <c r="N8" s="21" t="n"/>
-      <c r="O8" s="21" t="n"/>
-      <c r="P8" s="21" t="n"/>
-      <c r="Q8" s="21" t="n"/>
-      <c r="R8" s="21" t="n"/>
-      <c r="S8" s="21" t="n"/>
-      <c r="T8" s="21" t="n"/>
-      <c r="U8" s="21" t="n"/>
-      <c r="V8" s="21" t="n"/>
-      <c r="W8" s="21" t="n"/>
-      <c r="X8" s="21" t="n"/>
-      <c r="Y8" s="21" t="n"/>
-      <c r="Z8" s="21" t="n"/>
-      <c r="AA8" s="21" t="n"/>
-      <c r="AB8" s="21" t="n"/>
-      <c r="AC8" s="21" t="n"/>
-      <c r="AD8" s="21" t="n"/>
-      <c r="AE8" s="21" t="n"/>
-      <c r="AF8" s="21" t="n"/>
-      <c r="AG8" s="24" t="inlineStr">
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="29" t="n"/>
+      <c r="H8" s="29" t="n"/>
+      <c r="I8" s="29" t="n"/>
+      <c r="J8" s="29" t="n"/>
+      <c r="K8" s="29" t="n"/>
+      <c r="L8" s="29" t="n"/>
+      <c r="M8" s="29" t="n"/>
+      <c r="N8" s="29" t="n"/>
+      <c r="O8" s="29" t="n"/>
+      <c r="P8" s="29" t="n"/>
+      <c r="Q8" s="29" t="n"/>
+      <c r="R8" s="29" t="n"/>
+      <c r="S8" s="29" t="n"/>
+      <c r="T8" s="29" t="n"/>
+      <c r="U8" s="29" t="n"/>
+      <c r="V8" s="29" t="n"/>
+      <c r="W8" s="29" t="n"/>
+      <c r="X8" s="29" t="n"/>
+      <c r="Y8" s="29" t="n"/>
+      <c r="Z8" s="29" t="n"/>
+      <c r="AA8" s="29" t="n"/>
+      <c r="AB8" s="29" t="n"/>
+      <c r="AC8" s="29" t="n"/>
+      <c r="AD8" s="29" t="n"/>
+      <c r="AE8" s="29" t="n"/>
+      <c r="AF8" s="29" t="n"/>
+      <c r="AG8" s="32" t="inlineStr">
         <is>
           <t>Jul 1  ·  Seattle</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
+      <c r="A9" s="33">
+        <f>'Clasificados'!$C$4</f>
+        <v/>
       </c>
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="10" t="n"/>
-      <c r="D9" s="26" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="n"/>
-      <c r="F9" s="21" t="n"/>
-      <c r="G9" s="21" t="n"/>
-      <c r="H9" s="21" t="n"/>
-      <c r="I9" s="21" t="n"/>
-      <c r="J9" s="21" t="n"/>
-      <c r="K9" s="21" t="n"/>
-      <c r="L9" s="21" t="n"/>
-      <c r="M9" s="21" t="n"/>
-      <c r="N9" s="21" t="n"/>
-      <c r="O9" s="21" t="n"/>
-      <c r="P9" s="21" t="n"/>
-      <c r="Q9" s="21" t="n"/>
-      <c r="R9" s="21" t="n"/>
-      <c r="S9" s="21" t="n"/>
-      <c r="T9" s="21" t="n"/>
-      <c r="U9" s="21" t="n"/>
-      <c r="V9" s="21" t="n"/>
-      <c r="W9" s="21" t="n"/>
-      <c r="X9" s="21" t="n"/>
-      <c r="Y9" s="21" t="n"/>
-      <c r="Z9" s="21" t="n"/>
-      <c r="AA9" s="21" t="n"/>
-      <c r="AB9" s="21" t="n"/>
-      <c r="AC9" s="21" t="n"/>
-      <c r="AD9" s="21" t="n"/>
-      <c r="AE9" s="21" t="n"/>
-      <c r="AF9" s="21" t="n"/>
-      <c r="AG9" s="25" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
+      <c r="D9" s="34">
+        <f>'Clasificados'!$C$5</f>
+        <v/>
+      </c>
+      <c r="E9" s="29" t="n"/>
+      <c r="F9" s="29" t="n"/>
+      <c r="G9" s="29" t="n"/>
+      <c r="H9" s="29" t="n"/>
+      <c r="I9" s="29" t="n"/>
+      <c r="J9" s="29" t="n"/>
+      <c r="K9" s="29" t="n"/>
+      <c r="L9" s="29" t="n"/>
+      <c r="M9" s="29" t="n"/>
+      <c r="N9" s="29" t="n"/>
+      <c r="O9" s="29" t="n"/>
+      <c r="P9" s="29" t="n"/>
+      <c r="Q9" s="29" t="n"/>
+      <c r="R9" s="29" t="n"/>
+      <c r="S9" s="29" t="n"/>
+      <c r="T9" s="29" t="n"/>
+      <c r="U9" s="29" t="n"/>
+      <c r="V9" s="29" t="n"/>
+      <c r="W9" s="29" t="n"/>
+      <c r="X9" s="29" t="n"/>
+      <c r="Y9" s="29" t="n"/>
+      <c r="Z9" s="29" t="n"/>
+      <c r="AA9" s="29" t="n"/>
+      <c r="AB9" s="29" t="n"/>
+      <c r="AC9" s="29" t="n"/>
+      <c r="AD9" s="29" t="n"/>
+      <c r="AE9" s="29" t="n"/>
+      <c r="AF9" s="29" t="n"/>
+      <c r="AG9" s="33">
+        <f>'Clasificados'!$B$10</f>
+        <v/>
       </c>
       <c r="AH9" s="10" t="n"/>
       <c r="AI9" s="10" t="n"/>
-      <c r="AJ9" s="26" t="inlineStr">
-        <is>
-          <t>3rd*</t>
+      <c r="AJ9" s="35" t="inlineStr">
+        <is>
+          <t>◀ Enter 3rd</t>
         </is>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="B10" s="28" t="n"/>
-      <c r="C10" s="28" t="n"/>
-      <c r="D10" s="29" t="inlineStr">
+      <c r="B10" s="37" t="n"/>
+      <c r="C10" s="37" t="n"/>
+      <c r="D10" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="21" t="n"/>
-      <c r="G10" s="21" t="n"/>
-      <c r="H10" s="21" t="n"/>
-      <c r="I10" s="21" t="n"/>
-      <c r="J10" s="21" t="n"/>
-      <c r="K10" s="21" t="n"/>
-      <c r="L10" s="21" t="n"/>
-      <c r="M10" s="21" t="n"/>
-      <c r="N10" s="21" t="n"/>
-      <c r="O10" s="21" t="n"/>
-      <c r="P10" s="21" t="n"/>
-      <c r="Q10" s="21" t="n"/>
-      <c r="R10" s="21" t="n"/>
-      <c r="S10" s="21" t="n"/>
-      <c r="T10" s="21" t="n"/>
-      <c r="U10" s="21" t="n"/>
-      <c r="V10" s="21" t="n"/>
-      <c r="W10" s="21" t="n"/>
-      <c r="X10" s="21" t="n"/>
-      <c r="Y10" s="21" t="n"/>
-      <c r="Z10" s="21" t="n"/>
-      <c r="AA10" s="21" t="n"/>
-      <c r="AB10" s="21" t="n"/>
-      <c r="AC10" s="21" t="n"/>
-      <c r="AD10" s="21" t="n"/>
-      <c r="AE10" s="21" t="n"/>
-      <c r="AF10" s="21" t="n"/>
-      <c r="AG10" s="27" t="inlineStr">
+      <c r="E10" s="29" t="n"/>
+      <c r="F10" s="29" t="n"/>
+      <c r="G10" s="29" t="n"/>
+      <c r="H10" s="29" t="n"/>
+      <c r="I10" s="29" t="n"/>
+      <c r="J10" s="29" t="n"/>
+      <c r="K10" s="29" t="n"/>
+      <c r="L10" s="29" t="n"/>
+      <c r="M10" s="29" t="n"/>
+      <c r="N10" s="29" t="n"/>
+      <c r="O10" s="29" t="n"/>
+      <c r="P10" s="29" t="n"/>
+      <c r="Q10" s="29" t="n"/>
+      <c r="R10" s="29" t="n"/>
+      <c r="S10" s="29" t="n"/>
+      <c r="T10" s="29" t="n"/>
+      <c r="U10" s="29" t="n"/>
+      <c r="V10" s="29" t="n"/>
+      <c r="W10" s="29" t="n"/>
+      <c r="X10" s="29" t="n"/>
+      <c r="Y10" s="29" t="n"/>
+      <c r="Z10" s="29" t="n"/>
+      <c r="AA10" s="29" t="n"/>
+      <c r="AB10" s="29" t="n"/>
+      <c r="AC10" s="29" t="n"/>
+      <c r="AD10" s="29" t="n"/>
+      <c r="AE10" s="29" t="n"/>
+      <c r="AF10" s="29" t="n"/>
+      <c r="AG10" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="AH10" s="28" t="n"/>
-      <c r="AI10" s="28" t="n"/>
-      <c r="AJ10" s="29" t="inlineStr">
+      <c r="AH10" s="37" t="n"/>
+      <c r="AI10" s="37" t="n"/>
+      <c r="AJ10" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="21" t="n"/>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="A11" s="29" t="n"/>
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="29" t="n"/>
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t>Jul 4  ·  Houston</t>
         </is>
       </c>
-      <c r="I11" s="21" t="n"/>
-      <c r="J11" s="21" t="n"/>
-      <c r="K11" s="21" t="n"/>
-      <c r="L11" s="21" t="n"/>
-      <c r="M11" s="21" t="n"/>
-      <c r="N11" s="21" t="n"/>
-      <c r="O11" s="21" t="n"/>
-      <c r="P11" s="21" t="n"/>
-      <c r="Q11" s="21" t="n"/>
-      <c r="R11" s="21" t="n"/>
-      <c r="S11" s="21" t="n"/>
-      <c r="T11" s="21" t="n"/>
-      <c r="U11" s="21" t="n"/>
-      <c r="V11" s="21" t="n"/>
-      <c r="W11" s="21" t="n"/>
-      <c r="X11" s="21" t="n"/>
-      <c r="Y11" s="21" t="n"/>
-      <c r="Z11" s="21" t="n"/>
-      <c r="AA11" s="21" t="n"/>
-      <c r="AB11" s="21" t="n"/>
-      <c r="AC11" s="24" t="inlineStr">
+      <c r="I11" s="29" t="n"/>
+      <c r="J11" s="29" t="n"/>
+      <c r="K11" s="29" t="n"/>
+      <c r="L11" s="29" t="n"/>
+      <c r="M11" s="29" t="n"/>
+      <c r="N11" s="29" t="n"/>
+      <c r="O11" s="29" t="n"/>
+      <c r="P11" s="29" t="n"/>
+      <c r="Q11" s="29" t="n"/>
+      <c r="R11" s="29" t="n"/>
+      <c r="S11" s="29" t="n"/>
+      <c r="T11" s="29" t="n"/>
+      <c r="U11" s="29" t="n"/>
+      <c r="V11" s="29" t="n"/>
+      <c r="W11" s="29" t="n"/>
+      <c r="X11" s="29" t="n"/>
+      <c r="Y11" s="29" t="n"/>
+      <c r="Z11" s="29" t="n"/>
+      <c r="AA11" s="29" t="n"/>
+      <c r="AB11" s="29" t="n"/>
+      <c r="AC11" s="32" t="inlineStr">
         <is>
           <t>Jul 6  ·  Dallas</t>
         </is>
       </c>
-      <c r="AG11" s="21" t="n"/>
-      <c r="AH11" s="21" t="n"/>
-      <c r="AI11" s="21" t="n"/>
-      <c r="AJ11" s="21" t="n"/>
+      <c r="AG11" s="29" t="n"/>
+      <c r="AH11" s="29" t="n"/>
+      <c r="AI11" s="29" t="n"/>
+      <c r="AJ11" s="29" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>Jun 29  ·  Houston</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>W R32 #1</t>
-        </is>
+      <c r="E12" s="33">
+        <f>IF(AND($B$9&lt;&gt;"",$C$9&lt;&gt;""),IF($B$9&gt;$C$9,$A$9,IF($C$9&gt;$B$9,$D$9,IF(AND($B$10&lt;&gt;"",$C$10&lt;&gt;""),IF($B$10&gt;$C$10,$A$9,$D$9),"TBD"))),"—")</f>
+        <v/>
       </c>
       <c r="F12" s="10" t="n"/>
       <c r="G12" s="10" t="n"/>
-      <c r="H12" s="26" t="inlineStr">
-        <is>
-          <t>W R32 #2</t>
-        </is>
-      </c>
-      <c r="I12" s="21" t="n"/>
-      <c r="J12" s="21" t="n"/>
-      <c r="K12" s="21" t="n"/>
-      <c r="L12" s="21" t="n"/>
-      <c r="M12" s="21" t="n"/>
-      <c r="N12" s="21" t="n"/>
-      <c r="O12" s="21" t="n"/>
-      <c r="P12" s="21" t="n"/>
-      <c r="Q12" s="21" t="n"/>
-      <c r="R12" s="21" t="n"/>
-      <c r="S12" s="21" t="n"/>
-      <c r="T12" s="21" t="n"/>
-      <c r="U12" s="21" t="n"/>
-      <c r="V12" s="21" t="n"/>
-      <c r="W12" s="21" t="n"/>
-      <c r="X12" s="21" t="n"/>
-      <c r="Y12" s="21" t="n"/>
-      <c r="Z12" s="21" t="n"/>
-      <c r="AA12" s="21" t="n"/>
-      <c r="AB12" s="21" t="n"/>
-      <c r="AC12" s="25" t="inlineStr">
-        <is>
-          <t>W R32 #9</t>
-        </is>
+      <c r="H12" s="34">
+        <f>IF(AND($B$13&lt;&gt;"",$C$13&lt;&gt;""),IF($B$13&gt;$C$13,$A$13,IF($C$13&gt;$B$13,$D$13,IF(AND($B$14&lt;&gt;"",$C$14&lt;&gt;""),IF($B$14&gt;$C$14,$A$13,$D$13),"TBD"))),"—")</f>
+        <v/>
+      </c>
+      <c r="I12" s="29" t="n"/>
+      <c r="J12" s="29" t="n"/>
+      <c r="K12" s="29" t="n"/>
+      <c r="L12" s="29" t="n"/>
+      <c r="M12" s="29" t="n"/>
+      <c r="N12" s="29" t="n"/>
+      <c r="O12" s="29" t="n"/>
+      <c r="P12" s="29" t="n"/>
+      <c r="Q12" s="29" t="n"/>
+      <c r="R12" s="29" t="n"/>
+      <c r="S12" s="29" t="n"/>
+      <c r="T12" s="29" t="n"/>
+      <c r="U12" s="29" t="n"/>
+      <c r="V12" s="29" t="n"/>
+      <c r="W12" s="29" t="n"/>
+      <c r="X12" s="29" t="n"/>
+      <c r="Y12" s="29" t="n"/>
+      <c r="Z12" s="29" t="n"/>
+      <c r="AA12" s="29" t="n"/>
+      <c r="AB12" s="29" t="n"/>
+      <c r="AC12" s="33">
+        <f>IF(AND($AH$9&lt;&gt;"",$AI$9&lt;&gt;""),IF($AH$9&gt;$AI$9,$AG$9,IF($AI$9&gt;$AH$9,$AJ$9,IF(AND($AH$10&lt;&gt;"",$AI$10&lt;&gt;""),IF($AH$10&gt;$AI$10,$AG$9,$AJ$9),"TBD"))),"—")</f>
+        <v/>
       </c>
       <c r="AD12" s="10" t="n"/>
       <c r="AE12" s="10" t="n"/>
-      <c r="AF12" s="26" t="inlineStr">
-        <is>
-          <t>W R32 #10</t>
-        </is>
-      </c>
-      <c r="AG12" s="24" t="inlineStr">
+      <c r="AF12" s="34">
+        <f>IF(AND($AH$13&lt;&gt;"",$AI$13&lt;&gt;""),IF($AH$13&gt;$AI$13,$AG$13,IF($AI$13&gt;$AH$13,$AJ$13,IF(AND($AH$14&lt;&gt;"",$AI$14&lt;&gt;""),IF($AH$14&gt;$AI$14,$AG$13,$AJ$13),"TBD"))),"—")</f>
+        <v/>
+      </c>
+      <c r="AG12" s="32" t="inlineStr">
         <is>
           <t>Jul 1  ·  San Francisco</t>
         </is>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
+      <c r="A13" s="33">
+        <f>'Clasificados'!$B$6</f>
+        <v/>
       </c>
       <c r="B13" s="10" t="n"/>
       <c r="C13" s="10" t="n"/>
-      <c r="D13" s="26" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="E13" s="27" t="inlineStr">
+      <c r="D13" s="34">
+        <f>'Clasificados'!$C$9</f>
+        <v/>
+      </c>
+      <c r="E13" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="F13" s="28" t="n"/>
-      <c r="G13" s="28" t="n"/>
-      <c r="H13" s="29" t="inlineStr">
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
+      <c r="H13" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="I13" s="21" t="n"/>
-      <c r="J13" s="21" t="n"/>
-      <c r="K13" s="21" t="n"/>
-      <c r="L13" s="21" t="n"/>
-      <c r="M13" s="21" t="n"/>
-      <c r="N13" s="21" t="n"/>
-      <c r="O13" s="21" t="n"/>
-      <c r="P13" s="21" t="n"/>
-      <c r="Q13" s="21" t="n"/>
-      <c r="R13" s="21" t="n"/>
-      <c r="S13" s="21" t="n"/>
-      <c r="T13" s="21" t="n"/>
-      <c r="U13" s="21" t="n"/>
-      <c r="V13" s="21" t="n"/>
-      <c r="W13" s="21" t="n"/>
-      <c r="X13" s="21" t="n"/>
-      <c r="Y13" s="21" t="n"/>
-      <c r="Z13" s="21" t="n"/>
-      <c r="AA13" s="21" t="n"/>
-      <c r="AB13" s="21" t="n"/>
-      <c r="AC13" s="27" t="inlineStr">
+      <c r="I13" s="29" t="n"/>
+      <c r="J13" s="29" t="n"/>
+      <c r="K13" s="29" t="n"/>
+      <c r="L13" s="29" t="n"/>
+      <c r="M13" s="29" t="n"/>
+      <c r="N13" s="29" t="n"/>
+      <c r="O13" s="29" t="n"/>
+      <c r="P13" s="29" t="n"/>
+      <c r="Q13" s="29" t="n"/>
+      <c r="R13" s="29" t="n"/>
+      <c r="S13" s="29" t="n"/>
+      <c r="T13" s="29" t="n"/>
+      <c r="U13" s="29" t="n"/>
+      <c r="V13" s="29" t="n"/>
+      <c r="W13" s="29" t="n"/>
+      <c r="X13" s="29" t="n"/>
+      <c r="Y13" s="29" t="n"/>
+      <c r="Z13" s="29" t="n"/>
+      <c r="AA13" s="29" t="n"/>
+      <c r="AB13" s="29" t="n"/>
+      <c r="AC13" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="AD13" s="28" t="n"/>
-      <c r="AE13" s="28" t="n"/>
-      <c r="AF13" s="29" t="inlineStr">
+      <c r="AD13" s="37" t="n"/>
+      <c r="AE13" s="37" t="n"/>
+      <c r="AF13" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="AG13" s="25" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
+      <c r="AG13" s="33">
+        <f>'Clasificados'!$B$7</f>
+        <v/>
       </c>
       <c r="AH13" s="10" t="n"/>
       <c r="AI13" s="10" t="n"/>
-      <c r="AJ13" s="26" t="inlineStr">
-        <is>
-          <t>3rd*</t>
+      <c r="AJ13" s="35" t="inlineStr">
+        <is>
+          <t>◀ Enter 3rd</t>
         </is>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="B14" s="28" t="n"/>
-      <c r="C14" s="28" t="n"/>
-      <c r="D14" s="29" t="inlineStr">
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="37" t="n"/>
+      <c r="D14" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="E14" s="21" t="n"/>
-      <c r="F14" s="21" t="n"/>
-      <c r="G14" s="21" t="n"/>
-      <c r="H14" s="21" t="n"/>
-      <c r="I14" s="21" t="n"/>
-      <c r="J14" s="21" t="n"/>
-      <c r="K14" s="21" t="n"/>
-      <c r="L14" s="21" t="n"/>
-      <c r="M14" s="21" t="n"/>
-      <c r="N14" s="21" t="n"/>
-      <c r="O14" s="21" t="n"/>
-      <c r="P14" s="21" t="n"/>
-      <c r="Q14" s="21" t="n"/>
-      <c r="R14" s="21" t="n"/>
-      <c r="S14" s="21" t="n"/>
-      <c r="T14" s="21" t="n"/>
-      <c r="U14" s="21" t="n"/>
-      <c r="V14" s="21" t="n"/>
-      <c r="W14" s="21" t="n"/>
-      <c r="X14" s="21" t="n"/>
-      <c r="Y14" s="21" t="n"/>
-      <c r="Z14" s="21" t="n"/>
-      <c r="AA14" s="21" t="n"/>
-      <c r="AB14" s="21" t="n"/>
-      <c r="AC14" s="21" t="n"/>
-      <c r="AD14" s="21" t="n"/>
-      <c r="AE14" s="21" t="n"/>
-      <c r="AF14" s="21" t="n"/>
-      <c r="AG14" s="27" t="inlineStr">
+      <c r="E14" s="29" t="n"/>
+      <c r="F14" s="29" t="n"/>
+      <c r="G14" s="29" t="n"/>
+      <c r="H14" s="29" t="n"/>
+      <c r="I14" s="29" t="n"/>
+      <c r="J14" s="29" t="n"/>
+      <c r="K14" s="29" t="n"/>
+      <c r="L14" s="29" t="n"/>
+      <c r="M14" s="29" t="n"/>
+      <c r="N14" s="29" t="n"/>
+      <c r="O14" s="29" t="n"/>
+      <c r="P14" s="29" t="n"/>
+      <c r="Q14" s="29" t="n"/>
+      <c r="R14" s="29" t="n"/>
+      <c r="S14" s="29" t="n"/>
+      <c r="T14" s="29" t="n"/>
+      <c r="U14" s="29" t="n"/>
+      <c r="V14" s="29" t="n"/>
+      <c r="W14" s="29" t="n"/>
+      <c r="X14" s="29" t="n"/>
+      <c r="Y14" s="29" t="n"/>
+      <c r="Z14" s="29" t="n"/>
+      <c r="AA14" s="29" t="n"/>
+      <c r="AB14" s="29" t="n"/>
+      <c r="AC14" s="29" t="n"/>
+      <c r="AD14" s="29" t="n"/>
+      <c r="AE14" s="29" t="n"/>
+      <c r="AF14" s="29" t="n"/>
+      <c r="AG14" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="AH14" s="28" t="n"/>
-      <c r="AI14" s="28" t="n"/>
-      <c r="AJ14" s="29" t="inlineStr">
+      <c r="AH14" s="37" t="n"/>
+      <c r="AI14" s="37" t="n"/>
+      <c r="AJ14" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="21" t="n"/>
-      <c r="B15" s="21" t="n"/>
-      <c r="C15" s="21" t="n"/>
-      <c r="D15" s="21" t="n"/>
-      <c r="E15" s="21" t="n"/>
-      <c r="F15" s="21" t="n"/>
-      <c r="G15" s="21" t="n"/>
-      <c r="H15" s="21" t="n"/>
-      <c r="I15" s="24" t="inlineStr">
+      <c r="A15" s="29" t="n"/>
+      <c r="B15" s="29" t="n"/>
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="29" t="n"/>
+      <c r="E15" s="29" t="n"/>
+      <c r="F15" s="29" t="n"/>
+      <c r="G15" s="29" t="n"/>
+      <c r="H15" s="29" t="n"/>
+      <c r="I15" s="32" t="inlineStr">
         <is>
           <t>Jul 9  ·  Boston</t>
         </is>
       </c>
-      <c r="M15" s="21" t="n"/>
-      <c r="N15" s="21" t="n"/>
-      <c r="O15" s="21" t="n"/>
-      <c r="P15" s="21" t="n"/>
-      <c r="Q15" s="21" t="n"/>
-      <c r="R15" s="21" t="n"/>
-      <c r="S15" s="21" t="n"/>
-      <c r="T15" s="21" t="n"/>
-      <c r="U15" s="21" t="n"/>
-      <c r="V15" s="21" t="n"/>
-      <c r="W15" s="21" t="n"/>
-      <c r="X15" s="21" t="n"/>
-      <c r="Y15" s="24" t="inlineStr">
+      <c r="M15" s="29" t="n"/>
+      <c r="N15" s="29" t="n"/>
+      <c r="O15" s="29" t="n"/>
+      <c r="P15" s="29" t="n"/>
+      <c r="Q15" s="29" t="n"/>
+      <c r="R15" s="29" t="n"/>
+      <c r="S15" s="29" t="n"/>
+      <c r="T15" s="29" t="n"/>
+      <c r="U15" s="29" t="n"/>
+      <c r="V15" s="29" t="n"/>
+      <c r="W15" s="29" t="n"/>
+      <c r="X15" s="29" t="n"/>
+      <c r="Y15" s="32" t="inlineStr">
         <is>
           <t>Jul 11  ·  Miami</t>
         </is>
       </c>
-      <c r="AC15" s="21" t="n"/>
-      <c r="AD15" s="21" t="n"/>
-      <c r="AE15" s="21" t="n"/>
-      <c r="AF15" s="21" t="n"/>
-      <c r="AG15" s="21" t="n"/>
-      <c r="AH15" s="21" t="n"/>
-      <c r="AI15" s="21" t="n"/>
-      <c r="AJ15" s="21" t="n"/>
+      <c r="AC15" s="29" t="n"/>
+      <c r="AD15" s="29" t="n"/>
+      <c r="AE15" s="29" t="n"/>
+      <c r="AF15" s="29" t="n"/>
+      <c r="AG15" s="29" t="n"/>
+      <c r="AH15" s="29" t="n"/>
+      <c r="AI15" s="29" t="n"/>
+      <c r="AJ15" s="29" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>Jun 29  ·  Boston</t>
         </is>
       </c>
-      <c r="E16" s="21" t="n"/>
-      <c r="F16" s="21" t="n"/>
-      <c r="G16" s="21" t="n"/>
-      <c r="H16" s="21" t="n"/>
-      <c r="I16" s="25" t="inlineStr">
-        <is>
-          <t>W R16-L1</t>
-        </is>
+      <c r="E16" s="29" t="n"/>
+      <c r="F16" s="29" t="n"/>
+      <c r="G16" s="29" t="n"/>
+      <c r="H16" s="29" t="n"/>
+      <c r="I16" s="33">
+        <f>IF(AND($F$12&lt;&gt;"",$G$12&lt;&gt;""),IF($F$12&gt;$G$12,$E$12,IF($G$12&gt;$F$12,$H$12,IF(AND($F$13&lt;&gt;"",$G$13&lt;&gt;""),IF($F$13&gt;$G$13,$E$12,$H$12),"TBD"))),"—")</f>
+        <v/>
       </c>
       <c r="J16" s="10" t="n"/>
       <c r="K16" s="10" t="n"/>
-      <c r="L16" s="26" t="inlineStr">
-        <is>
-          <t>W R16-L2</t>
-        </is>
-      </c>
-      <c r="M16" s="21" t="n"/>
-      <c r="N16" s="21" t="n"/>
-      <c r="O16" s="21" t="n"/>
-      <c r="P16" s="21" t="n"/>
-      <c r="Q16" s="21" t="n"/>
-      <c r="R16" s="21" t="n"/>
-      <c r="S16" s="21" t="n"/>
-      <c r="T16" s="21" t="n"/>
-      <c r="U16" s="21" t="n"/>
-      <c r="V16" s="21" t="n"/>
-      <c r="W16" s="21" t="n"/>
-      <c r="X16" s="21" t="n"/>
-      <c r="Y16" s="25" t="inlineStr">
-        <is>
-          <t>W R16-R1</t>
-        </is>
+      <c r="L16" s="34">
+        <f>IF(AND($F$20&lt;&gt;"",$G$20&lt;&gt;""),IF($F$20&gt;$G$20,$E$20,IF($G$20&gt;$F$20,$H$20,IF(AND($F$21&lt;&gt;"",$G$21&lt;&gt;""),IF($F$21&gt;$G$21,$E$20,$H$20),"TBD"))),"—")</f>
+        <v/>
+      </c>
+      <c r="M16" s="29" t="n"/>
+      <c r="N16" s="29" t="n"/>
+      <c r="O16" s="29" t="n"/>
+      <c r="P16" s="29" t="n"/>
+      <c r="Q16" s="29" t="n"/>
+      <c r="R16" s="29" t="n"/>
+      <c r="S16" s="29" t="n"/>
+      <c r="T16" s="29" t="n"/>
+      <c r="U16" s="29" t="n"/>
+      <c r="V16" s="29" t="n"/>
+      <c r="W16" s="29" t="n"/>
+      <c r="X16" s="29" t="n"/>
+      <c r="Y16" s="33">
+        <f>IF(AND($AD$12&lt;&gt;"",$AE$12&lt;&gt;""),IF($AD$12&gt;$AE$12,$AC$12,IF($AE$12&gt;$AD$12,$AF$12,IF(AND($AD$13&lt;&gt;"",$AE$13&lt;&gt;""),IF($AD$13&gt;$AE$13,$AC$12,$AF$12),"TBD"))),"—")</f>
+        <v/>
       </c>
       <c r="Z16" s="10" t="n"/>
       <c r="AA16" s="10" t="n"/>
-      <c r="AB16" s="26" t="inlineStr">
-        <is>
-          <t>W R16-R2</t>
-        </is>
-      </c>
-      <c r="AC16" s="21" t="n"/>
-      <c r="AD16" s="21" t="n"/>
-      <c r="AE16" s="21" t="n"/>
-      <c r="AF16" s="21" t="n"/>
-      <c r="AG16" s="24" t="inlineStr">
+      <c r="AB16" s="34">
+        <f>IF(AND($AD$20&lt;&gt;"",$AE$20&lt;&gt;""),IF($AD$20&gt;$AE$20,$AC$20,IF($AE$20&gt;$AD$20,$AF$20,IF(AND($AD$21&lt;&gt;"",$AE$21&lt;&gt;""),IF($AD$21&gt;$AE$21,$AC$20,$AF$20),"TBD"))),"—")</f>
+        <v/>
+      </c>
+      <c r="AC16" s="29" t="n"/>
+      <c r="AD16" s="29" t="n"/>
+      <c r="AE16" s="29" t="n"/>
+      <c r="AF16" s="29" t="n"/>
+      <c r="AG16" s="32" t="inlineStr">
         <is>
           <t>Jul 2  ·  Los Angeles</t>
         </is>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
+      <c r="A17" s="33">
+        <f>'Clasificados'!$B$8</f>
+        <v/>
       </c>
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="10" t="n"/>
-      <c r="D17" s="26" t="inlineStr">
-        <is>
-          <t>3rd*</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="21" t="n"/>
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="27" t="inlineStr">
+      <c r="D17" s="35" t="inlineStr">
+        <is>
+          <t>◀ Enter 3rd</t>
+        </is>
+      </c>
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="29" t="n"/>
+      <c r="G17" s="29" t="n"/>
+      <c r="H17" s="29" t="n"/>
+      <c r="I17" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="J17" s="28" t="n"/>
-      <c r="K17" s="28" t="n"/>
-      <c r="L17" s="29" t="inlineStr">
+      <c r="J17" s="37" t="n"/>
+      <c r="K17" s="37" t="n"/>
+      <c r="L17" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="M17" s="21" t="n"/>
-      <c r="N17" s="21" t="n"/>
-      <c r="O17" s="21" t="n"/>
-      <c r="P17" s="21" t="n"/>
-      <c r="Q17" s="21" t="n"/>
-      <c r="R17" s="21" t="n"/>
-      <c r="S17" s="21" t="n"/>
-      <c r="T17" s="21" t="n"/>
-      <c r="U17" s="21" t="n"/>
-      <c r="V17" s="21" t="n"/>
-      <c r="W17" s="21" t="n"/>
-      <c r="X17" s="21" t="n"/>
-      <c r="Y17" s="27" t="inlineStr">
+      <c r="M17" s="29" t="n"/>
+      <c r="N17" s="29" t="n"/>
+      <c r="O17" s="29" t="n"/>
+      <c r="P17" s="29" t="n"/>
+      <c r="Q17" s="29" t="n"/>
+      <c r="R17" s="29" t="n"/>
+      <c r="S17" s="29" t="n"/>
+      <c r="T17" s="29" t="n"/>
+      <c r="U17" s="29" t="n"/>
+      <c r="V17" s="29" t="n"/>
+      <c r="W17" s="29" t="n"/>
+      <c r="X17" s="29" t="n"/>
+      <c r="Y17" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="Z17" s="28" t="n"/>
-      <c r="AA17" s="28" t="n"/>
-      <c r="AB17" s="29" t="inlineStr">
+      <c r="Z17" s="37" t="n"/>
+      <c r="AA17" s="37" t="n"/>
+      <c r="AB17" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="AC17" s="21" t="n"/>
-      <c r="AD17" s="21" t="n"/>
-      <c r="AE17" s="21" t="n"/>
-      <c r="AF17" s="21" t="n"/>
-      <c r="AG17" s="25" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
+      <c r="AC17" s="29" t="n"/>
+      <c r="AD17" s="29" t="n"/>
+      <c r="AE17" s="29" t="n"/>
+      <c r="AF17" s="29" t="n"/>
+      <c r="AG17" s="33">
+        <f>'Clasificados'!$B$11</f>
+        <v/>
       </c>
       <c r="AH17" s="10" t="n"/>
       <c r="AI17" s="10" t="n"/>
-      <c r="AJ17" s="26" t="inlineStr">
-        <is>
-          <t>J2</t>
-        </is>
+      <c r="AJ17" s="34">
+        <f>'Clasificados'!$C$13</f>
+        <v/>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="B18" s="28" t="n"/>
-      <c r="C18" s="28" t="n"/>
-      <c r="D18" s="29" t="inlineStr">
+      <c r="B18" s="37" t="n"/>
+      <c r="C18" s="37" t="n"/>
+      <c r="D18" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="E18" s="21" t="n"/>
-      <c r="F18" s="21" t="n"/>
-      <c r="G18" s="21" t="n"/>
-      <c r="H18" s="21" t="n"/>
-      <c r="I18" s="21" t="n"/>
-      <c r="J18" s="21" t="n"/>
-      <c r="K18" s="21" t="n"/>
-      <c r="L18" s="21" t="n"/>
-      <c r="M18" s="21" t="n"/>
-      <c r="N18" s="21" t="n"/>
-      <c r="O18" s="21" t="n"/>
-      <c r="P18" s="21" t="n"/>
-      <c r="Q18" s="21" t="n"/>
-      <c r="R18" s="21" t="n"/>
-      <c r="S18" s="21" t="n"/>
-      <c r="T18" s="21" t="n"/>
-      <c r="U18" s="21" t="n"/>
-      <c r="V18" s="21" t="n"/>
-      <c r="W18" s="21" t="n"/>
-      <c r="X18" s="21" t="n"/>
-      <c r="Y18" s="21" t="n"/>
-      <c r="Z18" s="21" t="n"/>
-      <c r="AA18" s="21" t="n"/>
-      <c r="AB18" s="21" t="n"/>
-      <c r="AC18" s="21" t="n"/>
-      <c r="AD18" s="21" t="n"/>
-      <c r="AE18" s="21" t="n"/>
-      <c r="AF18" s="21" t="n"/>
-      <c r="AG18" s="27" t="inlineStr">
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="29" t="n"/>
+      <c r="G18" s="29" t="n"/>
+      <c r="H18" s="29" t="n"/>
+      <c r="I18" s="29" t="n"/>
+      <c r="J18" s="29" t="n"/>
+      <c r="K18" s="29" t="n"/>
+      <c r="L18" s="29" t="n"/>
+      <c r="M18" s="29" t="n"/>
+      <c r="N18" s="29" t="n"/>
+      <c r="O18" s="29" t="n"/>
+      <c r="P18" s="29" t="n"/>
+      <c r="Q18" s="29" t="n"/>
+      <c r="R18" s="29" t="n"/>
+      <c r="S18" s="29" t="n"/>
+      <c r="T18" s="29" t="n"/>
+      <c r="U18" s="29" t="n"/>
+      <c r="V18" s="29" t="n"/>
+      <c r="W18" s="29" t="n"/>
+      <c r="X18" s="29" t="n"/>
+      <c r="Y18" s="29" t="n"/>
+      <c r="Z18" s="29" t="n"/>
+      <c r="AA18" s="29" t="n"/>
+      <c r="AB18" s="29" t="n"/>
+      <c r="AC18" s="29" t="n"/>
+      <c r="AD18" s="29" t="n"/>
+      <c r="AE18" s="29" t="n"/>
+      <c r="AF18" s="29" t="n"/>
+      <c r="AG18" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="AH18" s="28" t="n"/>
-      <c r="AI18" s="28" t="n"/>
-      <c r="AJ18" s="29" t="inlineStr">
+      <c r="AH18" s="37" t="n"/>
+      <c r="AI18" s="37" t="n"/>
+      <c r="AJ18" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
     </row>
     <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="21" t="n"/>
-      <c r="B19" s="21" t="n"/>
-      <c r="C19" s="21" t="n"/>
-      <c r="D19" s="21" t="n"/>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="A19" s="29" t="n"/>
+      <c r="B19" s="29" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="32" t="inlineStr">
         <is>
           <t>Jul 4  ·  Philadelphia</t>
         </is>
       </c>
-      <c r="I19" s="21" t="n"/>
-      <c r="J19" s="21" t="n"/>
-      <c r="K19" s="21" t="n"/>
-      <c r="L19" s="21" t="n"/>
-      <c r="M19" s="21" t="n"/>
-      <c r="N19" s="21" t="n"/>
-      <c r="O19" s="21" t="n"/>
-      <c r="P19" s="21" t="n"/>
-      <c r="Q19" s="21" t="n"/>
-      <c r="R19" s="21" t="n"/>
-      <c r="S19" s="21" t="n"/>
-      <c r="T19" s="21" t="n"/>
-      <c r="U19" s="21" t="n"/>
-      <c r="V19" s="21" t="n"/>
-      <c r="W19" s="21" t="n"/>
-      <c r="X19" s="21" t="n"/>
-      <c r="Y19" s="21" t="n"/>
-      <c r="Z19" s="21" t="n"/>
-      <c r="AA19" s="21" t="n"/>
-      <c r="AB19" s="21" t="n"/>
-      <c r="AC19" s="24" t="inlineStr">
+      <c r="I19" s="29" t="n"/>
+      <c r="J19" s="29" t="n"/>
+      <c r="K19" s="29" t="n"/>
+      <c r="L19" s="29" t="n"/>
+      <c r="M19" s="29" t="n"/>
+      <c r="N19" s="29" t="n"/>
+      <c r="O19" s="29" t="n"/>
+      <c r="P19" s="29" t="n"/>
+      <c r="Q19" s="29" t="n"/>
+      <c r="R19" s="29" t="n"/>
+      <c r="S19" s="29" t="n"/>
+      <c r="T19" s="29" t="n"/>
+      <c r="U19" s="29" t="n"/>
+      <c r="V19" s="29" t="n"/>
+      <c r="W19" s="29" t="n"/>
+      <c r="X19" s="29" t="n"/>
+      <c r="Y19" s="29" t="n"/>
+      <c r="Z19" s="29" t="n"/>
+      <c r="AA19" s="29" t="n"/>
+      <c r="AB19" s="29" t="n"/>
+      <c r="AC19" s="32" t="inlineStr">
         <is>
           <t>Jul 6  ·  Seattle</t>
         </is>
       </c>
-      <c r="AG19" s="21" t="n"/>
-      <c r="AH19" s="21" t="n"/>
-      <c r="AI19" s="21" t="n"/>
-      <c r="AJ19" s="21" t="n"/>
+      <c r="AG19" s="29" t="n"/>
+      <c r="AH19" s="29" t="n"/>
+      <c r="AI19" s="29" t="n"/>
+      <c r="AJ19" s="29" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>Jun 29  ·  Monterrey</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
-        <is>
-          <t>W R32 #3</t>
-        </is>
+      <c r="E20" s="33">
+        <f>IF(AND($B$17&lt;&gt;"",$C$17&lt;&gt;""),IF($B$17&gt;$C$17,$A$17,IF($C$17&gt;$B$17,$D$17,IF(AND($B$18&lt;&gt;"",$C$18&lt;&gt;""),IF($B$18&gt;$C$18,$A$17,$D$17),"TBD"))),"—")</f>
+        <v/>
       </c>
       <c r="F20" s="10" t="n"/>
       <c r="G20" s="10" t="n"/>
-      <c r="H20" s="26" t="inlineStr">
-        <is>
-          <t>W R32 #4</t>
-        </is>
-      </c>
-      <c r="I20" s="21" t="n"/>
-      <c r="J20" s="21" t="n"/>
-      <c r="K20" s="21" t="n"/>
-      <c r="L20" s="21" t="n"/>
-      <c r="M20" s="21" t="n"/>
-      <c r="N20" s="21" t="n"/>
-      <c r="O20" s="21" t="n"/>
-      <c r="P20" s="21" t="n"/>
-      <c r="Q20" s="21" t="n"/>
-      <c r="R20" s="21" t="n"/>
-      <c r="S20" s="21" t="n"/>
-      <c r="T20" s="21" t="n"/>
-      <c r="U20" s="21" t="n"/>
-      <c r="V20" s="21" t="n"/>
-      <c r="W20" s="21" t="n"/>
-      <c r="X20" s="21" t="n"/>
-      <c r="Y20" s="21" t="n"/>
-      <c r="Z20" s="21" t="n"/>
-      <c r="AA20" s="21" t="n"/>
-      <c r="AB20" s="21" t="n"/>
-      <c r="AC20" s="25" t="inlineStr">
-        <is>
-          <t>W R32 #11</t>
-        </is>
+      <c r="H20" s="34">
+        <f>IF(AND($B$21&lt;&gt;"",$C$21&lt;&gt;""),IF($B$21&gt;$C$21,$A$21,IF($C$21&gt;$B$21,$D$21,IF(AND($B$22&lt;&gt;"",$C$22&lt;&gt;""),IF($B$22&gt;$C$22,$A$21,$D$21),"TBD"))),"—")</f>
+        <v/>
+      </c>
+      <c r="I20" s="29" t="n"/>
+      <c r="J20" s="29" t="n"/>
+      <c r="K20" s="29" t="n"/>
+      <c r="L20" s="29" t="n"/>
+      <c r="M20" s="29" t="n"/>
+      <c r="N20" s="29" t="n"/>
+      <c r="O20" s="29" t="n"/>
+      <c r="P20" s="29" t="n"/>
+      <c r="Q20" s="29" t="n"/>
+      <c r="R20" s="29" t="n"/>
+      <c r="S20" s="29" t="n"/>
+      <c r="T20" s="29" t="n"/>
+      <c r="U20" s="29" t="n"/>
+      <c r="V20" s="29" t="n"/>
+      <c r="W20" s="29" t="n"/>
+      <c r="X20" s="29" t="n"/>
+      <c r="Y20" s="29" t="n"/>
+      <c r="Z20" s="29" t="n"/>
+      <c r="AA20" s="29" t="n"/>
+      <c r="AB20" s="29" t="n"/>
+      <c r="AC20" s="33">
+        <f>IF(AND($AH$17&lt;&gt;"",$AI$17&lt;&gt;""),IF($AH$17&gt;$AI$17,$AG$17,IF($AI$17&gt;$AH$17,$AJ$17,IF(AND($AH$18&lt;&gt;"",$AI$18&lt;&gt;""),IF($AH$18&gt;$AI$18,$AG$17,$AJ$17),"TBD"))),"—")</f>
+        <v/>
       </c>
       <c r="AD20" s="10" t="n"/>
       <c r="AE20" s="10" t="n"/>
-      <c r="AF20" s="26" t="inlineStr">
-        <is>
-          <t>W R32 #12</t>
-        </is>
-      </c>
-      <c r="AG20" s="24" t="inlineStr">
+      <c r="AF20" s="34">
+        <f>IF(AND($AH$21&lt;&gt;"",$AI$21&lt;&gt;""),IF($AH$21&gt;$AI$21,$AG$21,IF($AI$21&gt;$AH$21,$AJ$21,IF(AND($AH$22&lt;&gt;"",$AI$22&lt;&gt;""),IF($AH$22&gt;$AI$22,$AG$21,$AJ$21),"TBD"))),"—")</f>
+        <v/>
+      </c>
+      <c r="AG20" s="32" t="inlineStr">
         <is>
           <t>Jul 2  ·  Toronto</t>
         </is>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
+      <c r="A21" s="33">
+        <f>'Clasificados'!$B$9</f>
+        <v/>
       </c>
       <c r="B21" s="10" t="n"/>
       <c r="C21" s="10" t="n"/>
-      <c r="D21" s="26" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E21" s="27" t="inlineStr">
+      <c r="D21" s="34">
+        <f>'Clasificados'!$C$6</f>
+        <v/>
+      </c>
+      <c r="E21" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="F21" s="28" t="n"/>
-      <c r="G21" s="28" t="n"/>
-      <c r="H21" s="29" t="inlineStr">
+      <c r="F21" s="37" t="n"/>
+      <c r="G21" s="37" t="n"/>
+      <c r="H21" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="I21" s="21" t="n"/>
-      <c r="J21" s="21" t="n"/>
-      <c r="K21" s="21" t="n"/>
-      <c r="L21" s="21" t="n"/>
-      <c r="M21" s="21" t="n"/>
-      <c r="N21" s="21" t="n"/>
-      <c r="O21" s="21" t="n"/>
-      <c r="P21" s="21" t="n"/>
-      <c r="Q21" s="21" t="n"/>
-      <c r="R21" s="21" t="n"/>
-      <c r="S21" s="21" t="n"/>
-      <c r="T21" s="21" t="n"/>
-      <c r="U21" s="21" t="n"/>
-      <c r="V21" s="21" t="n"/>
-      <c r="W21" s="21" t="n"/>
-      <c r="X21" s="21" t="n"/>
-      <c r="Y21" s="21" t="n"/>
-      <c r="Z21" s="21" t="n"/>
-      <c r="AA21" s="21" t="n"/>
-      <c r="AB21" s="21" t="n"/>
-      <c r="AC21" s="27" t="inlineStr">
+      <c r="I21" s="29" t="n"/>
+      <c r="J21" s="29" t="n"/>
+      <c r="K21" s="29" t="n"/>
+      <c r="L21" s="29" t="n"/>
+      <c r="M21" s="29" t="n"/>
+      <c r="N21" s="29" t="n"/>
+      <c r="O21" s="29" t="n"/>
+      <c r="P21" s="29" t="n"/>
+      <c r="Q21" s="29" t="n"/>
+      <c r="R21" s="29" t="n"/>
+      <c r="S21" s="29" t="n"/>
+      <c r="T21" s="29" t="n"/>
+      <c r="U21" s="29" t="n"/>
+      <c r="V21" s="29" t="n"/>
+      <c r="W21" s="29" t="n"/>
+      <c r="X21" s="29" t="n"/>
+      <c r="Y21" s="29" t="n"/>
+      <c r="Z21" s="29" t="n"/>
+      <c r="AA21" s="29" t="n"/>
+      <c r="AB21" s="29" t="n"/>
+      <c r="AC21" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="AD21" s="28" t="n"/>
-      <c r="AE21" s="28" t="n"/>
-      <c r="AF21" s="29" t="inlineStr">
+      <c r="AD21" s="37" t="n"/>
+      <c r="AE21" s="37" t="n"/>
+      <c r="AF21" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="AG21" s="25" t="inlineStr">
-        <is>
-          <t>K2</t>
-        </is>
+      <c r="AG21" s="33">
+        <f>'Clasificados'!$C$14</f>
+        <v/>
       </c>
       <c r="AH21" s="10" t="n"/>
       <c r="AI21" s="10" t="n"/>
-      <c r="AJ21" s="26" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
+      <c r="AJ21" s="34">
+        <f>'Clasificados'!$C$15</f>
+        <v/>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="B22" s="28" t="n"/>
-      <c r="C22" s="28" t="n"/>
-      <c r="D22" s="29" t="inlineStr">
+      <c r="B22" s="37" t="n"/>
+      <c r="C22" s="37" t="n"/>
+      <c r="D22" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="E22" s="21" t="n"/>
-      <c r="F22" s="21" t="n"/>
-      <c r="G22" s="21" t="n"/>
-      <c r="H22" s="21" t="n"/>
-      <c r="I22" s="21" t="n"/>
-      <c r="J22" s="21" t="n"/>
-      <c r="K22" s="21" t="n"/>
-      <c r="L22" s="21" t="n"/>
-      <c r="M22" s="21" t="n"/>
-      <c r="N22" s="21" t="n"/>
-      <c r="O22" s="21" t="n"/>
-      <c r="P22" s="21" t="n"/>
-      <c r="Q22" s="21" t="n"/>
-      <c r="R22" s="21" t="n"/>
-      <c r="S22" s="21" t="n"/>
-      <c r="T22" s="21" t="n"/>
-      <c r="U22" s="21" t="n"/>
-      <c r="V22" s="21" t="n"/>
-      <c r="W22" s="21" t="n"/>
-      <c r="X22" s="21" t="n"/>
-      <c r="Y22" s="21" t="n"/>
-      <c r="Z22" s="21" t="n"/>
-      <c r="AA22" s="21" t="n"/>
-      <c r="AB22" s="21" t="n"/>
-      <c r="AC22" s="21" t="n"/>
-      <c r="AD22" s="21" t="n"/>
-      <c r="AE22" s="21" t="n"/>
-      <c r="AF22" s="21" t="n"/>
-      <c r="AG22" s="27" t="inlineStr">
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="29" t="n"/>
+      <c r="G22" s="29" t="n"/>
+      <c r="H22" s="29" t="n"/>
+      <c r="I22" s="29" t="n"/>
+      <c r="J22" s="29" t="n"/>
+      <c r="K22" s="29" t="n"/>
+      <c r="L22" s="29" t="n"/>
+      <c r="M22" s="29" t="n"/>
+      <c r="N22" s="29" t="n"/>
+      <c r="O22" s="29" t="n"/>
+      <c r="P22" s="29" t="n"/>
+      <c r="Q22" s="29" t="n"/>
+      <c r="R22" s="29" t="n"/>
+      <c r="S22" s="29" t="n"/>
+      <c r="T22" s="29" t="n"/>
+      <c r="U22" s="29" t="n"/>
+      <c r="V22" s="29" t="n"/>
+      <c r="W22" s="29" t="n"/>
+      <c r="X22" s="29" t="n"/>
+      <c r="Y22" s="29" t="n"/>
+      <c r="Z22" s="29" t="n"/>
+      <c r="AA22" s="29" t="n"/>
+      <c r="AB22" s="29" t="n"/>
+      <c r="AC22" s="29" t="n"/>
+      <c r="AD22" s="29" t="n"/>
+      <c r="AE22" s="29" t="n"/>
+      <c r="AF22" s="29" t="n"/>
+      <c r="AG22" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="AH22" s="28" t="n"/>
-      <c r="AI22" s="28" t="n"/>
-      <c r="AJ22" s="29" t="inlineStr">
+      <c r="AH22" s="37" t="n"/>
+      <c r="AI22" s="37" t="n"/>
+      <c r="AJ22" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
     </row>
     <row r="23" ht="13" customHeight="1">
-      <c r="A23" s="21" t="n"/>
-      <c r="B23" s="21" t="n"/>
-      <c r="C23" s="21" t="n"/>
-      <c r="D23" s="21" t="n"/>
-      <c r="E23" s="21" t="n"/>
-      <c r="F23" s="21" t="n"/>
-      <c r="G23" s="21" t="n"/>
-      <c r="H23" s="21" t="n"/>
-      <c r="I23" s="21" t="n"/>
-      <c r="J23" s="21" t="n"/>
-      <c r="K23" s="21" t="n"/>
-      <c r="L23" s="21" t="n"/>
-      <c r="M23" s="24" t="inlineStr">
+      <c r="A23" s="29" t="n"/>
+      <c r="B23" s="29" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="29" t="n"/>
+      <c r="G23" s="29" t="n"/>
+      <c r="H23" s="29" t="n"/>
+      <c r="I23" s="29" t="n"/>
+      <c r="J23" s="29" t="n"/>
+      <c r="K23" s="29" t="n"/>
+      <c r="L23" s="29" t="n"/>
+      <c r="M23" s="32" t="inlineStr">
         <is>
           <t>Jul 14  ·  Dallas</t>
         </is>
       </c>
-      <c r="Q23" s="30" t="inlineStr">
-        <is>
-          <t>Jul 19  ·  New York / NJ · MetLife Stadium</t>
-        </is>
-      </c>
-      <c r="U23" s="24" t="inlineStr">
+      <c r="Q23" s="39" t="inlineStr">
+        <is>
+          <t>Jul 19  ·  New York/NJ · MetLife Stadium</t>
+        </is>
+      </c>
+      <c r="U23" s="32" t="inlineStr">
         <is>
           <t>Jul 15  ·  Atlanta</t>
         </is>
       </c>
-      <c r="Y23" s="21" t="n"/>
-      <c r="Z23" s="21" t="n"/>
-      <c r="AA23" s="21" t="n"/>
-      <c r="AB23" s="21" t="n"/>
-      <c r="AC23" s="21" t="n"/>
-      <c r="AD23" s="21" t="n"/>
-      <c r="AE23" s="21" t="n"/>
-      <c r="AF23" s="21" t="n"/>
-      <c r="AG23" s="21" t="n"/>
-      <c r="AH23" s="21" t="n"/>
-      <c r="AI23" s="21" t="n"/>
-      <c r="AJ23" s="21" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="Y23" s="29" t="n"/>
+      <c r="Z23" s="29" t="n"/>
+      <c r="AA23" s="29" t="n"/>
+      <c r="AB23" s="29" t="n"/>
+      <c r="AC23" s="29" t="n"/>
+      <c r="AD23" s="29" t="n"/>
+      <c r="AE23" s="29" t="n"/>
+      <c r="AF23" s="29" t="n"/>
+      <c r="AG23" s="29" t="n"/>
+      <c r="AH23" s="29" t="n"/>
+      <c r="AI23" s="29" t="n"/>
+      <c r="AJ23" s="29" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>Jun 30  ·  Dallas</t>
         </is>
       </c>
-      <c r="E24" s="21" t="n"/>
-      <c r="F24" s="21" t="n"/>
-      <c r="G24" s="21" t="n"/>
-      <c r="H24" s="21" t="n"/>
-      <c r="I24" s="21" t="n"/>
-      <c r="J24" s="21" t="n"/>
-      <c r="K24" s="21" t="n"/>
-      <c r="L24" s="21" t="n"/>
-      <c r="M24" s="25" t="inlineStr">
-        <is>
-          <t>W QF-L1</t>
-        </is>
+      <c r="E24" s="29" t="n"/>
+      <c r="F24" s="29" t="n"/>
+      <c r="G24" s="29" t="n"/>
+      <c r="H24" s="29" t="n"/>
+      <c r="I24" s="29" t="n"/>
+      <c r="J24" s="29" t="n"/>
+      <c r="K24" s="29" t="n"/>
+      <c r="L24" s="29" t="n"/>
+      <c r="M24" s="33">
+        <f>IF(AND($J$16&lt;&gt;"",$K$16&lt;&gt;""),IF($J$16&gt;$K$16,$I$16,IF($K$16&gt;$J$16,$L$16,IF(AND($J$17&lt;&gt;"",$K$17&lt;&gt;""),IF($J$17&gt;$K$17,$I$16,$L$16),"TBD"))),"—")</f>
+        <v/>
       </c>
       <c r="N24" s="10" t="n"/>
       <c r="O24" s="10" t="n"/>
-      <c r="P24" s="26" t="inlineStr">
-        <is>
-          <t>W QF-L2</t>
-        </is>
-      </c>
-      <c r="Q24" s="31" t="inlineStr">
-        <is>
-          <t>W SF-L</t>
-        </is>
-      </c>
-      <c r="R24" s="32" t="n"/>
-      <c r="S24" s="32" t="n"/>
-      <c r="T24" s="33" t="inlineStr">
-        <is>
-          <t>W SF-R</t>
-        </is>
-      </c>
-      <c r="U24" s="25" t="inlineStr">
-        <is>
-          <t>W QF-R1</t>
-        </is>
+      <c r="P24" s="34">
+        <f>IF(AND($J$32&lt;&gt;"",$K$32&lt;&gt;""),IF($J$32&gt;$K$32,$I$32,IF($K$32&gt;$J$32,$L$32,IF(AND($J$33&lt;&gt;"",$K$33&lt;&gt;""),IF($J$33&gt;$K$33,$I$32,$L$32),"TBD"))),"—")</f>
+        <v/>
+      </c>
+      <c r="Q24" s="40">
+        <f>IF(AND($N$24&lt;&gt;"",$O$24&lt;&gt;""),IF($N$24&gt;$O$24,$M$24,IF($O$24&gt;$N$24,$P$24,IF(AND($N$25&lt;&gt;"",$O$25&lt;&gt;""),IF($N$25&gt;$O$25,$M$24,$P$24),"TBD"))),"—")</f>
+        <v/>
+      </c>
+      <c r="R24" s="41" t="n"/>
+      <c r="S24" s="41" t="n"/>
+      <c r="T24" s="42">
+        <f>IF(AND($V$24&lt;&gt;"",$W$24&lt;&gt;""),IF($V$24&gt;$W$24,$U$24,IF($W$24&gt;$V$24,$X$24,IF(AND($V$25&lt;&gt;"",$W$25&lt;&gt;""),IF($V$25&gt;$W$25,$U$24,$X$24),"TBD"))),"—")</f>
+        <v/>
+      </c>
+      <c r="U24" s="33">
+        <f>IF(AND($Z$16&lt;&gt;"",$AA$16&lt;&gt;""),IF($Z$16&gt;$AA$16,$Y$16,IF($AA$16&gt;$Z$16,$AB$16,IF(AND($Z$17&lt;&gt;"",$AA$17&lt;&gt;""),IF($Z$17&gt;$AA$17,$Y$16,$AB$16),"TBD"))),"—")</f>
+        <v/>
       </c>
       <c r="V24" s="10" t="n"/>
       <c r="W24" s="10" t="n"/>
-      <c r="X24" s="26" t="inlineStr">
-        <is>
-          <t>W QF-R2</t>
-        </is>
-      </c>
-      <c r="Y24" s="21" t="n"/>
-      <c r="Z24" s="21" t="n"/>
-      <c r="AA24" s="21" t="n"/>
-      <c r="AB24" s="21" t="n"/>
-      <c r="AC24" s="21" t="n"/>
-      <c r="AD24" s="21" t="n"/>
-      <c r="AE24" s="21" t="n"/>
-      <c r="AF24" s="21" t="n"/>
-      <c r="AG24" s="24" t="inlineStr">
+      <c r="X24" s="34">
+        <f>IF(AND($Z$32&lt;&gt;"",$AA$32&lt;&gt;""),IF($Z$32&gt;$AA$32,$Y$32,IF($AA$32&gt;$Z$32,$AB$32,IF(AND($Z$33&lt;&gt;"",$AA$33&lt;&gt;""),IF($Z$33&gt;$AA$33,$Y$32,$AB$32),"TBD"))),"—")</f>
+        <v/>
+      </c>
+      <c r="Y24" s="29" t="n"/>
+      <c r="Z24" s="29" t="n"/>
+      <c r="AA24" s="29" t="n"/>
+      <c r="AB24" s="29" t="n"/>
+      <c r="AC24" s="29" t="n"/>
+      <c r="AD24" s="29" t="n"/>
+      <c r="AE24" s="29" t="n"/>
+      <c r="AF24" s="29" t="n"/>
+      <c r="AG24" s="32" t="inlineStr">
         <is>
           <t>Jul 2  ·  Vancouver</t>
         </is>
       </c>
     </row>
     <row r="25" ht="14" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
+      <c r="A25" s="33">
+        <f>'Clasificados'!$C$8</f>
+        <v/>
       </c>
       <c r="B25" s="10" t="n"/>
       <c r="C25" s="10" t="n"/>
-      <c r="D25" s="26" t="inlineStr">
-        <is>
-          <t>I2</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="n"/>
-      <c r="F25" s="21" t="n"/>
-      <c r="G25" s="21" t="n"/>
-      <c r="H25" s="21" t="n"/>
-      <c r="I25" s="21" t="n"/>
-      <c r="J25" s="21" t="n"/>
-      <c r="K25" s="21" t="n"/>
-      <c r="L25" s="21" t="n"/>
-      <c r="M25" s="27" t="inlineStr">
+      <c r="D25" s="34">
+        <f>'Clasificados'!$C$12</f>
+        <v/>
+      </c>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="29" t="n"/>
+      <c r="G25" s="29" t="n"/>
+      <c r="H25" s="29" t="n"/>
+      <c r="I25" s="29" t="n"/>
+      <c r="J25" s="29" t="n"/>
+      <c r="K25" s="29" t="n"/>
+      <c r="L25" s="29" t="n"/>
+      <c r="M25" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="N25" s="28" t="n"/>
-      <c r="O25" s="28" t="n"/>
-      <c r="P25" s="29" t="inlineStr">
+      <c r="N25" s="37" t="n"/>
+      <c r="O25" s="37" t="n"/>
+      <c r="P25" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="Q25" s="27" t="inlineStr">
+      <c r="Q25" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="R25" s="28" t="n"/>
-      <c r="S25" s="28" t="n"/>
-      <c r="T25" s="29" t="inlineStr">
+      <c r="R25" s="37" t="n"/>
+      <c r="S25" s="37" t="n"/>
+      <c r="T25" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="U25" s="27" t="inlineStr">
+      <c r="U25" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="V25" s="28" t="n"/>
-      <c r="W25" s="28" t="n"/>
-      <c r="X25" s="29" t="inlineStr">
+      <c r="V25" s="37" t="n"/>
+      <c r="W25" s="37" t="n"/>
+      <c r="X25" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="Y25" s="21" t="n"/>
-      <c r="Z25" s="21" t="n"/>
-      <c r="AA25" s="21" t="n"/>
-      <c r="AB25" s="21" t="n"/>
-      <c r="AC25" s="21" t="n"/>
-      <c r="AD25" s="21" t="n"/>
-      <c r="AE25" s="21" t="n"/>
-      <c r="AF25" s="21" t="n"/>
-      <c r="AG25" s="25" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
+      <c r="Y25" s="29" t="n"/>
+      <c r="Z25" s="29" t="n"/>
+      <c r="AA25" s="29" t="n"/>
+      <c r="AB25" s="29" t="n"/>
+      <c r="AC25" s="29" t="n"/>
+      <c r="AD25" s="29" t="n"/>
+      <c r="AE25" s="29" t="n"/>
+      <c r="AF25" s="29" t="n"/>
+      <c r="AG25" s="33">
+        <f>'Clasificados'!$B$5</f>
+        <v/>
       </c>
       <c r="AH25" s="10" t="n"/>
       <c r="AI25" s="10" t="n"/>
-      <c r="AJ25" s="26" t="inlineStr">
-        <is>
-          <t>3rd*</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="27" t="inlineStr">
+      <c r="AJ25" s="35" t="inlineStr">
+        <is>
+          <t>◀ Enter 3rd</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="B26" s="28" t="n"/>
-      <c r="C26" s="28" t="n"/>
-      <c r="D26" s="29" t="inlineStr">
+      <c r="B26" s="37" t="n"/>
+      <c r="C26" s="37" t="n"/>
+      <c r="D26" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="E26" s="21" t="n"/>
-      <c r="F26" s="21" t="n"/>
-      <c r="G26" s="21" t="n"/>
-      <c r="H26" s="21" t="n"/>
-      <c r="I26" s="21" t="n"/>
-      <c r="J26" s="21" t="n"/>
-      <c r="K26" s="21" t="n"/>
-      <c r="L26" s="21" t="n"/>
-      <c r="M26" s="21" t="n"/>
-      <c r="N26" s="21" t="n"/>
-      <c r="O26" s="21" t="n"/>
-      <c r="P26" s="21" t="n"/>
-      <c r="Q26" s="34" t="inlineStr">
-        <is>
-          <t>🏆  WORLD CHAMPION  🏆</t>
-        </is>
-      </c>
-      <c r="U26" s="21" t="n"/>
-      <c r="V26" s="21" t="n"/>
-      <c r="W26" s="21" t="n"/>
-      <c r="X26" s="21" t="n"/>
-      <c r="Y26" s="21" t="n"/>
-      <c r="Z26" s="21" t="n"/>
-      <c r="AA26" s="21" t="n"/>
-      <c r="AB26" s="21" t="n"/>
-      <c r="AC26" s="21" t="n"/>
-      <c r="AD26" s="21" t="n"/>
-      <c r="AE26" s="21" t="n"/>
-      <c r="AF26" s="21" t="n"/>
-      <c r="AG26" s="27" t="inlineStr">
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="29" t="n"/>
+      <c r="G26" s="29" t="n"/>
+      <c r="H26" s="29" t="n"/>
+      <c r="I26" s="29" t="n"/>
+      <c r="J26" s="29" t="n"/>
+      <c r="K26" s="29" t="n"/>
+      <c r="L26" s="29" t="n"/>
+      <c r="M26" s="29" t="n"/>
+      <c r="N26" s="29" t="n"/>
+      <c r="O26" s="29" t="n"/>
+      <c r="P26" s="29" t="n"/>
+      <c r="Q26" s="43">
+        <f>IF($R$24&lt;&gt;"","🏆 "&amp;IF(AND($R$24&lt;&gt;"",$S$24&lt;&gt;""),IF($R$24&gt;$S$24,$Q$24,IF($S$24&gt;$R$24,$T$24,IF(AND($R$25&lt;&gt;"",$S$25&lt;&gt;""),IF($R$25&gt;$S$25,$Q$24,$T$24),"TBD"))),"—")&amp;" 🏆","🏆 WORLD CHAMPION 🏆")</f>
+        <v/>
+      </c>
+      <c r="U26" s="29" t="n"/>
+      <c r="V26" s="29" t="n"/>
+      <c r="W26" s="29" t="n"/>
+      <c r="X26" s="29" t="n"/>
+      <c r="Y26" s="29" t="n"/>
+      <c r="Z26" s="29" t="n"/>
+      <c r="AA26" s="29" t="n"/>
+      <c r="AB26" s="29" t="n"/>
+      <c r="AC26" s="29" t="n"/>
+      <c r="AD26" s="29" t="n"/>
+      <c r="AE26" s="29" t="n"/>
+      <c r="AF26" s="29" t="n"/>
+      <c r="AG26" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="AH26" s="28" t="n"/>
-      <c r="AI26" s="28" t="n"/>
-      <c r="AJ26" s="29" t="inlineStr">
+      <c r="AH26" s="37" t="n"/>
+      <c r="AI26" s="37" t="n"/>
+      <c r="AJ26" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
     </row>
     <row r="27" ht="13" customHeight="1">
-      <c r="A27" s="21" t="n"/>
-      <c r="B27" s="21" t="n"/>
-      <c r="C27" s="21" t="n"/>
-      <c r="D27" s="21" t="n"/>
-      <c r="E27" s="24" t="inlineStr">
+      <c r="A27" s="29" t="n"/>
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="32" t="inlineStr">
         <is>
           <t>Jul 5  ·  New York/NJ</t>
         </is>
       </c>
-      <c r="I27" s="21" t="n"/>
-      <c r="J27" s="21" t="n"/>
-      <c r="K27" s="21" t="n"/>
-      <c r="L27" s="21" t="n"/>
-      <c r="M27" s="21" t="n"/>
-      <c r="N27" s="21" t="n"/>
-      <c r="O27" s="21" t="n"/>
-      <c r="P27" s="21" t="n"/>
-      <c r="Q27" s="21" t="n"/>
-      <c r="R27" s="21" t="n"/>
-      <c r="S27" s="21" t="n"/>
-      <c r="T27" s="21" t="n"/>
-      <c r="U27" s="21" t="n"/>
-      <c r="V27" s="21" t="n"/>
-      <c r="W27" s="21" t="n"/>
-      <c r="X27" s="21" t="n"/>
-      <c r="Y27" s="21" t="n"/>
-      <c r="Z27" s="21" t="n"/>
-      <c r="AA27" s="21" t="n"/>
-      <c r="AB27" s="21" t="n"/>
-      <c r="AC27" s="24" t="inlineStr">
+      <c r="I27" s="29" t="n"/>
+      <c r="J27" s="29" t="n"/>
+      <c r="K27" s="29" t="n"/>
+      <c r="L27" s="29" t="n"/>
+      <c r="M27" s="29" t="n"/>
+      <c r="N27" s="29" t="n"/>
+      <c r="O27" s="29" t="n"/>
+      <c r="P27" s="29" t="n"/>
+      <c r="Q27" s="29" t="n"/>
+      <c r="R27" s="29" t="n"/>
+      <c r="S27" s="29" t="n"/>
+      <c r="T27" s="29" t="n"/>
+      <c r="U27" s="29" t="n"/>
+      <c r="V27" s="29" t="n"/>
+      <c r="W27" s="29" t="n"/>
+      <c r="X27" s="29" t="n"/>
+      <c r="Y27" s="29" t="n"/>
+      <c r="Z27" s="29" t="n"/>
+      <c r="AA27" s="29" t="n"/>
+      <c r="AB27" s="29" t="n"/>
+      <c r="AC27" s="32" t="inlineStr">
         <is>
           <t>Jul 7  ·  Atlanta</t>
         </is>
       </c>
-      <c r="AG27" s="21" t="n"/>
-      <c r="AH27" s="21" t="n"/>
-      <c r="AI27" s="21" t="n"/>
-      <c r="AJ27" s="21" t="n"/>
+      <c r="AG27" s="29" t="n"/>
+      <c r="AH27" s="29" t="n"/>
+      <c r="AI27" s="29" t="n"/>
+      <c r="AJ27" s="29" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="32" t="inlineStr">
         <is>
           <t>Jun 30  ·  New York/NJ</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>W R32 #5</t>
-        </is>
+      <c r="E28" s="33">
+        <f>IF(AND($B$25&lt;&gt;"",$C$25&lt;&gt;""),IF($B$25&gt;$C$25,$A$25,IF($C$25&gt;$B$25,$D$25,IF(AND($B$26&lt;&gt;"",$C$26&lt;&gt;""),IF($B$26&gt;$C$26,$A$25,$D$25),"TBD"))),"—")</f>
+        <v/>
       </c>
       <c r="F28" s="10" t="n"/>
       <c r="G28" s="10" t="n"/>
-      <c r="H28" s="26" t="inlineStr">
-        <is>
-          <t>W R32 #6</t>
-        </is>
-      </c>
-      <c r="I28" s="21" t="n"/>
-      <c r="J28" s="21" t="n"/>
-      <c r="K28" s="21" t="n"/>
-      <c r="L28" s="21" t="n"/>
-      <c r="M28" s="21" t="n"/>
-      <c r="N28" s="21" t="n"/>
-      <c r="O28" s="21" t="n"/>
-      <c r="P28" s="21" t="n"/>
-      <c r="Q28" s="21" t="n"/>
-      <c r="R28" s="21" t="n"/>
-      <c r="S28" s="21" t="n"/>
-      <c r="T28" s="21" t="n"/>
-      <c r="U28" s="21" t="n"/>
-      <c r="V28" s="21" t="n"/>
-      <c r="W28" s="21" t="n"/>
-      <c r="X28" s="21" t="n"/>
-      <c r="Y28" s="21" t="n"/>
-      <c r="Z28" s="21" t="n"/>
-      <c r="AA28" s="21" t="n"/>
-      <c r="AB28" s="21" t="n"/>
-      <c r="AC28" s="25" t="inlineStr">
-        <is>
-          <t>W R32 #13</t>
-        </is>
+      <c r="H28" s="34">
+        <f>IF(AND($B$29&lt;&gt;"",$C$29&lt;&gt;""),IF($B$29&gt;$C$29,$A$29,IF($C$29&gt;$B$29,$D$29,IF(AND($B$30&lt;&gt;"",$C$30&lt;&gt;""),IF($B$30&gt;$C$30,$A$29,$D$29),"TBD"))),"—")</f>
+        <v/>
+      </c>
+      <c r="I28" s="29" t="n"/>
+      <c r="J28" s="29" t="n"/>
+      <c r="K28" s="29" t="n"/>
+      <c r="L28" s="29" t="n"/>
+      <c r="M28" s="29" t="n"/>
+      <c r="N28" s="29" t="n"/>
+      <c r="O28" s="29" t="n"/>
+      <c r="P28" s="29" t="n"/>
+      <c r="Q28" s="29" t="n"/>
+      <c r="R28" s="29" t="n"/>
+      <c r="S28" s="29" t="n"/>
+      <c r="T28" s="29" t="n"/>
+      <c r="U28" s="29" t="n"/>
+      <c r="V28" s="29" t="n"/>
+      <c r="W28" s="29" t="n"/>
+      <c r="X28" s="29" t="n"/>
+      <c r="Y28" s="29" t="n"/>
+      <c r="Z28" s="29" t="n"/>
+      <c r="AA28" s="29" t="n"/>
+      <c r="AB28" s="29" t="n"/>
+      <c r="AC28" s="33">
+        <f>IF(AND($AH$25&lt;&gt;"",$AI$25&lt;&gt;""),IF($AH$25&gt;$AI$25,$AG$25,IF($AI$25&gt;$AH$25,$AJ$25,IF(AND($AH$26&lt;&gt;"",$AI$26&lt;&gt;""),IF($AH$26&gt;$AI$26,$AG$25,$AJ$25),"TBD"))),"—")</f>
+        <v/>
       </c>
       <c r="AD28" s="10" t="n"/>
       <c r="AE28" s="10" t="n"/>
-      <c r="AF28" s="26" t="inlineStr">
-        <is>
-          <t>W R32 #14</t>
-        </is>
-      </c>
-      <c r="AG28" s="24" t="inlineStr">
+      <c r="AF28" s="34">
+        <f>IF(AND($AH$29&lt;&gt;"",$AI$29&lt;&gt;""),IF($AH$29&gt;$AI$29,$AG$29,IF($AI$29&gt;$AH$29,$AJ$29,IF(AND($AH$30&lt;&gt;"",$AI$30&lt;&gt;""),IF($AH$30&gt;$AI$30,$AG$29,$AJ$29),"TBD"))),"—")</f>
+        <v/>
+      </c>
+      <c r="AG28" s="32" t="inlineStr">
         <is>
           <t>Jul 3  ·  Dallas</t>
         </is>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
-        <is>
-          <t>I1</t>
-        </is>
+      <c r="A29" s="33">
+        <f>'Clasificados'!$B$12</f>
+        <v/>
       </c>
       <c r="B29" s="10" t="n"/>
       <c r="C29" s="10" t="n"/>
-      <c r="D29" s="26" t="inlineStr">
-        <is>
-          <t>3rd*</t>
-        </is>
-      </c>
-      <c r="E29" s="27" t="inlineStr">
+      <c r="D29" s="35" t="inlineStr">
+        <is>
+          <t>◀ Enter 3rd</t>
+        </is>
+      </c>
+      <c r="E29" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="F29" s="28" t="n"/>
-      <c r="G29" s="28" t="n"/>
-      <c r="H29" s="29" t="inlineStr">
+      <c r="F29" s="37" t="n"/>
+      <c r="G29" s="37" t="n"/>
+      <c r="H29" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="I29" s="21" t="n"/>
-      <c r="J29" s="21" t="n"/>
-      <c r="K29" s="21" t="n"/>
-      <c r="L29" s="21" t="n"/>
-      <c r="M29" s="21" t="n"/>
-      <c r="N29" s="21" t="n"/>
-      <c r="O29" s="21" t="n"/>
-      <c r="P29" s="21" t="n"/>
-      <c r="Q29" s="21" t="n"/>
-      <c r="R29" s="21" t="n"/>
-      <c r="S29" s="21" t="n"/>
-      <c r="T29" s="21" t="n"/>
-      <c r="U29" s="21" t="n"/>
-      <c r="V29" s="21" t="n"/>
-      <c r="W29" s="21" t="n"/>
-      <c r="X29" s="21" t="n"/>
-      <c r="Y29" s="21" t="n"/>
-      <c r="Z29" s="21" t="n"/>
-      <c r="AA29" s="21" t="n"/>
-      <c r="AB29" s="21" t="n"/>
-      <c r="AC29" s="27" t="inlineStr">
+      <c r="I29" s="29" t="n"/>
+      <c r="J29" s="29" t="n"/>
+      <c r="K29" s="29" t="n"/>
+      <c r="L29" s="29" t="n"/>
+      <c r="M29" s="29" t="n"/>
+      <c r="N29" s="29" t="n"/>
+      <c r="O29" s="29" t="n"/>
+      <c r="P29" s="29" t="n"/>
+      <c r="Q29" s="29" t="n"/>
+      <c r="R29" s="29" t="n"/>
+      <c r="S29" s="29" t="n"/>
+      <c r="T29" s="29" t="n"/>
+      <c r="U29" s="29" t="n"/>
+      <c r="V29" s="29" t="n"/>
+      <c r="W29" s="29" t="n"/>
+      <c r="X29" s="29" t="n"/>
+      <c r="Y29" s="29" t="n"/>
+      <c r="Z29" s="29" t="n"/>
+      <c r="AA29" s="29" t="n"/>
+      <c r="AB29" s="29" t="n"/>
+      <c r="AC29" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="AD29" s="28" t="n"/>
-      <c r="AE29" s="28" t="n"/>
-      <c r="AF29" s="29" t="inlineStr">
+      <c r="AD29" s="37" t="n"/>
+      <c r="AE29" s="37" t="n"/>
+      <c r="AF29" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="AG29" s="25" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
+      <c r="AG29" s="33">
+        <f>'Clasificados'!$C$7</f>
+        <v/>
       </c>
       <c r="AH29" s="10" t="n"/>
       <c r="AI29" s="10" t="n"/>
-      <c r="AJ29" s="26" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
+      <c r="AJ29" s="34">
+        <f>'Clasificados'!$C$10</f>
+        <v/>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="B30" s="28" t="n"/>
-      <c r="C30" s="28" t="n"/>
-      <c r="D30" s="29" t="inlineStr">
+      <c r="B30" s="37" t="n"/>
+      <c r="C30" s="37" t="n"/>
+      <c r="D30" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="E30" s="21" t="n"/>
-      <c r="F30" s="21" t="n"/>
-      <c r="G30" s="21" t="n"/>
-      <c r="H30" s="21" t="n"/>
-      <c r="I30" s="21" t="n"/>
-      <c r="J30" s="21" t="n"/>
-      <c r="K30" s="21" t="n"/>
-      <c r="L30" s="21" t="n"/>
-      <c r="M30" s="21" t="n"/>
-      <c r="N30" s="21" t="n"/>
-      <c r="O30" s="21" t="n"/>
-      <c r="P30" s="21" t="n"/>
-      <c r="Q30" s="21" t="n"/>
-      <c r="R30" s="21" t="n"/>
-      <c r="S30" s="21" t="n"/>
-      <c r="T30" s="21" t="n"/>
-      <c r="U30" s="21" t="n"/>
-      <c r="V30" s="21" t="n"/>
-      <c r="W30" s="21" t="n"/>
-      <c r="X30" s="21" t="n"/>
-      <c r="Y30" s="21" t="n"/>
-      <c r="Z30" s="21" t="n"/>
-      <c r="AA30" s="21" t="n"/>
-      <c r="AB30" s="21" t="n"/>
-      <c r="AC30" s="21" t="n"/>
-      <c r="AD30" s="21" t="n"/>
-      <c r="AE30" s="21" t="n"/>
-      <c r="AF30" s="21" t="n"/>
-      <c r="AG30" s="27" t="inlineStr">
+      <c r="E30" s="29" t="n"/>
+      <c r="F30" s="29" t="n"/>
+      <c r="G30" s="29" t="n"/>
+      <c r="H30" s="29" t="n"/>
+      <c r="I30" s="29" t="n"/>
+      <c r="J30" s="29" t="n"/>
+      <c r="K30" s="29" t="n"/>
+      <c r="L30" s="29" t="n"/>
+      <c r="M30" s="29" t="n"/>
+      <c r="N30" s="29" t="n"/>
+      <c r="O30" s="29" t="n"/>
+      <c r="P30" s="29" t="n"/>
+      <c r="Q30" s="29" t="n"/>
+      <c r="R30" s="29" t="n"/>
+      <c r="S30" s="29" t="n"/>
+      <c r="T30" s="29" t="n"/>
+      <c r="U30" s="29" t="n"/>
+      <c r="V30" s="29" t="n"/>
+      <c r="W30" s="29" t="n"/>
+      <c r="X30" s="29" t="n"/>
+      <c r="Y30" s="29" t="n"/>
+      <c r="Z30" s="29" t="n"/>
+      <c r="AA30" s="29" t="n"/>
+      <c r="AB30" s="29" t="n"/>
+      <c r="AC30" s="29" t="n"/>
+      <c r="AD30" s="29" t="n"/>
+      <c r="AE30" s="29" t="n"/>
+      <c r="AF30" s="29" t="n"/>
+      <c r="AG30" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="AH30" s="28" t="n"/>
-      <c r="AI30" s="28" t="n"/>
-      <c r="AJ30" s="29" t="inlineStr">
+      <c r="AH30" s="37" t="n"/>
+      <c r="AI30" s="37" t="n"/>
+      <c r="AJ30" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
     </row>
     <row r="31" ht="13" customHeight="1">
-      <c r="A31" s="21" t="n"/>
-      <c r="B31" s="21" t="n"/>
-      <c r="C31" s="21" t="n"/>
-      <c r="D31" s="21" t="n"/>
-      <c r="E31" s="21" t="n"/>
-      <c r="F31" s="21" t="n"/>
-      <c r="G31" s="21" t="n"/>
-      <c r="H31" s="21" t="n"/>
-      <c r="I31" s="24" t="inlineStr">
+      <c r="A31" s="29" t="n"/>
+      <c r="B31" s="29" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="29" t="n"/>
+      <c r="F31" s="29" t="n"/>
+      <c r="G31" s="29" t="n"/>
+      <c r="H31" s="29" t="n"/>
+      <c r="I31" s="32" t="inlineStr">
         <is>
           <t>Jul 10  ·  Los Angeles</t>
         </is>
       </c>
-      <c r="M31" s="21" t="n"/>
-      <c r="N31" s="21" t="n"/>
-      <c r="O31" s="21" t="n"/>
-      <c r="P31" s="21" t="n"/>
-      <c r="Q31" s="21" t="n"/>
-      <c r="R31" s="21" t="n"/>
-      <c r="S31" s="21" t="n"/>
-      <c r="T31" s="21" t="n"/>
-      <c r="U31" s="21" t="n"/>
-      <c r="V31" s="21" t="n"/>
-      <c r="W31" s="21" t="n"/>
-      <c r="X31" s="21" t="n"/>
-      <c r="Y31" s="24" t="inlineStr">
+      <c r="M31" s="29" t="n"/>
+      <c r="N31" s="29" t="n"/>
+      <c r="O31" s="29" t="n"/>
+      <c r="P31" s="29" t="n"/>
+      <c r="Q31" s="29" t="n"/>
+      <c r="R31" s="29" t="n"/>
+      <c r="S31" s="29" t="n"/>
+      <c r="T31" s="29" t="n"/>
+      <c r="U31" s="29" t="n"/>
+      <c r="V31" s="29" t="n"/>
+      <c r="W31" s="29" t="n"/>
+      <c r="X31" s="29" t="n"/>
+      <c r="Y31" s="32" t="inlineStr">
         <is>
           <t>Jul 11  ·  Kansas City</t>
         </is>
       </c>
-      <c r="AC31" s="21" t="n"/>
-      <c r="AD31" s="21" t="n"/>
-      <c r="AE31" s="21" t="n"/>
-      <c r="AF31" s="21" t="n"/>
-      <c r="AG31" s="21" t="n"/>
-      <c r="AH31" s="21" t="n"/>
-      <c r="AI31" s="21" t="n"/>
-      <c r="AJ31" s="21" t="n"/>
+      <c r="AC31" s="29" t="n"/>
+      <c r="AD31" s="29" t="n"/>
+      <c r="AE31" s="29" t="n"/>
+      <c r="AF31" s="29" t="n"/>
+      <c r="AG31" s="29" t="n"/>
+      <c r="AH31" s="29" t="n"/>
+      <c r="AI31" s="29" t="n"/>
+      <c r="AJ31" s="29" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>Jun 30  ·  Mexico City</t>
         </is>
       </c>
-      <c r="E32" s="21" t="n"/>
-      <c r="F32" s="21" t="n"/>
-      <c r="G32" s="21" t="n"/>
-      <c r="H32" s="21" t="n"/>
-      <c r="I32" s="25" t="inlineStr">
-        <is>
-          <t>W R16-L3</t>
-        </is>
+      <c r="E32" s="29" t="n"/>
+      <c r="F32" s="29" t="n"/>
+      <c r="G32" s="29" t="n"/>
+      <c r="H32" s="29" t="n"/>
+      <c r="I32" s="33">
+        <f>IF(AND($F$28&lt;&gt;"",$G$28&lt;&gt;""),IF($F$28&gt;$G$28,$E$28,IF($G$28&gt;$F$28,$H$28,IF(AND($F$29&lt;&gt;"",$G$29&lt;&gt;""),IF($F$29&gt;$G$29,$E$28,$H$28),"TBD"))),"—")</f>
+        <v/>
       </c>
       <c r="J32" s="10" t="n"/>
       <c r="K32" s="10" t="n"/>
-      <c r="L32" s="26" t="inlineStr">
-        <is>
-          <t>W R16-L4</t>
-        </is>
-      </c>
-      <c r="M32" s="21" t="n"/>
-      <c r="N32" s="21" t="n"/>
-      <c r="O32" s="21" t="n"/>
-      <c r="P32" s="21" t="n"/>
-      <c r="Q32" s="21" t="n"/>
-      <c r="R32" s="21" t="n"/>
-      <c r="S32" s="21" t="n"/>
-      <c r="T32" s="21" t="n"/>
-      <c r="U32" s="21" t="n"/>
-      <c r="V32" s="21" t="n"/>
-      <c r="W32" s="21" t="n"/>
-      <c r="X32" s="21" t="n"/>
-      <c r="Y32" s="25" t="inlineStr">
-        <is>
-          <t>W R16-R3</t>
-        </is>
+      <c r="L32" s="34">
+        <f>IF(AND($F$36&lt;&gt;"",$G$36&lt;&gt;""),IF($F$36&gt;$G$36,$E$36,IF($G$36&gt;$F$36,$H$36,IF(AND($F$37&lt;&gt;"",$G$37&lt;&gt;""),IF($F$37&gt;$G$37,$E$36,$H$36),"TBD"))),"—")</f>
+        <v/>
+      </c>
+      <c r="M32" s="29" t="n"/>
+      <c r="N32" s="29" t="n"/>
+      <c r="O32" s="29" t="n"/>
+      <c r="P32" s="29" t="n"/>
+      <c r="Q32" s="29" t="n"/>
+      <c r="R32" s="29" t="n"/>
+      <c r="S32" s="29" t="n"/>
+      <c r="T32" s="29" t="n"/>
+      <c r="U32" s="29" t="n"/>
+      <c r="V32" s="29" t="n"/>
+      <c r="W32" s="29" t="n"/>
+      <c r="X32" s="29" t="n"/>
+      <c r="Y32" s="33">
+        <f>IF(AND($AD$28&lt;&gt;"",$AE$28&lt;&gt;""),IF($AD$28&gt;$AE$28,$AC$28,IF($AE$28&gt;$AD$28,$AF$28,IF(AND($AD$29&lt;&gt;"",$AE$29&lt;&gt;""),IF($AD$29&gt;$AE$29,$AC$28,$AF$28),"TBD"))),"—")</f>
+        <v/>
       </c>
       <c r="Z32" s="10" t="n"/>
       <c r="AA32" s="10" t="n"/>
-      <c r="AB32" s="26" t="inlineStr">
-        <is>
-          <t>W R16-R4</t>
-        </is>
-      </c>
-      <c r="AC32" s="21" t="n"/>
-      <c r="AD32" s="21" t="n"/>
-      <c r="AE32" s="21" t="n"/>
-      <c r="AF32" s="21" t="n"/>
-      <c r="AG32" s="24" t="inlineStr">
+      <c r="AB32" s="34">
+        <f>IF(AND($AD$36&lt;&gt;"",$AE$36&lt;&gt;""),IF($AD$36&gt;$AE$36,$AC$36,IF($AE$36&gt;$AD$36,$AF$36,IF(AND($AD$37&lt;&gt;"",$AE$37&lt;&gt;""),IF($AD$37&gt;$AE$37,$AC$36,$AF$36),"TBD"))),"—")</f>
+        <v/>
+      </c>
+      <c r="AC32" s="29" t="n"/>
+      <c r="AD32" s="29" t="n"/>
+      <c r="AE32" s="29" t="n"/>
+      <c r="AF32" s="29" t="n"/>
+      <c r="AG32" s="32" t="inlineStr">
         <is>
           <t>Jul 3  ·  Miami</t>
         </is>
       </c>
     </row>
     <row r="33" ht="14" customHeight="1">
-      <c r="A33" s="25" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
+      <c r="A33" s="33">
+        <f>'Clasificados'!$B$4</f>
+        <v/>
       </c>
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="10" t="n"/>
-      <c r="D33" s="26" t="inlineStr">
-        <is>
-          <t>3rd*</t>
-        </is>
-      </c>
-      <c r="E33" s="21" t="n"/>
-      <c r="F33" s="21" t="n"/>
-      <c r="G33" s="21" t="n"/>
-      <c r="H33" s="21" t="n"/>
-      <c r="I33" s="27" t="inlineStr">
+      <c r="D33" s="35" t="inlineStr">
+        <is>
+          <t>◀ Enter 3rd</t>
+        </is>
+      </c>
+      <c r="E33" s="29" t="n"/>
+      <c r="F33" s="29" t="n"/>
+      <c r="G33" s="29" t="n"/>
+      <c r="H33" s="29" t="n"/>
+      <c r="I33" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="J33" s="28" t="n"/>
-      <c r="K33" s="28" t="n"/>
-      <c r="L33" s="29" t="inlineStr">
+      <c r="J33" s="37" t="n"/>
+      <c r="K33" s="37" t="n"/>
+      <c r="L33" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="M33" s="21" t="n"/>
-      <c r="N33" s="21" t="n"/>
-      <c r="O33" s="21" t="n"/>
-      <c r="P33" s="21" t="n"/>
-      <c r="Q33" s="21" t="n"/>
-      <c r="R33" s="21" t="n"/>
-      <c r="S33" s="21" t="n"/>
-      <c r="T33" s="21" t="n"/>
-      <c r="U33" s="21" t="n"/>
-      <c r="V33" s="21" t="n"/>
-      <c r="W33" s="21" t="n"/>
-      <c r="X33" s="21" t="n"/>
-      <c r="Y33" s="27" t="inlineStr">
+      <c r="M33" s="29" t="n"/>
+      <c r="N33" s="29" t="n"/>
+      <c r="O33" s="29" t="n"/>
+      <c r="P33" s="29" t="n"/>
+      <c r="Q33" s="29" t="n"/>
+      <c r="R33" s="29" t="n"/>
+      <c r="S33" s="29" t="n"/>
+      <c r="T33" s="29" t="n"/>
+      <c r="U33" s="29" t="n"/>
+      <c r="V33" s="29" t="n"/>
+      <c r="W33" s="29" t="n"/>
+      <c r="X33" s="29" t="n"/>
+      <c r="Y33" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="Z33" s="28" t="n"/>
-      <c r="AA33" s="28" t="n"/>
-      <c r="AB33" s="29" t="inlineStr">
+      <c r="Z33" s="37" t="n"/>
+      <c r="AA33" s="37" t="n"/>
+      <c r="AB33" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="AC33" s="21" t="n"/>
-      <c r="AD33" s="21" t="n"/>
-      <c r="AE33" s="21" t="n"/>
-      <c r="AF33" s="21" t="n"/>
-      <c r="AG33" s="25" t="inlineStr">
-        <is>
-          <t>J1</t>
-        </is>
+      <c r="AC33" s="29" t="n"/>
+      <c r="AD33" s="29" t="n"/>
+      <c r="AE33" s="29" t="n"/>
+      <c r="AF33" s="29" t="n"/>
+      <c r="AG33" s="33">
+        <f>'Clasificados'!$B$13</f>
+        <v/>
       </c>
       <c r="AH33" s="10" t="n"/>
       <c r="AI33" s="10" t="n"/>
-      <c r="AJ33" s="26" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
+      <c r="AJ33" s="34">
+        <f>'Clasificados'!$C$11</f>
+        <v/>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1">
-      <c r="A34" s="27" t="inlineStr">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="B34" s="28" t="n"/>
-      <c r="C34" s="28" t="n"/>
-      <c r="D34" s="29" t="inlineStr">
+      <c r="B34" s="37" t="n"/>
+      <c r="C34" s="37" t="n"/>
+      <c r="D34" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="E34" s="21" t="n"/>
-      <c r="F34" s="21" t="n"/>
-      <c r="G34" s="21" t="n"/>
-      <c r="H34" s="21" t="n"/>
-      <c r="I34" s="21" t="n"/>
-      <c r="J34" s="21" t="n"/>
-      <c r="K34" s="21" t="n"/>
-      <c r="L34" s="21" t="n"/>
-      <c r="M34" s="21" t="n"/>
-      <c r="N34" s="21" t="n"/>
-      <c r="O34" s="21" t="n"/>
-      <c r="P34" s="21" t="n"/>
-      <c r="Q34" s="21" t="n"/>
-      <c r="R34" s="21" t="n"/>
-      <c r="S34" s="21" t="n"/>
-      <c r="T34" s="21" t="n"/>
-      <c r="U34" s="21" t="n"/>
-      <c r="V34" s="21" t="n"/>
-      <c r="W34" s="21" t="n"/>
-      <c r="X34" s="21" t="n"/>
-      <c r="Y34" s="21" t="n"/>
-      <c r="Z34" s="21" t="n"/>
-      <c r="AA34" s="21" t="n"/>
-      <c r="AB34" s="21" t="n"/>
-      <c r="AC34" s="21" t="n"/>
-      <c r="AD34" s="21" t="n"/>
-      <c r="AE34" s="21" t="n"/>
-      <c r="AF34" s="21" t="n"/>
-      <c r="AG34" s="27" t="inlineStr">
+      <c r="E34" s="29" t="n"/>
+      <c r="F34" s="29" t="n"/>
+      <c r="G34" s="29" t="n"/>
+      <c r="H34" s="29" t="n"/>
+      <c r="I34" s="29" t="n"/>
+      <c r="J34" s="29" t="n"/>
+      <c r="K34" s="29" t="n"/>
+      <c r="L34" s="29" t="n"/>
+      <c r="M34" s="29" t="n"/>
+      <c r="N34" s="29" t="n"/>
+      <c r="O34" s="29" t="n"/>
+      <c r="P34" s="29" t="n"/>
+      <c r="Q34" s="29" t="n"/>
+      <c r="R34" s="29" t="n"/>
+      <c r="S34" s="29" t="n"/>
+      <c r="T34" s="29" t="n"/>
+      <c r="U34" s="29" t="n"/>
+      <c r="V34" s="29" t="n"/>
+      <c r="W34" s="29" t="n"/>
+      <c r="X34" s="29" t="n"/>
+      <c r="Y34" s="29" t="n"/>
+      <c r="Z34" s="29" t="n"/>
+      <c r="AA34" s="29" t="n"/>
+      <c r="AB34" s="29" t="n"/>
+      <c r="AC34" s="29" t="n"/>
+      <c r="AD34" s="29" t="n"/>
+      <c r="AE34" s="29" t="n"/>
+      <c r="AF34" s="29" t="n"/>
+      <c r="AG34" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="AH34" s="28" t="n"/>
-      <c r="AI34" s="28" t="n"/>
-      <c r="AJ34" s="29" t="inlineStr">
+      <c r="AH34" s="37" t="n"/>
+      <c r="AI34" s="37" t="n"/>
+      <c r="AJ34" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
     </row>
     <row r="35" ht="13" customHeight="1">
-      <c r="A35" s="21" t="n"/>
-      <c r="B35" s="21" t="n"/>
-      <c r="C35" s="21" t="n"/>
-      <c r="D35" s="21" t="n"/>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="A35" s="29" t="n"/>
+      <c r="B35" s="29" t="n"/>
+      <c r="C35" s="29" t="n"/>
+      <c r="D35" s="29" t="n"/>
+      <c r="E35" s="32" t="inlineStr">
         <is>
           <t>Jul 5  ·  Mexico City</t>
         </is>
       </c>
-      <c r="I35" s="21" t="n"/>
-      <c r="J35" s="21" t="n"/>
-      <c r="K35" s="21" t="n"/>
-      <c r="L35" s="21" t="n"/>
-      <c r="M35" s="21" t="n"/>
-      <c r="N35" s="21" t="n"/>
-      <c r="O35" s="21" t="n"/>
-      <c r="P35" s="21" t="n"/>
-      <c r="Q35" s="21" t="n"/>
-      <c r="R35" s="21" t="n"/>
-      <c r="S35" s="21" t="n"/>
-      <c r="T35" s="21" t="n"/>
-      <c r="U35" s="21" t="n"/>
-      <c r="V35" s="21" t="n"/>
-      <c r="W35" s="21" t="n"/>
-      <c r="X35" s="21" t="n"/>
-      <c r="Y35" s="21" t="n"/>
-      <c r="Z35" s="21" t="n"/>
-      <c r="AA35" s="21" t="n"/>
-      <c r="AB35" s="21" t="n"/>
-      <c r="AC35" s="24" t="inlineStr">
+      <c r="I35" s="29" t="n"/>
+      <c r="J35" s="29" t="n"/>
+      <c r="K35" s="29" t="n"/>
+      <c r="L35" s="29" t="n"/>
+      <c r="M35" s="29" t="n"/>
+      <c r="N35" s="29" t="n"/>
+      <c r="O35" s="29" t="n"/>
+      <c r="P35" s="29" t="n"/>
+      <c r="Q35" s="29" t="n"/>
+      <c r="R35" s="29" t="n"/>
+      <c r="S35" s="29" t="n"/>
+      <c r="T35" s="29" t="n"/>
+      <c r="U35" s="29" t="n"/>
+      <c r="V35" s="29" t="n"/>
+      <c r="W35" s="29" t="n"/>
+      <c r="X35" s="29" t="n"/>
+      <c r="Y35" s="29" t="n"/>
+      <c r="Z35" s="29" t="n"/>
+      <c r="AA35" s="29" t="n"/>
+      <c r="AB35" s="29" t="n"/>
+      <c r="AC35" s="32" t="inlineStr">
         <is>
           <t>Jul 7  ·  Vancouver</t>
         </is>
       </c>
-      <c r="AG35" s="21" t="n"/>
-      <c r="AH35" s="21" t="n"/>
-      <c r="AI35" s="21" t="n"/>
-      <c r="AJ35" s="21" t="n"/>
+      <c r="AG35" s="29" t="n"/>
+      <c r="AH35" s="29" t="n"/>
+      <c r="AI35" s="29" t="n"/>
+      <c r="AJ35" s="29" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="24" t="inlineStr">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>Jul 1  ·  Atlanta</t>
         </is>
       </c>
-      <c r="E36" s="25" t="inlineStr">
-        <is>
-          <t>W R32 #7</t>
-        </is>
+      <c r="E36" s="33">
+        <f>IF(AND($B$33&lt;&gt;"",$C$33&lt;&gt;""),IF($B$33&gt;$C$33,$A$33,IF($C$33&gt;$B$33,$D$33,IF(AND($B$34&lt;&gt;"",$C$34&lt;&gt;""),IF($B$34&gt;$C$34,$A$33,$D$33),"TBD"))),"—")</f>
+        <v/>
       </c>
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="10" t="n"/>
-      <c r="H36" s="26" t="inlineStr">
-        <is>
-          <t>W R32 #8</t>
-        </is>
-      </c>
-      <c r="I36" s="21" t="n"/>
-      <c r="J36" s="21" t="n"/>
-      <c r="K36" s="21" t="n"/>
-      <c r="L36" s="21" t="n"/>
-      <c r="M36" s="21" t="n"/>
-      <c r="N36" s="21" t="n"/>
-      <c r="O36" s="21" t="n"/>
-      <c r="P36" s="21" t="n"/>
-      <c r="Q36" s="21" t="n"/>
-      <c r="R36" s="21" t="n"/>
-      <c r="S36" s="21" t="n"/>
-      <c r="T36" s="21" t="n"/>
-      <c r="U36" s="21" t="n"/>
-      <c r="V36" s="21" t="n"/>
-      <c r="W36" s="21" t="n"/>
-      <c r="X36" s="21" t="n"/>
-      <c r="Y36" s="21" t="n"/>
-      <c r="Z36" s="21" t="n"/>
-      <c r="AA36" s="21" t="n"/>
-      <c r="AB36" s="21" t="n"/>
-      <c r="AC36" s="25" t="inlineStr">
-        <is>
-          <t>W R32 #15</t>
-        </is>
+      <c r="H36" s="34">
+        <f>IF(AND($B$37&lt;&gt;"",$C$37&lt;&gt;""),IF($B$37&gt;$C$37,$A$37,IF($C$37&gt;$B$37,$D$37,IF(AND($B$38&lt;&gt;"",$C$38&lt;&gt;""),IF($B$38&gt;$C$38,$A$37,$D$37),"TBD"))),"—")</f>
+        <v/>
+      </c>
+      <c r="I36" s="29" t="n"/>
+      <c r="J36" s="29" t="n"/>
+      <c r="K36" s="29" t="n"/>
+      <c r="L36" s="29" t="n"/>
+      <c r="M36" s="29" t="n"/>
+      <c r="N36" s="29" t="n"/>
+      <c r="O36" s="29" t="n"/>
+      <c r="P36" s="29" t="n"/>
+      <c r="Q36" s="29" t="n"/>
+      <c r="R36" s="29" t="n"/>
+      <c r="S36" s="29" t="n"/>
+      <c r="T36" s="29" t="n"/>
+      <c r="U36" s="29" t="n"/>
+      <c r="V36" s="29" t="n"/>
+      <c r="W36" s="29" t="n"/>
+      <c r="X36" s="29" t="n"/>
+      <c r="Y36" s="29" t="n"/>
+      <c r="Z36" s="29" t="n"/>
+      <c r="AA36" s="29" t="n"/>
+      <c r="AB36" s="29" t="n"/>
+      <c r="AC36" s="33">
+        <f>IF(AND($AH$33&lt;&gt;"",$AI$33&lt;&gt;""),IF($AH$33&gt;$AI$33,$AG$33,IF($AI$33&gt;$AH$33,$AJ$33,IF(AND($AH$34&lt;&gt;"",$AI$34&lt;&gt;""),IF($AH$34&gt;$AI$34,$AG$33,$AJ$33),"TBD"))),"—")</f>
+        <v/>
       </c>
       <c r="AD36" s="10" t="n"/>
       <c r="AE36" s="10" t="n"/>
-      <c r="AF36" s="26" t="inlineStr">
-        <is>
-          <t>W R32 #16</t>
-        </is>
-      </c>
-      <c r="AG36" s="24" t="inlineStr">
+      <c r="AF36" s="34">
+        <f>IF(AND($AH$37&lt;&gt;"",$AI$37&lt;&gt;""),IF($AH$37&gt;$AI$37,$AG$37,IF($AI$37&gt;$AH$37,$AJ$37,IF(AND($AH$38&lt;&gt;"",$AI$38&lt;&gt;""),IF($AH$38&gt;$AI$38,$AG$37,$AJ$37),"TBD"))),"—")</f>
+        <v/>
+      </c>
+      <c r="AG36" s="32" t="inlineStr">
         <is>
           <t>Jul 3  ·  Kansas City</t>
         </is>
       </c>
     </row>
     <row r="37" ht="14" customHeight="1">
-      <c r="A37" s="25" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
+      <c r="A37" s="33">
+        <f>'Clasificados'!$B$15</f>
+        <v/>
       </c>
       <c r="B37" s="10" t="n"/>
       <c r="C37" s="10" t="n"/>
-      <c r="D37" s="26" t="inlineStr">
-        <is>
-          <t>3rd*</t>
-        </is>
-      </c>
-      <c r="E37" s="27" t="inlineStr">
+      <c r="D37" s="35" t="inlineStr">
+        <is>
+          <t>◀ Enter 3rd</t>
+        </is>
+      </c>
+      <c r="E37" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="F37" s="28" t="n"/>
-      <c r="G37" s="28" t="n"/>
-      <c r="H37" s="29" t="inlineStr">
+      <c r="F37" s="37" t="n"/>
+      <c r="G37" s="37" t="n"/>
+      <c r="H37" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="I37" s="21" t="n"/>
-      <c r="J37" s="21" t="n"/>
-      <c r="K37" s="21" t="n"/>
-      <c r="L37" s="21" t="n"/>
-      <c r="M37" s="21" t="n"/>
-      <c r="N37" s="21" t="n"/>
-      <c r="O37" s="21" t="n"/>
-      <c r="P37" s="21" t="n"/>
-      <c r="Q37" s="21" t="n"/>
-      <c r="R37" s="21" t="n"/>
-      <c r="S37" s="21" t="n"/>
-      <c r="T37" s="21" t="n"/>
-      <c r="U37" s="21" t="n"/>
-      <c r="V37" s="21" t="n"/>
-      <c r="W37" s="21" t="n"/>
-      <c r="X37" s="21" t="n"/>
-      <c r="Y37" s="21" t="n"/>
-      <c r="Z37" s="21" t="n"/>
-      <c r="AA37" s="21" t="n"/>
-      <c r="AB37" s="21" t="n"/>
-      <c r="AC37" s="27" t="inlineStr">
+      <c r="I37" s="29" t="n"/>
+      <c r="J37" s="29" t="n"/>
+      <c r="K37" s="29" t="n"/>
+      <c r="L37" s="29" t="n"/>
+      <c r="M37" s="29" t="n"/>
+      <c r="N37" s="29" t="n"/>
+      <c r="O37" s="29" t="n"/>
+      <c r="P37" s="29" t="n"/>
+      <c r="Q37" s="29" t="n"/>
+      <c r="R37" s="29" t="n"/>
+      <c r="S37" s="29" t="n"/>
+      <c r="T37" s="29" t="n"/>
+      <c r="U37" s="29" t="n"/>
+      <c r="V37" s="29" t="n"/>
+      <c r="W37" s="29" t="n"/>
+      <c r="X37" s="29" t="n"/>
+      <c r="Y37" s="29" t="n"/>
+      <c r="Z37" s="29" t="n"/>
+      <c r="AA37" s="29" t="n"/>
+      <c r="AB37" s="29" t="n"/>
+      <c r="AC37" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="AD37" s="28" t="n"/>
-      <c r="AE37" s="28" t="n"/>
-      <c r="AF37" s="29" t="inlineStr">
+      <c r="AD37" s="37" t="n"/>
+      <c r="AE37" s="37" t="n"/>
+      <c r="AF37" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="AG37" s="25" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
+      <c r="AG37" s="33">
+        <f>'Clasificados'!$B$14</f>
+        <v/>
       </c>
       <c r="AH37" s="10" t="n"/>
       <c r="AI37" s="10" t="n"/>
-      <c r="AJ37" s="26" t="inlineStr">
-        <is>
-          <t>3rd*</t>
+      <c r="AJ37" s="35" t="inlineStr">
+        <is>
+          <t>◀ Enter 3rd</t>
         </is>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
-      <c r="A38" s="27" t="inlineStr">
+      <c r="A38" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="B38" s="28" t="n"/>
-      <c r="C38" s="28" t="n"/>
-      <c r="D38" s="29" t="inlineStr">
+      <c r="B38" s="37" t="n"/>
+      <c r="C38" s="37" t="n"/>
+      <c r="D38" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="E38" s="21" t="n"/>
-      <c r="F38" s="21" t="n"/>
-      <c r="G38" s="21" t="n"/>
-      <c r="H38" s="21" t="n"/>
-      <c r="I38" s="21" t="n"/>
-      <c r="J38" s="21" t="n"/>
-      <c r="K38" s="21" t="n"/>
-      <c r="L38" s="21" t="n"/>
-      <c r="M38" s="21" t="n"/>
-      <c r="N38" s="21" t="n"/>
-      <c r="O38" s="21" t="n"/>
-      <c r="P38" s="21" t="n"/>
-      <c r="Q38" s="21" t="n"/>
-      <c r="R38" s="21" t="n"/>
-      <c r="S38" s="21" t="n"/>
-      <c r="T38" s="21" t="n"/>
-      <c r="U38" s="21" t="n"/>
-      <c r="V38" s="21" t="n"/>
-      <c r="W38" s="21" t="n"/>
-      <c r="X38" s="21" t="n"/>
-      <c r="Y38" s="21" t="n"/>
-      <c r="Z38" s="21" t="n"/>
-      <c r="AA38" s="21" t="n"/>
-      <c r="AB38" s="21" t="n"/>
-      <c r="AC38" s="21" t="n"/>
-      <c r="AD38" s="21" t="n"/>
-      <c r="AE38" s="21" t="n"/>
-      <c r="AF38" s="21" t="n"/>
-      <c r="AG38" s="27" t="inlineStr">
+      <c r="E38" s="29" t="n"/>
+      <c r="F38" s="29" t="n"/>
+      <c r="G38" s="29" t="n"/>
+      <c r="H38" s="29" t="n"/>
+      <c r="I38" s="29" t="n"/>
+      <c r="J38" s="29" t="n"/>
+      <c r="K38" s="29" t="n"/>
+      <c r="L38" s="29" t="n"/>
+      <c r="M38" s="29" t="n"/>
+      <c r="N38" s="29" t="n"/>
+      <c r="O38" s="29" t="n"/>
+      <c r="P38" s="29" t="n"/>
+      <c r="Q38" s="29" t="n"/>
+      <c r="R38" s="29" t="n"/>
+      <c r="S38" s="29" t="n"/>
+      <c r="T38" s="29" t="n"/>
+      <c r="U38" s="29" t="n"/>
+      <c r="V38" s="29" t="n"/>
+      <c r="W38" s="29" t="n"/>
+      <c r="X38" s="29" t="n"/>
+      <c r="Y38" s="29" t="n"/>
+      <c r="Z38" s="29" t="n"/>
+      <c r="AA38" s="29" t="n"/>
+      <c r="AB38" s="29" t="n"/>
+      <c r="AC38" s="29" t="n"/>
+      <c r="AD38" s="29" t="n"/>
+      <c r="AE38" s="29" t="n"/>
+      <c r="AF38" s="29" t="n"/>
+      <c r="AG38" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="AH38" s="28" t="n"/>
-      <c r="AI38" s="28" t="n"/>
-      <c r="AJ38" s="29" t="inlineStr">
+      <c r="AH38" s="37" t="n"/>
+      <c r="AI38" s="37" t="n"/>
+      <c r="AJ38" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="21" t="n"/>
-      <c r="B39" s="21" t="n"/>
-      <c r="C39" s="21" t="n"/>
-      <c r="D39" s="21" t="n"/>
-      <c r="E39" s="21" t="n"/>
-      <c r="F39" s="21" t="n"/>
-      <c r="G39" s="21" t="n"/>
-      <c r="H39" s="21" t="n"/>
-      <c r="I39" s="21" t="n"/>
-      <c r="J39" s="21" t="n"/>
-      <c r="K39" s="21" t="n"/>
-      <c r="L39" s="21" t="n"/>
-      <c r="M39" s="21" t="n"/>
-      <c r="N39" s="21" t="n"/>
-      <c r="O39" s="21" t="n"/>
-      <c r="P39" s="21" t="n"/>
-      <c r="Q39" s="21" t="n"/>
-      <c r="R39" s="21" t="n"/>
-      <c r="S39" s="21" t="n"/>
-      <c r="T39" s="21" t="n"/>
-      <c r="U39" s="21" t="n"/>
-      <c r="V39" s="21" t="n"/>
-      <c r="W39" s="21" t="n"/>
-      <c r="X39" s="21" t="n"/>
-      <c r="Y39" s="21" t="n"/>
-      <c r="Z39" s="21" t="n"/>
-      <c r="AA39" s="21" t="n"/>
-      <c r="AB39" s="21" t="n"/>
-      <c r="AC39" s="21" t="n"/>
-      <c r="AD39" s="21" t="n"/>
-      <c r="AE39" s="21" t="n"/>
-      <c r="AF39" s="21" t="n"/>
-      <c r="AG39" s="21" t="n"/>
-      <c r="AH39" s="21" t="n"/>
-      <c r="AI39" s="21" t="n"/>
-      <c r="AJ39" s="21" t="n"/>
+      <c r="A39" s="29" t="n"/>
+      <c r="B39" s="29" t="n"/>
+      <c r="C39" s="29" t="n"/>
+      <c r="D39" s="29" t="n"/>
+      <c r="E39" s="29" t="n"/>
+      <c r="F39" s="29" t="n"/>
+      <c r="G39" s="29" t="n"/>
+      <c r="H39" s="29" t="n"/>
+      <c r="I39" s="29" t="n"/>
+      <c r="J39" s="29" t="n"/>
+      <c r="K39" s="29" t="n"/>
+      <c r="L39" s="29" t="n"/>
+      <c r="M39" s="29" t="n"/>
+      <c r="N39" s="29" t="n"/>
+      <c r="O39" s="29" t="n"/>
+      <c r="P39" s="29" t="n"/>
+      <c r="Q39" s="29" t="n"/>
+      <c r="R39" s="29" t="n"/>
+      <c r="S39" s="29" t="n"/>
+      <c r="T39" s="29" t="n"/>
+      <c r="U39" s="29" t="n"/>
+      <c r="V39" s="29" t="n"/>
+      <c r="W39" s="29" t="n"/>
+      <c r="X39" s="29" t="n"/>
+      <c r="Y39" s="29" t="n"/>
+      <c r="Z39" s="29" t="n"/>
+      <c r="AA39" s="29" t="n"/>
+      <c r="AB39" s="29" t="n"/>
+      <c r="AC39" s="29" t="n"/>
+      <c r="AD39" s="29" t="n"/>
+      <c r="AE39" s="29" t="n"/>
+      <c r="AF39" s="29" t="n"/>
+      <c r="AG39" s="29" t="n"/>
+      <c r="AH39" s="29" t="n"/>
+      <c r="AI39" s="29" t="n"/>
+      <c r="AJ39" s="29" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="21" t="n"/>
-      <c r="B40" s="21" t="n"/>
-      <c r="C40" s="21" t="n"/>
-      <c r="D40" s="21" t="n"/>
-      <c r="E40" s="21" t="n"/>
-      <c r="F40" s="21" t="n"/>
-      <c r="G40" s="21" t="n"/>
-      <c r="H40" s="21" t="n"/>
-      <c r="I40" s="21" t="n"/>
-      <c r="J40" s="21" t="n"/>
-      <c r="K40" s="21" t="n"/>
-      <c r="L40" s="21" t="n"/>
-      <c r="M40" s="21" t="n"/>
-      <c r="N40" s="21" t="n"/>
-      <c r="O40" s="21" t="n"/>
-      <c r="P40" s="21" t="n"/>
-      <c r="Q40" s="21" t="n"/>
-      <c r="R40" s="21" t="n"/>
-      <c r="S40" s="21" t="n"/>
-      <c r="T40" s="21" t="n"/>
-      <c r="U40" s="21" t="n"/>
-      <c r="V40" s="21" t="n"/>
-      <c r="W40" s="21" t="n"/>
-      <c r="X40" s="21" t="n"/>
-      <c r="Y40" s="21" t="n"/>
-      <c r="Z40" s="21" t="n"/>
-      <c r="AA40" s="21" t="n"/>
-      <c r="AB40" s="21" t="n"/>
-      <c r="AC40" s="21" t="n"/>
-      <c r="AD40" s="21" t="n"/>
-      <c r="AE40" s="21" t="n"/>
-      <c r="AF40" s="21" t="n"/>
-      <c r="AG40" s="21" t="n"/>
-      <c r="AH40" s="21" t="n"/>
-      <c r="AI40" s="21" t="n"/>
-      <c r="AJ40" s="21" t="n"/>
+      <c r="A40" s="29" t="n"/>
+      <c r="B40" s="29" t="n"/>
+      <c r="C40" s="29" t="n"/>
+      <c r="D40" s="29" t="n"/>
+      <c r="E40" s="29" t="n"/>
+      <c r="F40" s="29" t="n"/>
+      <c r="G40" s="29" t="n"/>
+      <c r="H40" s="29" t="n"/>
+      <c r="I40" s="29" t="n"/>
+      <c r="J40" s="29" t="n"/>
+      <c r="K40" s="29" t="n"/>
+      <c r="L40" s="29" t="n"/>
+      <c r="M40" s="29" t="n"/>
+      <c r="N40" s="29" t="n"/>
+      <c r="O40" s="29" t="n"/>
+      <c r="P40" s="29" t="n"/>
+      <c r="Q40" s="29" t="n"/>
+      <c r="R40" s="29" t="n"/>
+      <c r="S40" s="29" t="n"/>
+      <c r="T40" s="29" t="n"/>
+      <c r="U40" s="29" t="n"/>
+      <c r="V40" s="29" t="n"/>
+      <c r="W40" s="29" t="n"/>
+      <c r="X40" s="29" t="n"/>
+      <c r="Y40" s="29" t="n"/>
+      <c r="Z40" s="29" t="n"/>
+      <c r="AA40" s="29" t="n"/>
+      <c r="AB40" s="29" t="n"/>
+      <c r="AC40" s="29" t="n"/>
+      <c r="AD40" s="29" t="n"/>
+      <c r="AE40" s="29" t="n"/>
+      <c r="AF40" s="29" t="n"/>
+      <c r="AG40" s="29" t="n"/>
+      <c r="AH40" s="29" t="n"/>
+      <c r="AI40" s="29" t="n"/>
+      <c r="AJ40" s="29" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="21" t="n"/>
-      <c r="B41" s="21" t="n"/>
-      <c r="C41" s="21" t="n"/>
-      <c r="D41" s="21" t="n"/>
-      <c r="E41" s="21" t="n"/>
-      <c r="F41" s="21" t="n"/>
-      <c r="G41" s="21" t="n"/>
-      <c r="H41" s="21" t="n"/>
-      <c r="I41" s="21" t="n"/>
-      <c r="J41" s="21" t="n"/>
-      <c r="K41" s="21" t="n"/>
-      <c r="L41" s="21" t="n"/>
-      <c r="M41" s="21" t="n"/>
-      <c r="N41" s="21" t="n"/>
-      <c r="O41" s="21" t="n"/>
-      <c r="P41" s="21" t="n"/>
-      <c r="Q41" s="21" t="n"/>
-      <c r="R41" s="21" t="n"/>
-      <c r="S41" s="21" t="n"/>
-      <c r="T41" s="21" t="n"/>
-      <c r="U41" s="21" t="n"/>
-      <c r="V41" s="21" t="n"/>
-      <c r="W41" s="21" t="n"/>
-      <c r="X41" s="21" t="n"/>
-      <c r="Y41" s="21" t="n"/>
-      <c r="Z41" s="21" t="n"/>
-      <c r="AA41" s="21" t="n"/>
-      <c r="AB41" s="21" t="n"/>
-      <c r="AC41" s="21" t="n"/>
-      <c r="AD41" s="21" t="n"/>
-      <c r="AE41" s="21" t="n"/>
-      <c r="AF41" s="21" t="n"/>
-      <c r="AG41" s="21" t="n"/>
-      <c r="AH41" s="21" t="n"/>
-      <c r="AI41" s="21" t="n"/>
-      <c r="AJ41" s="21" t="n"/>
+      <c r="A41" s="29" t="n"/>
+      <c r="B41" s="29" t="n"/>
+      <c r="C41" s="29" t="n"/>
+      <c r="D41" s="29" t="n"/>
+      <c r="E41" s="29" t="n"/>
+      <c r="F41" s="29" t="n"/>
+      <c r="G41" s="29" t="n"/>
+      <c r="H41" s="29" t="n"/>
+      <c r="I41" s="29" t="n"/>
+      <c r="J41" s="29" t="n"/>
+      <c r="K41" s="29" t="n"/>
+      <c r="L41" s="29" t="n"/>
+      <c r="M41" s="29" t="n"/>
+      <c r="N41" s="29" t="n"/>
+      <c r="O41" s="29" t="n"/>
+      <c r="P41" s="29" t="n"/>
+      <c r="Q41" s="29" t="n"/>
+      <c r="R41" s="29" t="n"/>
+      <c r="S41" s="29" t="n"/>
+      <c r="T41" s="29" t="n"/>
+      <c r="U41" s="29" t="n"/>
+      <c r="V41" s="29" t="n"/>
+      <c r="W41" s="29" t="n"/>
+      <c r="X41" s="29" t="n"/>
+      <c r="Y41" s="29" t="n"/>
+      <c r="Z41" s="29" t="n"/>
+      <c r="AA41" s="29" t="n"/>
+      <c r="AB41" s="29" t="n"/>
+      <c r="AC41" s="29" t="n"/>
+      <c r="AD41" s="29" t="n"/>
+      <c r="AE41" s="29" t="n"/>
+      <c r="AF41" s="29" t="n"/>
+      <c r="AG41" s="29" t="n"/>
+      <c r="AH41" s="29" t="n"/>
+      <c r="AI41" s="29" t="n"/>
+      <c r="AJ41" s="29" t="n"/>
     </row>
     <row r="42" ht="14" customHeight="1">
-      <c r="A42" s="21" t="n"/>
-      <c r="B42" s="21" t="n"/>
-      <c r="C42" s="21" t="n"/>
-      <c r="D42" s="21" t="n"/>
-      <c r="E42" s="21" t="n"/>
-      <c r="F42" s="21" t="n"/>
-      <c r="G42" s="21" t="n"/>
-      <c r="H42" s="21" t="n"/>
-      <c r="I42" s="21" t="n"/>
-      <c r="J42" s="21" t="n"/>
-      <c r="K42" s="21" t="n"/>
-      <c r="L42" s="21" t="n"/>
-      <c r="M42" s="21" t="n"/>
-      <c r="N42" s="21" t="n"/>
-      <c r="O42" s="21" t="n"/>
-      <c r="P42" s="21" t="n"/>
-      <c r="Q42" s="35" t="inlineStr">
+      <c r="A42" s="29" t="n"/>
+      <c r="B42" s="29" t="n"/>
+      <c r="C42" s="29" t="n"/>
+      <c r="D42" s="29" t="n"/>
+      <c r="E42" s="29" t="n"/>
+      <c r="F42" s="29" t="n"/>
+      <c r="G42" s="29" t="n"/>
+      <c r="H42" s="29" t="n"/>
+      <c r="I42" s="29" t="n"/>
+      <c r="J42" s="29" t="n"/>
+      <c r="K42" s="29" t="n"/>
+      <c r="L42" s="29" t="n"/>
+      <c r="M42" s="29" t="n"/>
+      <c r="N42" s="29" t="n"/>
+      <c r="O42" s="29" t="n"/>
+      <c r="P42" s="29" t="n"/>
+      <c r="Q42" s="44" t="inlineStr">
         <is>
           <t>THIRD PLACE MATCH</t>
         </is>
       </c>
-      <c r="U42" s="21" t="n"/>
-      <c r="V42" s="21" t="n"/>
-      <c r="W42" s="21" t="n"/>
-      <c r="X42" s="21" t="n"/>
-      <c r="Y42" s="21" t="n"/>
-      <c r="Z42" s="21" t="n"/>
-      <c r="AA42" s="21" t="n"/>
-      <c r="AB42" s="21" t="n"/>
-      <c r="AC42" s="21" t="n"/>
-      <c r="AD42" s="21" t="n"/>
-      <c r="AE42" s="21" t="n"/>
-      <c r="AF42" s="21" t="n"/>
-      <c r="AG42" s="21" t="n"/>
-      <c r="AH42" s="21" t="n"/>
-      <c r="AI42" s="21" t="n"/>
-      <c r="AJ42" s="21" t="n"/>
+      <c r="U42" s="29" t="n"/>
+      <c r="V42" s="29" t="n"/>
+      <c r="W42" s="29" t="n"/>
+      <c r="X42" s="29" t="n"/>
+      <c r="Y42" s="29" t="n"/>
+      <c r="Z42" s="29" t="n"/>
+      <c r="AA42" s="29" t="n"/>
+      <c r="AB42" s="29" t="n"/>
+      <c r="AC42" s="29" t="n"/>
+      <c r="AD42" s="29" t="n"/>
+      <c r="AE42" s="29" t="n"/>
+      <c r="AF42" s="29" t="n"/>
+      <c r="AG42" s="29" t="n"/>
+      <c r="AH42" s="29" t="n"/>
+      <c r="AI42" s="29" t="n"/>
+      <c r="AJ42" s="29" t="n"/>
     </row>
     <row r="43" ht="13" customHeight="1">
-      <c r="A43" s="21" t="n"/>
-      <c r="B43" s="21" t="n"/>
-      <c r="C43" s="21" t="n"/>
-      <c r="D43" s="21" t="n"/>
-      <c r="E43" s="21" t="n"/>
-      <c r="F43" s="21" t="n"/>
-      <c r="G43" s="21" t="n"/>
-      <c r="H43" s="21" t="n"/>
-      <c r="I43" s="21" t="n"/>
-      <c r="J43" s="21" t="n"/>
-      <c r="K43" s="21" t="n"/>
-      <c r="L43" s="21" t="n"/>
-      <c r="M43" s="21" t="n"/>
-      <c r="N43" s="21" t="n"/>
-      <c r="O43" s="21" t="n"/>
-      <c r="P43" s="21" t="n"/>
-      <c r="Q43" s="24" t="inlineStr">
+      <c r="A43" s="29" t="n"/>
+      <c r="B43" s="29" t="n"/>
+      <c r="C43" s="29" t="n"/>
+      <c r="D43" s="29" t="n"/>
+      <c r="E43" s="29" t="n"/>
+      <c r="F43" s="29" t="n"/>
+      <c r="G43" s="29" t="n"/>
+      <c r="H43" s="29" t="n"/>
+      <c r="I43" s="29" t="n"/>
+      <c r="J43" s="29" t="n"/>
+      <c r="K43" s="29" t="n"/>
+      <c r="L43" s="29" t="n"/>
+      <c r="M43" s="29" t="n"/>
+      <c r="N43" s="29" t="n"/>
+      <c r="O43" s="29" t="n"/>
+      <c r="P43" s="29" t="n"/>
+      <c r="Q43" s="32" t="inlineStr">
         <is>
           <t>Jul 18  ·  Miami</t>
         </is>
       </c>
-      <c r="U43" s="21" t="n"/>
-      <c r="V43" s="21" t="n"/>
-      <c r="W43" s="21" t="n"/>
-      <c r="X43" s="21" t="n"/>
-      <c r="Y43" s="21" t="n"/>
-      <c r="Z43" s="21" t="n"/>
-      <c r="AA43" s="21" t="n"/>
-      <c r="AB43" s="21" t="n"/>
-      <c r="AC43" s="21" t="n"/>
-      <c r="AD43" s="21" t="n"/>
-      <c r="AE43" s="21" t="n"/>
-      <c r="AF43" s="21" t="n"/>
-      <c r="AG43" s="21" t="n"/>
-      <c r="AH43" s="21" t="n"/>
-      <c r="AI43" s="21" t="n"/>
-      <c r="AJ43" s="21" t="n"/>
+      <c r="U43" s="29" t="n"/>
+      <c r="V43" s="29" t="n"/>
+      <c r="W43" s="29" t="n"/>
+      <c r="X43" s="29" t="n"/>
+      <c r="Y43" s="29" t="n"/>
+      <c r="Z43" s="29" t="n"/>
+      <c r="AA43" s="29" t="n"/>
+      <c r="AB43" s="29" t="n"/>
+      <c r="AC43" s="29" t="n"/>
+      <c r="AD43" s="29" t="n"/>
+      <c r="AE43" s="29" t="n"/>
+      <c r="AF43" s="29" t="n"/>
+      <c r="AG43" s="29" t="n"/>
+      <c r="AH43" s="29" t="n"/>
+      <c r="AI43" s="29" t="n"/>
+      <c r="AJ43" s="29" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="21" t="n"/>
-      <c r="B44" s="21" t="n"/>
-      <c r="C44" s="21" t="n"/>
-      <c r="D44" s="21" t="n"/>
-      <c r="E44" s="21" t="n"/>
-      <c r="F44" s="21" t="n"/>
-      <c r="G44" s="21" t="n"/>
-      <c r="H44" s="21" t="n"/>
-      <c r="I44" s="21" t="n"/>
-      <c r="J44" s="21" t="n"/>
-      <c r="K44" s="21" t="n"/>
-      <c r="L44" s="21" t="n"/>
-      <c r="M44" s="21" t="n"/>
-      <c r="N44" s="21" t="n"/>
-      <c r="O44" s="21" t="n"/>
-      <c r="P44" s="21" t="n"/>
-      <c r="Q44" s="25" t="inlineStr">
-        <is>
-          <t>L SF-L</t>
-        </is>
+      <c r="A44" s="29" t="n"/>
+      <c r="B44" s="29" t="n"/>
+      <c r="C44" s="29" t="n"/>
+      <c r="D44" s="29" t="n"/>
+      <c r="E44" s="29" t="n"/>
+      <c r="F44" s="29" t="n"/>
+      <c r="G44" s="29" t="n"/>
+      <c r="H44" s="29" t="n"/>
+      <c r="I44" s="29" t="n"/>
+      <c r="J44" s="29" t="n"/>
+      <c r="K44" s="29" t="n"/>
+      <c r="L44" s="29" t="n"/>
+      <c r="M44" s="29" t="n"/>
+      <c r="N44" s="29" t="n"/>
+      <c r="O44" s="29" t="n"/>
+      <c r="P44" s="29" t="n"/>
+      <c r="Q44" s="33">
+        <f>IF(AND($N$24&lt;&gt;"",$O$24&lt;&gt;""),IF($N$24&lt;$O$24,$M$24,IF($O$24&lt;$N$24,$P$24,IF(AND($N$25&lt;&gt;"",$O$25&lt;&gt;""),IF($N$25&lt;$O$25,$M$24,$P$24),"TBD"))),"—")</f>
+        <v/>
       </c>
       <c r="R44" s="10" t="n"/>
       <c r="S44" s="10" t="n"/>
-      <c r="T44" s="26" t="inlineStr">
-        <is>
-          <t>L SF-R</t>
-        </is>
-      </c>
-      <c r="U44" s="21" t="n"/>
-      <c r="V44" s="21" t="n"/>
-      <c r="W44" s="21" t="n"/>
-      <c r="X44" s="21" t="n"/>
-      <c r="Y44" s="21" t="n"/>
-      <c r="Z44" s="21" t="n"/>
-      <c r="AA44" s="21" t="n"/>
-      <c r="AB44" s="21" t="n"/>
-      <c r="AC44" s="21" t="n"/>
-      <c r="AD44" s="21" t="n"/>
-      <c r="AE44" s="21" t="n"/>
-      <c r="AF44" s="21" t="n"/>
-      <c r="AG44" s="21" t="n"/>
-      <c r="AH44" s="21" t="n"/>
-      <c r="AI44" s="21" t="n"/>
-      <c r="AJ44" s="21" t="n"/>
+      <c r="T44" s="34">
+        <f>IF(AND($V$24&lt;&gt;"",$W$24&lt;&gt;""),IF($V$24&lt;$W$24,$U$24,IF($W$24&lt;$V$24,$X$24,IF(AND($V$25&lt;&gt;"",$W$25&lt;&gt;""),IF($V$25&lt;$W$25,$U$24,$X$24),"TBD"))),"—")</f>
+        <v/>
+      </c>
+      <c r="U44" s="29" t="n"/>
+      <c r="V44" s="29" t="n"/>
+      <c r="W44" s="29" t="n"/>
+      <c r="X44" s="29" t="n"/>
+      <c r="Y44" s="29" t="n"/>
+      <c r="Z44" s="29" t="n"/>
+      <c r="AA44" s="29" t="n"/>
+      <c r="AB44" s="29" t="n"/>
+      <c r="AC44" s="29" t="n"/>
+      <c r="AD44" s="29" t="n"/>
+      <c r="AE44" s="29" t="n"/>
+      <c r="AF44" s="29" t="n"/>
+      <c r="AG44" s="29" t="n"/>
+      <c r="AH44" s="29" t="n"/>
+      <c r="AI44" s="29" t="n"/>
+      <c r="AJ44" s="29" t="n"/>
     </row>
     <row r="45" ht="14" customHeight="1">
-      <c r="A45" s="21" t="n"/>
-      <c r="B45" s="21" t="n"/>
-      <c r="C45" s="21" t="n"/>
-      <c r="D45" s="21" t="n"/>
-      <c r="E45" s="21" t="n"/>
-      <c r="F45" s="21" t="n"/>
-      <c r="G45" s="21" t="n"/>
-      <c r="H45" s="21" t="n"/>
-      <c r="I45" s="21" t="n"/>
-      <c r="J45" s="21" t="n"/>
-      <c r="K45" s="21" t="n"/>
-      <c r="L45" s="21" t="n"/>
-      <c r="M45" s="21" t="n"/>
-      <c r="N45" s="21" t="n"/>
-      <c r="O45" s="21" t="n"/>
-      <c r="P45" s="21" t="n"/>
-      <c r="Q45" s="27" t="inlineStr">
+      <c r="A45" s="29" t="n"/>
+      <c r="B45" s="29" t="n"/>
+      <c r="C45" s="29" t="n"/>
+      <c r="D45" s="29" t="n"/>
+      <c r="E45" s="29" t="n"/>
+      <c r="F45" s="29" t="n"/>
+      <c r="G45" s="29" t="n"/>
+      <c r="H45" s="29" t="n"/>
+      <c r="I45" s="29" t="n"/>
+      <c r="J45" s="29" t="n"/>
+      <c r="K45" s="29" t="n"/>
+      <c r="L45" s="29" t="n"/>
+      <c r="M45" s="29" t="n"/>
+      <c r="N45" s="29" t="n"/>
+      <c r="O45" s="29" t="n"/>
+      <c r="P45" s="29" t="n"/>
+      <c r="Q45" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
         </is>
       </c>
-      <c r="R45" s="28" t="n"/>
-      <c r="S45" s="28" t="n"/>
-      <c r="T45" s="29" t="inlineStr">
+      <c r="R45" s="37" t="n"/>
+      <c r="S45" s="37" t="n"/>
+      <c r="T45" s="38" t="inlineStr">
         <is>
           <t>← Pen</t>
         </is>
       </c>
-      <c r="U45" s="21" t="n"/>
-      <c r="V45" s="21" t="n"/>
-      <c r="W45" s="21" t="n"/>
-      <c r="X45" s="21" t="n"/>
-      <c r="Y45" s="21" t="n"/>
-      <c r="Z45" s="21" t="n"/>
-      <c r="AA45" s="21" t="n"/>
-      <c r="AB45" s="21" t="n"/>
-      <c r="AC45" s="21" t="n"/>
-      <c r="AD45" s="21" t="n"/>
-      <c r="AE45" s="21" t="n"/>
-      <c r="AF45" s="21" t="n"/>
-      <c r="AG45" s="21" t="n"/>
-      <c r="AH45" s="21" t="n"/>
-      <c r="AI45" s="21" t="n"/>
-      <c r="AJ45" s="21" t="n"/>
+      <c r="U45" s="29" t="n"/>
+      <c r="V45" s="29" t="n"/>
+      <c r="W45" s="29" t="n"/>
+      <c r="X45" s="29" t="n"/>
+      <c r="Y45" s="29" t="n"/>
+      <c r="Z45" s="29" t="n"/>
+      <c r="AA45" s="29" t="n"/>
+      <c r="AB45" s="29" t="n"/>
+      <c r="AC45" s="29" t="n"/>
+      <c r="AD45" s="29" t="n"/>
+      <c r="AE45" s="29" t="n"/>
+      <c r="AF45" s="29" t="n"/>
+      <c r="AG45" s="29" t="n"/>
+      <c r="AH45" s="29" t="n"/>
+      <c r="AI45" s="29" t="n"/>
+      <c r="AJ45" s="29" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="21" t="n"/>
-      <c r="B46" s="21" t="n"/>
-      <c r="C46" s="21" t="n"/>
-      <c r="D46" s="21" t="n"/>
-      <c r="E46" s="21" t="n"/>
-      <c r="F46" s="21" t="n"/>
-      <c r="G46" s="21" t="n"/>
-      <c r="H46" s="21" t="n"/>
-      <c r="I46" s="21" t="n"/>
-      <c r="J46" s="21" t="n"/>
-      <c r="K46" s="21" t="n"/>
-      <c r="L46" s="21" t="n"/>
-      <c r="M46" s="21" t="n"/>
-      <c r="N46" s="21" t="n"/>
-      <c r="O46" s="21" t="n"/>
-      <c r="P46" s="21" t="n"/>
-      <c r="Q46" s="21" t="n"/>
-      <c r="R46" s="21" t="n"/>
-      <c r="S46" s="21" t="n"/>
-      <c r="T46" s="21" t="n"/>
-      <c r="U46" s="21" t="n"/>
-      <c r="V46" s="21" t="n"/>
-      <c r="W46" s="21" t="n"/>
-      <c r="X46" s="21" t="n"/>
-      <c r="Y46" s="21" t="n"/>
-      <c r="Z46" s="21" t="n"/>
-      <c r="AA46" s="21" t="n"/>
-      <c r="AB46" s="21" t="n"/>
-      <c r="AC46" s="21" t="n"/>
-      <c r="AD46" s="21" t="n"/>
-      <c r="AE46" s="21" t="n"/>
-      <c r="AF46" s="21" t="n"/>
-      <c r="AG46" s="21" t="n"/>
-      <c r="AH46" s="21" t="n"/>
-      <c r="AI46" s="21" t="n"/>
-      <c r="AJ46" s="21" t="n"/>
+      <c r="A46" s="29" t="n"/>
+      <c r="B46" s="29" t="n"/>
+      <c r="C46" s="29" t="n"/>
+      <c r="D46" s="29" t="n"/>
+      <c r="E46" s="29" t="n"/>
+      <c r="F46" s="29" t="n"/>
+      <c r="G46" s="29" t="n"/>
+      <c r="H46" s="29" t="n"/>
+      <c r="I46" s="29" t="n"/>
+      <c r="J46" s="29" t="n"/>
+      <c r="K46" s="29" t="n"/>
+      <c r="L46" s="29" t="n"/>
+      <c r="M46" s="29" t="n"/>
+      <c r="N46" s="29" t="n"/>
+      <c r="O46" s="29" t="n"/>
+      <c r="P46" s="29" t="n"/>
+      <c r="Q46" s="29" t="n"/>
+      <c r="R46" s="29" t="n"/>
+      <c r="S46" s="29" t="n"/>
+      <c r="T46" s="29" t="n"/>
+      <c r="U46" s="29" t="n"/>
+      <c r="V46" s="29" t="n"/>
+      <c r="W46" s="29" t="n"/>
+      <c r="X46" s="29" t="n"/>
+      <c r="Y46" s="29" t="n"/>
+      <c r="Z46" s="29" t="n"/>
+      <c r="AA46" s="29" t="n"/>
+      <c r="AB46" s="29" t="n"/>
+      <c r="AC46" s="29" t="n"/>
+      <c r="AD46" s="29" t="n"/>
+      <c r="AE46" s="29" t="n"/>
+      <c r="AF46" s="29" t="n"/>
+      <c r="AG46" s="29" t="n"/>
+      <c r="AH46" s="29" t="n"/>
+      <c r="AI46" s="29" t="n"/>
+      <c r="AJ46" s="29" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="21" t="n"/>
-      <c r="B47" s="21" t="n"/>
-      <c r="C47" s="21" t="n"/>
-      <c r="D47" s="21" t="n"/>
-      <c r="E47" s="21" t="n"/>
-      <c r="F47" s="21" t="n"/>
-      <c r="G47" s="21" t="n"/>
-      <c r="H47" s="21" t="n"/>
-      <c r="I47" s="21" t="n"/>
-      <c r="J47" s="21" t="n"/>
-      <c r="K47" s="21" t="n"/>
-      <c r="L47" s="21" t="n"/>
-      <c r="M47" s="21" t="n"/>
-      <c r="N47" s="21" t="n"/>
-      <c r="O47" s="21" t="n"/>
-      <c r="P47" s="21" t="n"/>
-      <c r="Q47" s="21" t="n"/>
-      <c r="R47" s="21" t="n"/>
-      <c r="S47" s="21" t="n"/>
-      <c r="T47" s="21" t="n"/>
-      <c r="U47" s="21" t="n"/>
-      <c r="V47" s="21" t="n"/>
-      <c r="W47" s="21" t="n"/>
-      <c r="X47" s="21" t="n"/>
-      <c r="Y47" s="21" t="n"/>
-      <c r="Z47" s="21" t="n"/>
-      <c r="AA47" s="21" t="n"/>
-      <c r="AB47" s="21" t="n"/>
-      <c r="AC47" s="21" t="n"/>
-      <c r="AD47" s="21" t="n"/>
-      <c r="AE47" s="21" t="n"/>
-      <c r="AF47" s="21" t="n"/>
-      <c r="AG47" s="21" t="n"/>
-      <c r="AH47" s="21" t="n"/>
-      <c r="AI47" s="21" t="n"/>
-      <c r="AJ47" s="21" t="n"/>
+      <c r="A47" s="29" t="n"/>
+      <c r="B47" s="29" t="n"/>
+      <c r="C47" s="29" t="n"/>
+      <c r="D47" s="29" t="n"/>
+      <c r="E47" s="29" t="n"/>
+      <c r="F47" s="29" t="n"/>
+      <c r="G47" s="29" t="n"/>
+      <c r="H47" s="29" t="n"/>
+      <c r="I47" s="29" t="n"/>
+      <c r="J47" s="29" t="n"/>
+      <c r="K47" s="29" t="n"/>
+      <c r="L47" s="29" t="n"/>
+      <c r="M47" s="29" t="n"/>
+      <c r="N47" s="29" t="n"/>
+      <c r="O47" s="29" t="n"/>
+      <c r="P47" s="29" t="n"/>
+      <c r="Q47" s="29" t="n"/>
+      <c r="R47" s="29" t="n"/>
+      <c r="S47" s="29" t="n"/>
+      <c r="T47" s="29" t="n"/>
+      <c r="U47" s="29" t="n"/>
+      <c r="V47" s="29" t="n"/>
+      <c r="W47" s="29" t="n"/>
+      <c r="X47" s="29" t="n"/>
+      <c r="Y47" s="29" t="n"/>
+      <c r="Z47" s="29" t="n"/>
+      <c r="AA47" s="29" t="n"/>
+      <c r="AB47" s="29" t="n"/>
+      <c r="AC47" s="29" t="n"/>
+      <c r="AD47" s="29" t="n"/>
+      <c r="AE47" s="29" t="n"/>
+      <c r="AF47" s="29" t="n"/>
+      <c r="AG47" s="29" t="n"/>
+      <c r="AH47" s="29" t="n"/>
+      <c r="AI47" s="29" t="n"/>
+      <c r="AJ47" s="29" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="21" t="n"/>
-      <c r="B48" s="21" t="n"/>
-      <c r="C48" s="21" t="n"/>
-      <c r="D48" s="21" t="n"/>
-      <c r="E48" s="21" t="n"/>
-      <c r="F48" s="21" t="n"/>
-      <c r="G48" s="21" t="n"/>
-      <c r="H48" s="21" t="n"/>
-      <c r="I48" s="21" t="n"/>
-      <c r="J48" s="21" t="n"/>
-      <c r="K48" s="21" t="n"/>
-      <c r="L48" s="21" t="n"/>
-      <c r="M48" s="21" t="n"/>
-      <c r="N48" s="21" t="n"/>
-      <c r="O48" s="21" t="n"/>
-      <c r="P48" s="21" t="n"/>
-      <c r="Q48" s="21" t="n"/>
-      <c r="R48" s="21" t="n"/>
-      <c r="S48" s="21" t="n"/>
-      <c r="T48" s="21" t="n"/>
-      <c r="U48" s="21" t="n"/>
-      <c r="V48" s="21" t="n"/>
-      <c r="W48" s="21" t="n"/>
-      <c r="X48" s="21" t="n"/>
-      <c r="Y48" s="21" t="n"/>
-      <c r="Z48" s="21" t="n"/>
-      <c r="AA48" s="21" t="n"/>
-      <c r="AB48" s="21" t="n"/>
-      <c r="AC48" s="21" t="n"/>
-      <c r="AD48" s="21" t="n"/>
-      <c r="AE48" s="21" t="n"/>
-      <c r="AF48" s="21" t="n"/>
-      <c r="AG48" s="21" t="n"/>
-      <c r="AH48" s="21" t="n"/>
-      <c r="AI48" s="21" t="n"/>
-      <c r="AJ48" s="21" t="n"/>
+      <c r="A48" s="29" t="n"/>
+      <c r="B48" s="29" t="n"/>
+      <c r="C48" s="29" t="n"/>
+      <c r="D48" s="29" t="n"/>
+      <c r="E48" s="29" t="n"/>
+      <c r="F48" s="29" t="n"/>
+      <c r="G48" s="29" t="n"/>
+      <c r="H48" s="29" t="n"/>
+      <c r="I48" s="29" t="n"/>
+      <c r="J48" s="29" t="n"/>
+      <c r="K48" s="29" t="n"/>
+      <c r="L48" s="29" t="n"/>
+      <c r="M48" s="29" t="n"/>
+      <c r="N48" s="29" t="n"/>
+      <c r="O48" s="29" t="n"/>
+      <c r="P48" s="29" t="n"/>
+      <c r="Q48" s="29" t="n"/>
+      <c r="R48" s="29" t="n"/>
+      <c r="S48" s="29" t="n"/>
+      <c r="T48" s="29" t="n"/>
+      <c r="U48" s="29" t="n"/>
+      <c r="V48" s="29" t="n"/>
+      <c r="W48" s="29" t="n"/>
+      <c r="X48" s="29" t="n"/>
+      <c r="Y48" s="29" t="n"/>
+      <c r="Z48" s="29" t="n"/>
+      <c r="AA48" s="29" t="n"/>
+      <c r="AB48" s="29" t="n"/>
+      <c r="AC48" s="29" t="n"/>
+      <c r="AD48" s="29" t="n"/>
+      <c r="AE48" s="29" t="n"/>
+      <c r="AF48" s="29" t="n"/>
+      <c r="AG48" s="29" t="n"/>
+      <c r="AH48" s="29" t="n"/>
+      <c r="AI48" s="29" t="n"/>
+      <c r="AJ48" s="29" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="21" t="n"/>
-      <c r="B49" s="21" t="n"/>
-      <c r="C49" s="21" t="n"/>
-      <c r="D49" s="21" t="n"/>
-      <c r="E49" s="21" t="n"/>
-      <c r="F49" s="21" t="n"/>
-      <c r="G49" s="21" t="n"/>
-      <c r="H49" s="21" t="n"/>
-      <c r="I49" s="21" t="n"/>
-      <c r="J49" s="21" t="n"/>
-      <c r="K49" s="21" t="n"/>
-      <c r="L49" s="21" t="n"/>
-      <c r="M49" s="21" t="n"/>
-      <c r="N49" s="21" t="n"/>
-      <c r="O49" s="21" t="n"/>
-      <c r="P49" s="21" t="n"/>
-      <c r="Q49" s="21" t="n"/>
-      <c r="R49" s="21" t="n"/>
-      <c r="S49" s="21" t="n"/>
-      <c r="T49" s="21" t="n"/>
-      <c r="U49" s="21" t="n"/>
-      <c r="V49" s="21" t="n"/>
-      <c r="W49" s="21" t="n"/>
-      <c r="X49" s="21" t="n"/>
-      <c r="Y49" s="21" t="n"/>
-      <c r="Z49" s="21" t="n"/>
-      <c r="AA49" s="21" t="n"/>
-      <c r="AB49" s="21" t="n"/>
-      <c r="AC49" s="21" t="n"/>
-      <c r="AD49" s="21" t="n"/>
-      <c r="AE49" s="21" t="n"/>
-      <c r="AF49" s="21" t="n"/>
-      <c r="AG49" s="21" t="n"/>
-      <c r="AH49" s="21" t="n"/>
-      <c r="AI49" s="21" t="n"/>
-      <c r="AJ49" s="21" t="n"/>
+      <c r="A49" s="29" t="n"/>
+      <c r="B49" s="29" t="n"/>
+      <c r="C49" s="29" t="n"/>
+      <c r="D49" s="29" t="n"/>
+      <c r="E49" s="29" t="n"/>
+      <c r="F49" s="29" t="n"/>
+      <c r="G49" s="29" t="n"/>
+      <c r="H49" s="29" t="n"/>
+      <c r="I49" s="29" t="n"/>
+      <c r="J49" s="29" t="n"/>
+      <c r="K49" s="29" t="n"/>
+      <c r="L49" s="29" t="n"/>
+      <c r="M49" s="29" t="n"/>
+      <c r="N49" s="29" t="n"/>
+      <c r="O49" s="29" t="n"/>
+      <c r="P49" s="29" t="n"/>
+      <c r="Q49" s="29" t="n"/>
+      <c r="R49" s="29" t="n"/>
+      <c r="S49" s="29" t="n"/>
+      <c r="T49" s="29" t="n"/>
+      <c r="U49" s="29" t="n"/>
+      <c r="V49" s="29" t="n"/>
+      <c r="W49" s="29" t="n"/>
+      <c r="X49" s="29" t="n"/>
+      <c r="Y49" s="29" t="n"/>
+      <c r="Z49" s="29" t="n"/>
+      <c r="AA49" s="29" t="n"/>
+      <c r="AB49" s="29" t="n"/>
+      <c r="AC49" s="29" t="n"/>
+      <c r="AD49" s="29" t="n"/>
+      <c r="AE49" s="29" t="n"/>
+      <c r="AF49" s="29" t="n"/>
+      <c r="AG49" s="29" t="n"/>
+      <c r="AH49" s="29" t="n"/>
+      <c r="AI49" s="29" t="n"/>
+      <c r="AJ49" s="29" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="29" t="n"/>
+      <c r="B50" s="29" t="n"/>
+      <c r="C50" s="29" t="n"/>
+      <c r="D50" s="29" t="n"/>
+      <c r="E50" s="29" t="n"/>
+      <c r="F50" s="29" t="n"/>
+      <c r="G50" s="29" t="n"/>
+      <c r="H50" s="29" t="n"/>
+      <c r="I50" s="29" t="n"/>
+      <c r="J50" s="29" t="n"/>
+      <c r="K50" s="29" t="n"/>
+      <c r="L50" s="29" t="n"/>
+      <c r="M50" s="29" t="n"/>
+      <c r="N50" s="29" t="n"/>
+      <c r="O50" s="29" t="n"/>
+      <c r="P50" s="29" t="n"/>
+      <c r="Q50" s="29" t="n"/>
+      <c r="R50" s="29" t="n"/>
+      <c r="S50" s="29" t="n"/>
+      <c r="T50" s="29" t="n"/>
+      <c r="U50" s="29" t="n"/>
+      <c r="V50" s="29" t="n"/>
+      <c r="W50" s="29" t="n"/>
+      <c r="X50" s="29" t="n"/>
+      <c r="Y50" s="29" t="n"/>
+      <c r="Z50" s="29" t="n"/>
+      <c r="AA50" s="29" t="n"/>
+      <c r="AB50" s="29" t="n"/>
+      <c r="AC50" s="29" t="n"/>
+      <c r="AD50" s="29" t="n"/>
+      <c r="AE50" s="29" t="n"/>
+      <c r="AF50" s="29" t="n"/>
+      <c r="AG50" s="29" t="n"/>
+      <c r="AH50" s="29" t="n"/>
+      <c r="AI50" s="29" t="n"/>
+      <c r="AJ50" s="29" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="29" t="n"/>
+      <c r="B51" s="29" t="n"/>
+      <c r="C51" s="29" t="n"/>
+      <c r="D51" s="29" t="n"/>
+      <c r="E51" s="29" t="n"/>
+      <c r="F51" s="29" t="n"/>
+      <c r="G51" s="29" t="n"/>
+      <c r="H51" s="29" t="n"/>
+      <c r="I51" s="29" t="n"/>
+      <c r="J51" s="29" t="n"/>
+      <c r="K51" s="29" t="n"/>
+      <c r="L51" s="29" t="n"/>
+      <c r="M51" s="29" t="n"/>
+      <c r="N51" s="29" t="n"/>
+      <c r="O51" s="29" t="n"/>
+      <c r="P51" s="29" t="n"/>
+      <c r="Q51" s="29" t="n"/>
+      <c r="R51" s="29" t="n"/>
+      <c r="S51" s="29" t="n"/>
+      <c r="T51" s="29" t="n"/>
+      <c r="U51" s="29" t="n"/>
+      <c r="V51" s="29" t="n"/>
+      <c r="W51" s="29" t="n"/>
+      <c r="X51" s="29" t="n"/>
+      <c r="Y51" s="29" t="n"/>
+      <c r="Z51" s="29" t="n"/>
+      <c r="AA51" s="29" t="n"/>
+      <c r="AB51" s="29" t="n"/>
+      <c r="AC51" s="29" t="n"/>
+      <c r="AD51" s="29" t="n"/>
+      <c r="AE51" s="29" t="n"/>
+      <c r="AF51" s="29" t="n"/>
+      <c r="AG51" s="29" t="n"/>
+      <c r="AH51" s="29" t="n"/>
+      <c r="AI51" s="29" t="n"/>
+      <c r="AJ51" s="29" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="45">
@@ -9460,7 +10057,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9476,160 +10073,160 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="36" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>📚  References / Fuentes</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="37" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>All data sourced from the following public references as of April 1, 2026.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="38" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B3" s="38" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="C3" s="38" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>Accessed</t>
         </is>
       </c>
-      <c r="D3" s="38" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="45" t="inlineStr">
         <is>
           <t>FIFA Official</t>
         </is>
       </c>
-      <c r="B4" s="40" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/tournaments/mens/worldcup/canadamexicousa2026/articles/match-schedule-fixtures-results-teams-stadiums</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="45" t="inlineStr">
         <is>
           <t>Apr 1, 2026</t>
         </is>
       </c>
-      <c r="D4" s="41" t="inlineStr">
+      <c r="D4" s="47" t="inlineStr">
         <is>
           <t>Official match schedule and fixtures</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="42" t="inlineStr">
+      <c r="A5" s="48" t="inlineStr">
         <is>
           <t>FOX Sports</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="49" t="inlineStr">
         <is>
           <t>https://www.foxsports.com/stories/soccer/2026-world-cup-schedule-all-games-dates-matchups-how-watch</t>
         </is>
       </c>
-      <c r="C5" s="42" t="inlineStr">
+      <c r="C5" s="48" t="inlineStr">
         <is>
           <t>Apr 1, 2026</t>
         </is>
       </c>
-      <c r="D5" s="44" t="inlineStr">
+      <c r="D5" s="50" t="inlineStr">
         <is>
           <t>Full broadcast schedule with dates, times and venues</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t>CNN Español</t>
         </is>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
         <is>
           <t>https://cnnespanol.cnn.com/2026/04/01/deportes/grupos-zonas-copa-mundial-2026-orix</t>
         </is>
       </c>
-      <c r="C6" s="39" t="inlineStr">
+      <c r="C6" s="45" t="inlineStr">
         <is>
           <t>Apr 1, 2026</t>
         </is>
       </c>
-      <c r="D6" s="41" t="inlineStr">
+      <c r="D6" s="47" t="inlineStr">
         <is>
           <t>Complete groups and match calendar (post-playoff)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="48" t="inlineStr">
         <is>
           <t>Marca</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="49" t="inlineStr">
         <is>
           <t>https://www.marca.com/futbol/mundial/2026/04/01/estan-12-grupos-completos-mundial-falta-irak-bolivia.html</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr">
+      <c r="C7" s="48" t="inlineStr">
         <is>
           <t>Apr 1, 2026</t>
         </is>
       </c>
-      <c r="D7" s="44" t="inlineStr">
+      <c r="D7" s="50" t="inlineStr">
         <is>
           <t>12 complete groups confirmed; Iraq &amp; DR Congo qualify via inter-confederation playoff</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="A8" s="45" t="inlineStr">
         <is>
           <t>Wikipedia – 2026 FIFA World Cup</t>
         </is>
       </c>
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B8" s="46" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/2026_FIFA_World_Cup</t>
         </is>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" s="45" t="inlineStr">
         <is>
           <t>Apr 1, 2026</t>
         </is>
       </c>
-      <c r="D8" s="41" t="inlineStr">
+      <c r="D8" s="47" t="inlineStr">
         <is>
           <t>Tournament overview, format, host cities, qualification</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="45" t="inlineStr">
+      <c r="A10" s="51" t="inlineStr">
         <is>
           <t>Tournament format: 48 teams · 12 groups of 4 · Top 2 per group + 8 best 3rd-place finishers → Round of 32 · 104 total matches · June 11 – July 19, 2026 · Host cities: USA, Canada, Mexico</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="46" t="inlineStr">
+      <c r="A12" s="52" t="inlineStr">
         <is>
           <t>Generated by generate_quiniela.py  ·  MIT License</t>
         </is>

--- a/quiniela_mundial_2026.xlsx
+++ b/quiniela_mundial_2026.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -168,6 +168,12 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
+      <color rgb="008EAADB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="008EAADB"/>
       <sz val="9"/>
     </font>
@@ -521,7 +527,7 @@
     <xf numFmtId="0" fontId="2" fillId="14" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -533,46 +539,46 @@
     <xf numFmtId="0" fontId="24" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7284,7 +7290,7 @@
     <row r="3" ht="14" customHeight="1">
       <c r="A3" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ✏️ Yellow cells = goals (90 min + ET combined)  ·  Blue-grey rows = Penalty shootout score (optional — only if tied after ET)  ·  Blue-grey team cells = best 3rd-place slot — enter manually after group stage</t>
+          <t xml:space="preserve">  ✏️ Yellow cells = goals (90 min + ET combined)  ·  Blue-grey rows = Penalty shootout score (only if tied after ET)  ·  Blue-grey team cells = best 3rd-place qualifier — type the country name after the group stage</t>
         </is>
       </c>
     </row>
@@ -7543,11 +7549,7 @@
       </c>
       <c r="AH9" s="10" t="n"/>
       <c r="AI9" s="10" t="n"/>
-      <c r="AJ9" s="35" t="inlineStr">
-        <is>
-          <t>◀ Enter 3rd</t>
-        </is>
-      </c>
+      <c r="AJ9" s="35" t="inlineStr"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="36" t="inlineStr">
@@ -7650,13 +7652,13 @@
         </is>
       </c>
       <c r="E12" s="33">
-        <f>IF(AND($B$9&lt;&gt;"",$C$9&lt;&gt;""),IF($B$9&gt;$C$9,$A$9,IF($C$9&gt;$B$9,$D$9,IF(AND($B$10&lt;&gt;"",$C$10&lt;&gt;""),IF($B$10&gt;$C$10,$A$9,$D$9),"TBD"))),"—")</f>
+        <f>IF(AND($B$9&lt;&gt;"",$C$9&lt;&gt;"",$A$9&lt;&gt;"",$D$9&lt;&gt;""),IF($B$9&gt;$C$9,$A$9,IF($C$9&gt;$B$9,$D$9,IF(AND($B$10&lt;&gt;"",$C$10&lt;&gt;""),IF($B$10&gt;$C$10,$A$9,IF($B$10&lt;$C$10,$D$9,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="F12" s="10" t="n"/>
       <c r="G12" s="10" t="n"/>
       <c r="H12" s="34">
-        <f>IF(AND($B$13&lt;&gt;"",$C$13&lt;&gt;""),IF($B$13&gt;$C$13,$A$13,IF($C$13&gt;$B$13,$D$13,IF(AND($B$14&lt;&gt;"",$C$14&lt;&gt;""),IF($B$14&gt;$C$14,$A$13,$D$13),"TBD"))),"—")</f>
+        <f>IF(AND($B$13&lt;&gt;"",$C$13&lt;&gt;"",$A$13&lt;&gt;"",$D$13&lt;&gt;""),IF($B$13&gt;$C$13,$A$13,IF($C$13&gt;$B$13,$D$13,IF(AND($B$14&lt;&gt;"",$C$14&lt;&gt;""),IF($B$14&gt;$C$14,$A$13,IF($B$14&lt;$C$14,$D$13,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="I12" s="29" t="n"/>
@@ -7680,13 +7682,13 @@
       <c r="AA12" s="29" t="n"/>
       <c r="AB12" s="29" t="n"/>
       <c r="AC12" s="33">
-        <f>IF(AND($AH$9&lt;&gt;"",$AI$9&lt;&gt;""),IF($AH$9&gt;$AI$9,$AG$9,IF($AI$9&gt;$AH$9,$AJ$9,IF(AND($AH$10&lt;&gt;"",$AI$10&lt;&gt;""),IF($AH$10&gt;$AI$10,$AG$9,$AJ$9),"TBD"))),"—")</f>
+        <f>IF(AND($AH$9&lt;&gt;"",$AI$9&lt;&gt;"",$AG$9&lt;&gt;"",$AJ$9&lt;&gt;""),IF($AH$9&gt;$AI$9,$AG$9,IF($AI$9&gt;$AH$9,$AJ$9,IF(AND($AH$10&lt;&gt;"",$AI$10&lt;&gt;""),IF($AH$10&gt;$AI$10,$AG$9,IF($AH$10&lt;$AI$10,$AJ$9,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="AD12" s="10" t="n"/>
       <c r="AE12" s="10" t="n"/>
       <c r="AF12" s="34">
-        <f>IF(AND($AH$13&lt;&gt;"",$AI$13&lt;&gt;""),IF($AH$13&gt;$AI$13,$AG$13,IF($AI$13&gt;$AH$13,$AJ$13,IF(AND($AH$14&lt;&gt;"",$AI$14&lt;&gt;""),IF($AH$14&gt;$AI$14,$AG$13,$AJ$13),"TBD"))),"—")</f>
+        <f>IF(AND($AH$13&lt;&gt;"",$AI$13&lt;&gt;"",$AG$13&lt;&gt;"",$AJ$13&lt;&gt;""),IF($AH$13&gt;$AI$13,$AG$13,IF($AI$13&gt;$AH$13,$AJ$13,IF(AND($AH$14&lt;&gt;"",$AI$14&lt;&gt;""),IF($AH$14&gt;$AI$14,$AG$13,IF($AH$14&lt;$AI$14,$AJ$13,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="AG12" s="32" t="inlineStr">
@@ -7756,11 +7758,7 @@
       </c>
       <c r="AH13" s="10" t="n"/>
       <c r="AI13" s="10" t="n"/>
-      <c r="AJ13" s="35" t="inlineStr">
-        <is>
-          <t>◀ Enter 3rd</t>
-        </is>
-      </c>
+      <c r="AJ13" s="35" t="inlineStr"/>
     </row>
     <row r="14" ht="14" customHeight="1">
       <c r="A14" s="36" t="inlineStr">
@@ -7867,13 +7865,13 @@
       <c r="G16" s="29" t="n"/>
       <c r="H16" s="29" t="n"/>
       <c r="I16" s="33">
-        <f>IF(AND($F$12&lt;&gt;"",$G$12&lt;&gt;""),IF($F$12&gt;$G$12,$E$12,IF($G$12&gt;$F$12,$H$12,IF(AND($F$13&lt;&gt;"",$G$13&lt;&gt;""),IF($F$13&gt;$G$13,$E$12,$H$12),"TBD"))),"—")</f>
+        <f>IF(AND($F$12&lt;&gt;"",$G$12&lt;&gt;"",$E$12&lt;&gt;"",$H$12&lt;&gt;""),IF($F$12&gt;$G$12,$E$12,IF($G$12&gt;$F$12,$H$12,IF(AND($F$13&lt;&gt;"",$G$13&lt;&gt;""),IF($F$13&gt;$G$13,$E$12,IF($F$13&lt;$G$13,$H$12,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="J16" s="10" t="n"/>
       <c r="K16" s="10" t="n"/>
       <c r="L16" s="34">
-        <f>IF(AND($F$20&lt;&gt;"",$G$20&lt;&gt;""),IF($F$20&gt;$G$20,$E$20,IF($G$20&gt;$F$20,$H$20,IF(AND($F$21&lt;&gt;"",$G$21&lt;&gt;""),IF($F$21&gt;$G$21,$E$20,$H$20),"TBD"))),"—")</f>
+        <f>IF(AND($F$20&lt;&gt;"",$G$20&lt;&gt;"",$E$20&lt;&gt;"",$H$20&lt;&gt;""),IF($F$20&gt;$G$20,$E$20,IF($G$20&gt;$F$20,$H$20,IF(AND($F$21&lt;&gt;"",$G$21&lt;&gt;""),IF($F$21&gt;$G$21,$E$20,IF($F$21&lt;$G$21,$H$20,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="M16" s="29" t="n"/>
@@ -7889,13 +7887,13 @@
       <c r="W16" s="29" t="n"/>
       <c r="X16" s="29" t="n"/>
       <c r="Y16" s="33">
-        <f>IF(AND($AD$12&lt;&gt;"",$AE$12&lt;&gt;""),IF($AD$12&gt;$AE$12,$AC$12,IF($AE$12&gt;$AD$12,$AF$12,IF(AND($AD$13&lt;&gt;"",$AE$13&lt;&gt;""),IF($AD$13&gt;$AE$13,$AC$12,$AF$12),"TBD"))),"—")</f>
+        <f>IF(AND($AD$12&lt;&gt;"",$AE$12&lt;&gt;"",$AC$12&lt;&gt;"",$AF$12&lt;&gt;""),IF($AD$12&gt;$AE$12,$AC$12,IF($AE$12&gt;$AD$12,$AF$12,IF(AND($AD$13&lt;&gt;"",$AE$13&lt;&gt;""),IF($AD$13&gt;$AE$13,$AC$12,IF($AD$13&lt;$AE$13,$AF$12,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="Z16" s="10" t="n"/>
       <c r="AA16" s="10" t="n"/>
       <c r="AB16" s="34">
-        <f>IF(AND($AD$20&lt;&gt;"",$AE$20&lt;&gt;""),IF($AD$20&gt;$AE$20,$AC$20,IF($AE$20&gt;$AD$20,$AF$20,IF(AND($AD$21&lt;&gt;"",$AE$21&lt;&gt;""),IF($AD$21&gt;$AE$21,$AC$20,$AF$20),"TBD"))),"—")</f>
+        <f>IF(AND($AD$20&lt;&gt;"",$AE$20&lt;&gt;"",$AC$20&lt;&gt;"",$AF$20&lt;&gt;""),IF($AD$20&gt;$AE$20,$AC$20,IF($AE$20&gt;$AD$20,$AF$20,IF(AND($AD$21&lt;&gt;"",$AE$21&lt;&gt;""),IF($AD$21&gt;$AE$21,$AC$20,IF($AD$21&lt;$AE$21,$AF$20,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="AC16" s="29" t="n"/>
@@ -7915,11 +7913,7 @@
       </c>
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="10" t="n"/>
-      <c r="D17" s="35" t="inlineStr">
-        <is>
-          <t>◀ Enter 3rd</t>
-        </is>
-      </c>
+      <c r="D17" s="35" t="inlineStr"/>
       <c r="E17" s="29" t="n"/>
       <c r="F17" s="29" t="n"/>
       <c r="G17" s="29" t="n"/>
@@ -8076,13 +8070,13 @@
         </is>
       </c>
       <c r="E20" s="33">
-        <f>IF(AND($B$17&lt;&gt;"",$C$17&lt;&gt;""),IF($B$17&gt;$C$17,$A$17,IF($C$17&gt;$B$17,$D$17,IF(AND($B$18&lt;&gt;"",$C$18&lt;&gt;""),IF($B$18&gt;$C$18,$A$17,$D$17),"TBD"))),"—")</f>
+        <f>IF(AND($B$17&lt;&gt;"",$C$17&lt;&gt;"",$A$17&lt;&gt;"",$D$17&lt;&gt;""),IF($B$17&gt;$C$17,$A$17,IF($C$17&gt;$B$17,$D$17,IF(AND($B$18&lt;&gt;"",$C$18&lt;&gt;""),IF($B$18&gt;$C$18,$A$17,IF($B$18&lt;$C$18,$D$17,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="F20" s="10" t="n"/>
       <c r="G20" s="10" t="n"/>
       <c r="H20" s="34">
-        <f>IF(AND($B$21&lt;&gt;"",$C$21&lt;&gt;""),IF($B$21&gt;$C$21,$A$21,IF($C$21&gt;$B$21,$D$21,IF(AND($B$22&lt;&gt;"",$C$22&lt;&gt;""),IF($B$22&gt;$C$22,$A$21,$D$21),"TBD"))),"—")</f>
+        <f>IF(AND($B$21&lt;&gt;"",$C$21&lt;&gt;"",$A$21&lt;&gt;"",$D$21&lt;&gt;""),IF($B$21&gt;$C$21,$A$21,IF($C$21&gt;$B$21,$D$21,IF(AND($B$22&lt;&gt;"",$C$22&lt;&gt;""),IF($B$22&gt;$C$22,$A$21,IF($B$22&lt;$C$22,$D$21,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="I20" s="29" t="n"/>
@@ -8106,13 +8100,13 @@
       <c r="AA20" s="29" t="n"/>
       <c r="AB20" s="29" t="n"/>
       <c r="AC20" s="33">
-        <f>IF(AND($AH$17&lt;&gt;"",$AI$17&lt;&gt;""),IF($AH$17&gt;$AI$17,$AG$17,IF($AI$17&gt;$AH$17,$AJ$17,IF(AND($AH$18&lt;&gt;"",$AI$18&lt;&gt;""),IF($AH$18&gt;$AI$18,$AG$17,$AJ$17),"TBD"))),"—")</f>
+        <f>IF(AND($AH$17&lt;&gt;"",$AI$17&lt;&gt;"",$AG$17&lt;&gt;"",$AJ$17&lt;&gt;""),IF($AH$17&gt;$AI$17,$AG$17,IF($AI$17&gt;$AH$17,$AJ$17,IF(AND($AH$18&lt;&gt;"",$AI$18&lt;&gt;""),IF($AH$18&gt;$AI$18,$AG$17,IF($AH$18&lt;$AI$18,$AJ$17,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="AD20" s="10" t="n"/>
       <c r="AE20" s="10" t="n"/>
       <c r="AF20" s="34">
-        <f>IF(AND($AH$21&lt;&gt;"",$AI$21&lt;&gt;""),IF($AH$21&gt;$AI$21,$AG$21,IF($AI$21&gt;$AH$21,$AJ$21,IF(AND($AH$22&lt;&gt;"",$AI$22&lt;&gt;""),IF($AH$22&gt;$AI$22,$AG$21,$AJ$21),"TBD"))),"—")</f>
+        <f>IF(AND($AH$21&lt;&gt;"",$AI$21&lt;&gt;"",$AG$21&lt;&gt;"",$AJ$21&lt;&gt;""),IF($AH$21&gt;$AI$21,$AG$21,IF($AI$21&gt;$AH$21,$AJ$21,IF(AND($AH$22&lt;&gt;"",$AI$22&lt;&gt;""),IF($AH$22&gt;$AI$22,$AG$21,IF($AH$22&lt;$AI$22,$AJ$21,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="AG20" s="32" t="inlineStr">
@@ -8297,33 +8291,33 @@
       <c r="K24" s="29" t="n"/>
       <c r="L24" s="29" t="n"/>
       <c r="M24" s="33">
-        <f>IF(AND($J$16&lt;&gt;"",$K$16&lt;&gt;""),IF($J$16&gt;$K$16,$I$16,IF($K$16&gt;$J$16,$L$16,IF(AND($J$17&lt;&gt;"",$K$17&lt;&gt;""),IF($J$17&gt;$K$17,$I$16,$L$16),"TBD"))),"—")</f>
+        <f>IF(AND($J$16&lt;&gt;"",$K$16&lt;&gt;"",$I$16&lt;&gt;"",$L$16&lt;&gt;""),IF($J$16&gt;$K$16,$I$16,IF($K$16&gt;$J$16,$L$16,IF(AND($J$17&lt;&gt;"",$K$17&lt;&gt;""),IF($J$17&gt;$K$17,$I$16,IF($J$17&lt;$K$17,$L$16,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="N24" s="10" t="n"/>
       <c r="O24" s="10" t="n"/>
       <c r="P24" s="34">
-        <f>IF(AND($J$32&lt;&gt;"",$K$32&lt;&gt;""),IF($J$32&gt;$K$32,$I$32,IF($K$32&gt;$J$32,$L$32,IF(AND($J$33&lt;&gt;"",$K$33&lt;&gt;""),IF($J$33&gt;$K$33,$I$32,$L$32),"TBD"))),"—")</f>
+        <f>IF(AND($J$32&lt;&gt;"",$K$32&lt;&gt;"",$I$32&lt;&gt;"",$L$32&lt;&gt;""),IF($J$32&gt;$K$32,$I$32,IF($K$32&gt;$J$32,$L$32,IF(AND($J$33&lt;&gt;"",$K$33&lt;&gt;""),IF($J$33&gt;$K$33,$I$32,IF($J$33&lt;$K$33,$L$32,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="Q24" s="40">
-        <f>IF(AND($N$24&lt;&gt;"",$O$24&lt;&gt;""),IF($N$24&gt;$O$24,$M$24,IF($O$24&gt;$N$24,$P$24,IF(AND($N$25&lt;&gt;"",$O$25&lt;&gt;""),IF($N$25&gt;$O$25,$M$24,$P$24),"TBD"))),"—")</f>
+        <f>IF(AND($N$24&lt;&gt;"",$O$24&lt;&gt;"",$M$24&lt;&gt;"",$P$24&lt;&gt;""),IF($N$24&gt;$O$24,$M$24,IF($O$24&gt;$N$24,$P$24,IF(AND($N$25&lt;&gt;"",$O$25&lt;&gt;""),IF($N$25&gt;$O$25,$M$24,IF($N$25&lt;$O$25,$P$24,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="R24" s="41" t="n"/>
       <c r="S24" s="41" t="n"/>
       <c r="T24" s="42">
-        <f>IF(AND($V$24&lt;&gt;"",$W$24&lt;&gt;""),IF($V$24&gt;$W$24,$U$24,IF($W$24&gt;$V$24,$X$24,IF(AND($V$25&lt;&gt;"",$W$25&lt;&gt;""),IF($V$25&gt;$W$25,$U$24,$X$24),"TBD"))),"—")</f>
+        <f>IF(AND($V$24&lt;&gt;"",$W$24&lt;&gt;"",$U$24&lt;&gt;"",$X$24&lt;&gt;""),IF($V$24&gt;$W$24,$U$24,IF($W$24&gt;$V$24,$X$24,IF(AND($V$25&lt;&gt;"",$W$25&lt;&gt;""),IF($V$25&gt;$W$25,$U$24,IF($V$25&lt;$W$25,$X$24,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="U24" s="33">
-        <f>IF(AND($Z$16&lt;&gt;"",$AA$16&lt;&gt;""),IF($Z$16&gt;$AA$16,$Y$16,IF($AA$16&gt;$Z$16,$AB$16,IF(AND($Z$17&lt;&gt;"",$AA$17&lt;&gt;""),IF($Z$17&gt;$AA$17,$Y$16,$AB$16),"TBD"))),"—")</f>
+        <f>IF(AND($Z$16&lt;&gt;"",$AA$16&lt;&gt;"",$Y$16&lt;&gt;"",$AB$16&lt;&gt;""),IF($Z$16&gt;$AA$16,$Y$16,IF($AA$16&gt;$Z$16,$AB$16,IF(AND($Z$17&lt;&gt;"",$AA$17&lt;&gt;""),IF($Z$17&gt;$AA$17,$Y$16,IF($Z$17&lt;$AA$17,$AB$16,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="V24" s="10" t="n"/>
       <c r="W24" s="10" t="n"/>
       <c r="X24" s="34">
-        <f>IF(AND($Z$32&lt;&gt;"",$AA$32&lt;&gt;""),IF($Z$32&gt;$AA$32,$Y$32,IF($AA$32&gt;$Z$32,$AB$32,IF(AND($Z$33&lt;&gt;"",$AA$33&lt;&gt;""),IF($Z$33&gt;$AA$33,$Y$32,$AB$32),"TBD"))),"—")</f>
+        <f>IF(AND($Z$32&lt;&gt;"",$AA$32&lt;&gt;"",$Y$32&lt;&gt;"",$AB$32&lt;&gt;""),IF($Z$32&gt;$AA$32,$Y$32,IF($AA$32&gt;$Z$32,$AB$32,IF(AND($Z$33&lt;&gt;"",$AA$33&lt;&gt;""),IF($Z$33&gt;$AA$33,$Y$32,IF($Z$33&lt;$AA$33,$AB$32,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="Y24" s="29" t="n"/>
@@ -8409,11 +8403,7 @@
       </c>
       <c r="AH25" s="10" t="n"/>
       <c r="AI25" s="10" t="n"/>
-      <c r="AJ25" s="35" t="inlineStr">
-        <is>
-          <t>◀ Enter 3rd</t>
-        </is>
-      </c>
+      <c r="AJ25" s="35" t="inlineStr"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="36" t="inlineStr">
@@ -8441,7 +8431,7 @@
       <c r="O26" s="29" t="n"/>
       <c r="P26" s="29" t="n"/>
       <c r="Q26" s="43">
-        <f>IF($R$24&lt;&gt;"","🏆 "&amp;IF(AND($R$24&lt;&gt;"",$S$24&lt;&gt;""),IF($R$24&gt;$S$24,$Q$24,IF($S$24&gt;$R$24,$T$24,IF(AND($R$25&lt;&gt;"",$S$25&lt;&gt;""),IF($R$25&gt;$S$25,$Q$24,$T$24),"TBD"))),"—")&amp;" 🏆","🏆 WORLD CHAMPION 🏆")</f>
+        <f>IF($R$24&lt;&gt;"","🏆 "&amp;IF(AND($R$24&lt;&gt;"",$S$24&lt;&gt;"",$Q$24&lt;&gt;"",$T$24&lt;&gt;""),IF($R$24&gt;$S$24,$Q$24,IF($S$24&gt;$R$24,$T$24,IF(AND($R$25&lt;&gt;"",$S$25&lt;&gt;""),IF($R$25&gt;$S$25,$Q$24,IF($R$25&lt;$S$25,$T$24,"TBD")),"TBD"))),"—")&amp;" 🏆","🏆 WORLD CHAMPION 🏆")</f>
         <v/>
       </c>
       <c r="U26" s="29" t="n"/>
@@ -8516,13 +8506,13 @@
         </is>
       </c>
       <c r="E28" s="33">
-        <f>IF(AND($B$25&lt;&gt;"",$C$25&lt;&gt;""),IF($B$25&gt;$C$25,$A$25,IF($C$25&gt;$B$25,$D$25,IF(AND($B$26&lt;&gt;"",$C$26&lt;&gt;""),IF($B$26&gt;$C$26,$A$25,$D$25),"TBD"))),"—")</f>
+        <f>IF(AND($B$25&lt;&gt;"",$C$25&lt;&gt;"",$A$25&lt;&gt;"",$D$25&lt;&gt;""),IF($B$25&gt;$C$25,$A$25,IF($C$25&gt;$B$25,$D$25,IF(AND($B$26&lt;&gt;"",$C$26&lt;&gt;""),IF($B$26&gt;$C$26,$A$25,IF($B$26&lt;$C$26,$D$25,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="F28" s="10" t="n"/>
       <c r="G28" s="10" t="n"/>
       <c r="H28" s="34">
-        <f>IF(AND($B$29&lt;&gt;"",$C$29&lt;&gt;""),IF($B$29&gt;$C$29,$A$29,IF($C$29&gt;$B$29,$D$29,IF(AND($B$30&lt;&gt;"",$C$30&lt;&gt;""),IF($B$30&gt;$C$30,$A$29,$D$29),"TBD"))),"—")</f>
+        <f>IF(AND($B$29&lt;&gt;"",$C$29&lt;&gt;"",$A$29&lt;&gt;"",$D$29&lt;&gt;""),IF($B$29&gt;$C$29,$A$29,IF($C$29&gt;$B$29,$D$29,IF(AND($B$30&lt;&gt;"",$C$30&lt;&gt;""),IF($B$30&gt;$C$30,$A$29,IF($B$30&lt;$C$30,$D$29,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="I28" s="29" t="n"/>
@@ -8546,13 +8536,13 @@
       <c r="AA28" s="29" t="n"/>
       <c r="AB28" s="29" t="n"/>
       <c r="AC28" s="33">
-        <f>IF(AND($AH$25&lt;&gt;"",$AI$25&lt;&gt;""),IF($AH$25&gt;$AI$25,$AG$25,IF($AI$25&gt;$AH$25,$AJ$25,IF(AND($AH$26&lt;&gt;"",$AI$26&lt;&gt;""),IF($AH$26&gt;$AI$26,$AG$25,$AJ$25),"TBD"))),"—")</f>
+        <f>IF(AND($AH$25&lt;&gt;"",$AI$25&lt;&gt;"",$AG$25&lt;&gt;"",$AJ$25&lt;&gt;""),IF($AH$25&gt;$AI$25,$AG$25,IF($AI$25&gt;$AH$25,$AJ$25,IF(AND($AH$26&lt;&gt;"",$AI$26&lt;&gt;""),IF($AH$26&gt;$AI$26,$AG$25,IF($AH$26&lt;$AI$26,$AJ$25,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="AD28" s="10" t="n"/>
       <c r="AE28" s="10" t="n"/>
       <c r="AF28" s="34">
-        <f>IF(AND($AH$29&lt;&gt;"",$AI$29&lt;&gt;""),IF($AH$29&gt;$AI$29,$AG$29,IF($AI$29&gt;$AH$29,$AJ$29,IF(AND($AH$30&lt;&gt;"",$AI$30&lt;&gt;""),IF($AH$30&gt;$AI$30,$AG$29,$AJ$29),"TBD"))),"—")</f>
+        <f>IF(AND($AH$29&lt;&gt;"",$AI$29&lt;&gt;"",$AG$29&lt;&gt;"",$AJ$29&lt;&gt;""),IF($AH$29&gt;$AI$29,$AG$29,IF($AI$29&gt;$AH$29,$AJ$29,IF(AND($AH$30&lt;&gt;"",$AI$30&lt;&gt;""),IF($AH$30&gt;$AI$30,$AG$29,IF($AH$30&lt;$AI$30,$AJ$29,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="AG28" s="32" t="inlineStr">
@@ -8568,11 +8558,7 @@
       </c>
       <c r="B29" s="10" t="n"/>
       <c r="C29" s="10" t="n"/>
-      <c r="D29" s="35" t="inlineStr">
-        <is>
-          <t>◀ Enter 3rd</t>
-        </is>
-      </c>
+      <c r="D29" s="35" t="inlineStr"/>
       <c r="E29" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
@@ -8733,13 +8719,13 @@
       <c r="G32" s="29" t="n"/>
       <c r="H32" s="29" t="n"/>
       <c r="I32" s="33">
-        <f>IF(AND($F$28&lt;&gt;"",$G$28&lt;&gt;""),IF($F$28&gt;$G$28,$E$28,IF($G$28&gt;$F$28,$H$28,IF(AND($F$29&lt;&gt;"",$G$29&lt;&gt;""),IF($F$29&gt;$G$29,$E$28,$H$28),"TBD"))),"—")</f>
+        <f>IF(AND($F$28&lt;&gt;"",$G$28&lt;&gt;"",$E$28&lt;&gt;"",$H$28&lt;&gt;""),IF($F$28&gt;$G$28,$E$28,IF($G$28&gt;$F$28,$H$28,IF(AND($F$29&lt;&gt;"",$G$29&lt;&gt;""),IF($F$29&gt;$G$29,$E$28,IF($F$29&lt;$G$29,$H$28,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="J32" s="10" t="n"/>
       <c r="K32" s="10" t="n"/>
       <c r="L32" s="34">
-        <f>IF(AND($F$36&lt;&gt;"",$G$36&lt;&gt;""),IF($F$36&gt;$G$36,$E$36,IF($G$36&gt;$F$36,$H$36,IF(AND($F$37&lt;&gt;"",$G$37&lt;&gt;""),IF($F$37&gt;$G$37,$E$36,$H$36),"TBD"))),"—")</f>
+        <f>IF(AND($F$36&lt;&gt;"",$G$36&lt;&gt;"",$E$36&lt;&gt;"",$H$36&lt;&gt;""),IF($F$36&gt;$G$36,$E$36,IF($G$36&gt;$F$36,$H$36,IF(AND($F$37&lt;&gt;"",$G$37&lt;&gt;""),IF($F$37&gt;$G$37,$E$36,IF($F$37&lt;$G$37,$H$36,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="M32" s="29" t="n"/>
@@ -8755,13 +8741,13 @@
       <c r="W32" s="29" t="n"/>
       <c r="X32" s="29" t="n"/>
       <c r="Y32" s="33">
-        <f>IF(AND($AD$28&lt;&gt;"",$AE$28&lt;&gt;""),IF($AD$28&gt;$AE$28,$AC$28,IF($AE$28&gt;$AD$28,$AF$28,IF(AND($AD$29&lt;&gt;"",$AE$29&lt;&gt;""),IF($AD$29&gt;$AE$29,$AC$28,$AF$28),"TBD"))),"—")</f>
+        <f>IF(AND($AD$28&lt;&gt;"",$AE$28&lt;&gt;"",$AC$28&lt;&gt;"",$AF$28&lt;&gt;""),IF($AD$28&gt;$AE$28,$AC$28,IF($AE$28&gt;$AD$28,$AF$28,IF(AND($AD$29&lt;&gt;"",$AE$29&lt;&gt;""),IF($AD$29&gt;$AE$29,$AC$28,IF($AD$29&lt;$AE$29,$AF$28,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="Z32" s="10" t="n"/>
       <c r="AA32" s="10" t="n"/>
       <c r="AB32" s="34">
-        <f>IF(AND($AD$36&lt;&gt;"",$AE$36&lt;&gt;""),IF($AD$36&gt;$AE$36,$AC$36,IF($AE$36&gt;$AD$36,$AF$36,IF(AND($AD$37&lt;&gt;"",$AE$37&lt;&gt;""),IF($AD$37&gt;$AE$37,$AC$36,$AF$36),"TBD"))),"—")</f>
+        <f>IF(AND($AD$36&lt;&gt;"",$AE$36&lt;&gt;"",$AC$36&lt;&gt;"",$AF$36&lt;&gt;""),IF($AD$36&gt;$AE$36,$AC$36,IF($AE$36&gt;$AD$36,$AF$36,IF(AND($AD$37&lt;&gt;"",$AE$37&lt;&gt;""),IF($AD$37&gt;$AE$37,$AC$36,IF($AD$37&lt;$AE$37,$AF$36,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="AC32" s="29" t="n"/>
@@ -8781,11 +8767,7 @@
       </c>
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="10" t="n"/>
-      <c r="D33" s="35" t="inlineStr">
-        <is>
-          <t>◀ Enter 3rd</t>
-        </is>
-      </c>
+      <c r="D33" s="35" t="inlineStr"/>
       <c r="E33" s="29" t="n"/>
       <c r="F33" s="29" t="n"/>
       <c r="G33" s="29" t="n"/>
@@ -8942,13 +8924,13 @@
         </is>
       </c>
       <c r="E36" s="33">
-        <f>IF(AND($B$33&lt;&gt;"",$C$33&lt;&gt;""),IF($B$33&gt;$C$33,$A$33,IF($C$33&gt;$B$33,$D$33,IF(AND($B$34&lt;&gt;"",$C$34&lt;&gt;""),IF($B$34&gt;$C$34,$A$33,$D$33),"TBD"))),"—")</f>
+        <f>IF(AND($B$33&lt;&gt;"",$C$33&lt;&gt;"",$A$33&lt;&gt;"",$D$33&lt;&gt;""),IF($B$33&gt;$C$33,$A$33,IF($C$33&gt;$B$33,$D$33,IF(AND($B$34&lt;&gt;"",$C$34&lt;&gt;""),IF($B$34&gt;$C$34,$A$33,IF($B$34&lt;$C$34,$D$33,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="10" t="n"/>
       <c r="H36" s="34">
-        <f>IF(AND($B$37&lt;&gt;"",$C$37&lt;&gt;""),IF($B$37&gt;$C$37,$A$37,IF($C$37&gt;$B$37,$D$37,IF(AND($B$38&lt;&gt;"",$C$38&lt;&gt;""),IF($B$38&gt;$C$38,$A$37,$D$37),"TBD"))),"—")</f>
+        <f>IF(AND($B$37&lt;&gt;"",$C$37&lt;&gt;"",$A$37&lt;&gt;"",$D$37&lt;&gt;""),IF($B$37&gt;$C$37,$A$37,IF($C$37&gt;$B$37,$D$37,IF(AND($B$38&lt;&gt;"",$C$38&lt;&gt;""),IF($B$38&gt;$C$38,$A$37,IF($B$38&lt;$C$38,$D$37,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="I36" s="29" t="n"/>
@@ -8972,13 +8954,13 @@
       <c r="AA36" s="29" t="n"/>
       <c r="AB36" s="29" t="n"/>
       <c r="AC36" s="33">
-        <f>IF(AND($AH$33&lt;&gt;"",$AI$33&lt;&gt;""),IF($AH$33&gt;$AI$33,$AG$33,IF($AI$33&gt;$AH$33,$AJ$33,IF(AND($AH$34&lt;&gt;"",$AI$34&lt;&gt;""),IF($AH$34&gt;$AI$34,$AG$33,$AJ$33),"TBD"))),"—")</f>
+        <f>IF(AND($AH$33&lt;&gt;"",$AI$33&lt;&gt;"",$AG$33&lt;&gt;"",$AJ$33&lt;&gt;""),IF($AH$33&gt;$AI$33,$AG$33,IF($AI$33&gt;$AH$33,$AJ$33,IF(AND($AH$34&lt;&gt;"",$AI$34&lt;&gt;""),IF($AH$34&gt;$AI$34,$AG$33,IF($AH$34&lt;$AI$34,$AJ$33,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="AD36" s="10" t="n"/>
       <c r="AE36" s="10" t="n"/>
       <c r="AF36" s="34">
-        <f>IF(AND($AH$37&lt;&gt;"",$AI$37&lt;&gt;""),IF($AH$37&gt;$AI$37,$AG$37,IF($AI$37&gt;$AH$37,$AJ$37,IF(AND($AH$38&lt;&gt;"",$AI$38&lt;&gt;""),IF($AH$38&gt;$AI$38,$AG$37,$AJ$37),"TBD"))),"—")</f>
+        <f>IF(AND($AH$37&lt;&gt;"",$AI$37&lt;&gt;"",$AG$37&lt;&gt;"",$AJ$37&lt;&gt;""),IF($AH$37&gt;$AI$37,$AG$37,IF($AI$37&gt;$AH$37,$AJ$37,IF(AND($AH$38&lt;&gt;"",$AI$38&lt;&gt;""),IF($AH$38&gt;$AI$38,$AG$37,IF($AH$38&lt;$AI$38,$AJ$37,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="AG36" s="32" t="inlineStr">
@@ -8994,11 +8976,7 @@
       </c>
       <c r="B37" s="10" t="n"/>
       <c r="C37" s="10" t="n"/>
-      <c r="D37" s="35" t="inlineStr">
-        <is>
-          <t>◀ Enter 3rd</t>
-        </is>
-      </c>
+      <c r="D37" s="35" t="inlineStr"/>
       <c r="E37" s="36" t="inlineStr">
         <is>
           <t>Pen →</t>
@@ -9049,11 +9027,7 @@
       </c>
       <c r="AH37" s="10" t="n"/>
       <c r="AI37" s="10" t="n"/>
-      <c r="AJ37" s="35" t="inlineStr">
-        <is>
-          <t>◀ Enter 3rd</t>
-        </is>
-      </c>
+      <c r="AJ37" s="35" t="inlineStr"/>
     </row>
     <row r="38" ht="14" customHeight="1">
       <c r="A38" s="36" t="inlineStr">
@@ -9319,13 +9293,13 @@
       <c r="O44" s="29" t="n"/>
       <c r="P44" s="29" t="n"/>
       <c r="Q44" s="33">
-        <f>IF(AND($N$24&lt;&gt;"",$O$24&lt;&gt;""),IF($N$24&lt;$O$24,$M$24,IF($O$24&lt;$N$24,$P$24,IF(AND($N$25&lt;&gt;"",$O$25&lt;&gt;""),IF($N$25&lt;$O$25,$M$24,$P$24),"TBD"))),"—")</f>
+        <f>IF(AND($N$24&lt;&gt;"",$O$24&lt;&gt;"",$M$24&lt;&gt;"",$P$24&lt;&gt;""),IF($N$24&lt;$O$24,$M$24,IF($O$24&lt;$N$24,$P$24,IF(AND($N$25&lt;&gt;"",$O$25&lt;&gt;""),IF($N$25&lt;$O$25,$M$24,IF($N$25&gt;$O$25,$P$24,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="R44" s="10" t="n"/>
       <c r="S44" s="10" t="n"/>
       <c r="T44" s="34">
-        <f>IF(AND($V$24&lt;&gt;"",$W$24&lt;&gt;""),IF($V$24&lt;$W$24,$U$24,IF($W$24&lt;$V$24,$X$24,IF(AND($V$25&lt;&gt;"",$W$25&lt;&gt;""),IF($V$25&lt;$W$25,$U$24,$X$24),"TBD"))),"—")</f>
+        <f>IF(AND($V$24&lt;&gt;"",$W$24&lt;&gt;"",$U$24&lt;&gt;"",$X$24&lt;&gt;""),IF($V$24&lt;$W$24,$U$24,IF($W$24&lt;$V$24,$X$24,IF(AND($V$25&lt;&gt;"",$W$25&lt;&gt;""),IF($V$25&lt;$W$25,$U$24,IF($V$25&gt;$W$25,$X$24,"TBD")),"TBD"))),"—")</f>
         <v/>
       </c>
       <c r="U44" s="29" t="n"/>
